--- a/public/un-entities.xlsx
+++ b/public/un-entities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF171"/>
+  <dimension ref="A1:AG171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,11 @@
       <c r="AF1" t="inlineStr">
         <is>
           <t>socials_instagram</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>is_on_pdf</t>
         </is>
       </c>
     </row>
@@ -639,6 +644,9 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -739,6 +747,9 @@
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -801,6 +812,9 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -859,6 +873,9 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -917,6 +934,9 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1009,6 +1029,9 @@
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1067,6 +1090,9 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1125,6 +1151,9 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1183,6 +1212,9 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1241,6 +1273,9 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1299,6 +1334,9 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1357,6 +1395,9 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1456,6 +1497,9 @@
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1514,6 +1558,9 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1602,6 +1649,9 @@
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1702,6 +1752,9 @@
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1802,6 +1855,9 @@
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1904,6 +1960,9 @@
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1996,6 +2055,9 @@
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2088,6 +2150,9 @@
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2188,6 +2253,9 @@
         </is>
       </c>
       <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2290,6 +2358,9 @@
         </is>
       </c>
       <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2386,6 +2457,9 @@
         </is>
       </c>
       <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2482,6 +2556,9 @@
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2585,6 +2662,9 @@
         </is>
       </c>
       <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2684,6 +2764,9 @@
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2792,6 +2875,9 @@
         </is>
       </c>
       <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2880,6 +2966,9 @@
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2987,6 +3076,9 @@
         </is>
       </c>
       <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3094,6 +3186,9 @@
         </is>
       </c>
       <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3186,6 +3281,9 @@
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3298,6 +3396,9 @@
         </is>
       </c>
       <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3360,6 +3461,9 @@
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3422,6 +3526,9 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3484,6 +3591,9 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3543,6 +3653,9 @@
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3605,6 +3718,9 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3711,6 +3827,9 @@
         </is>
       </c>
       <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3819,6 +3938,9 @@
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3924,6 +4046,9 @@
         </is>
       </c>
       <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4016,6 +4141,9 @@
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4112,6 +4240,9 @@
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4218,6 +4349,9 @@
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4314,6 +4448,9 @@
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4406,6 +4543,9 @@
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4466,6 +4606,9 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4528,6 +4671,9 @@
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4638,6 +4784,9 @@
         </is>
       </c>
       <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4744,6 +4893,9 @@
         </is>
       </c>
       <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4846,6 +4998,9 @@
         </is>
       </c>
       <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4952,6 +5107,9 @@
         </is>
       </c>
       <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5045,6 +5203,9 @@
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5149,6 +5310,9 @@
         </is>
       </c>
       <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5250,6 +5414,9 @@
         </is>
       </c>
       <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5360,6 +5527,9 @@
         </is>
       </c>
       <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5460,6 +5630,9 @@
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5557,6 +5730,9 @@
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5654,6 +5830,9 @@
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5746,6 +5925,9 @@
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5804,6 +5986,9 @@
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5862,6 +6047,9 @@
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5954,6 +6142,9 @@
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6060,6 +6251,9 @@
         </is>
       </c>
       <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6160,6 +6354,9 @@
         </is>
       </c>
       <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6258,6 +6455,9 @@
         </is>
       </c>
       <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6346,6 +6546,9 @@
         </is>
       </c>
       <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6430,6 +6633,9 @@
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6532,6 +6738,9 @@
         </is>
       </c>
       <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6624,6 +6833,9 @@
         </is>
       </c>
       <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6712,6 +6924,9 @@
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6806,6 +7021,9 @@
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6894,6 +7112,9 @@
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6991,6 +7212,9 @@
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7083,6 +7307,9 @@
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7147,6 +7374,9 @@
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7245,6 +7475,9 @@
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7337,6 +7570,9 @@
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7425,6 +7661,9 @@
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7513,6 +7752,9 @@
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7609,6 +7851,9 @@
         </is>
       </c>
       <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7670,21 +7915,24 @@
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PoE-RES2745</t>
+          <t>SASG-PGRP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Panel of Experts pursuant to resolution 2745 (2024)</t>
+          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Panel of Experts pursuant to resolution 2745 (2024) (PoE-RES2745)</t>
+          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect (SASG-PGRP)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -7692,7 +7940,7 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://main.un.org/securitycouncil/en/sanctions/2745/panel-of-experts/work_mandate</t>
+          <t>https://www.un.org/en/genocide-prevention/</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -7704,10 +7952,20 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+        </is>
+      </c>
       <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
+      <c r="T83" t="b">
+        <v>0</v>
+      </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
@@ -7718,23 +7976,30 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>https://x.com/UNOSAPG</t>
+        </is>
+      </c>
       <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SASG-PGRP</t>
+          <t>SASG-SID</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect</t>
+          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect (SASG-PGRP)</t>
+          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement (SASG-SID)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -7742,7 +8007,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/genocide-prevention/</t>
+          <t>https://www.un.org/en/solutions-to-internal-displacement</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -7765,9 +8030,7 @@
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
-      <c r="T84" t="b">
-        <v>0</v>
-      </c>
+      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
@@ -7778,39 +8041,50 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr"/>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>https://x.com/UNOSAPG</t>
-        </is>
-      </c>
+      <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SASG-SID</t>
+          <t>SESG-GL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement</t>
+          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement (SASG-SID)</t>
+          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region (SESG-GL)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>The Special Envoy leads, coordinates and assesses implementation of the PSC Framework, to address the root causes of conflict and end recurring violence in eastern DRC and the Great Lakes.</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/solutions-to-internal-displacement</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+          <t>https://ungreatlakes.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Special_Envoy_for_the_Great_Lakes_Region</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://ungreatlakes.unmissions.org/en/news</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
@@ -7820,65 +8094,91 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
+      <c r="T85" t="b">
+        <v>0</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://ungreatlakes.unmissions.org/en/ungreatlakes/un-great-lakes-mandate
+</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
-      <c r="AC85" t="inlineStr"/>
-      <c r="AD85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>https://ungreatlakes.unmissions.org/secretary-generals-reports</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SESG-GL</t>
+          <t>SRSG-CAAC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region</t>
+          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region (SESG-GL)</t>
+          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict (SRSG-CAAC)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>The Special Envoy leads, coordinates and assesses implementation of the PSC Framework, to address the root causes of conflict and end recurring violence in eastern DRC and the Great Lakes.</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://ungreatlakes.unmissions.org/</t>
+          <t>https://childrenandarmedconflict.un.org/</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Special_Envoy_for_the_Great_Lakes_Region</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_for_Children_and_Armed_Conflict</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://ungreatlakes.unmissions.org/en/news</t>
+          <t>https://childrenandarmedconflict.un.org/news/</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
@@ -7890,24 +8190,19 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
         </is>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="b">
         <v>0</v>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://ungreatlakes.unmissions.org/en/ungreatlakes/un-great-lakes-mandate
-</t>
-        </is>
-      </c>
+      <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
@@ -7924,7 +8219,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>https://ungreatlakes.unmissions.org/secretary-generals-reports</t>
+          <t>https://childrenandarmedconflict.un.org/virtual-library/?wpv-document-type%5B%5D=annual-reports&amp;wpv_aux_current_post_id=2680&amp;wpv_aux_parent_post_id=2680&amp;wpv_view_count=110467</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -7939,21 +8234,24 @@
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SRSG-CAAC</t>
+          <t>SRSG-SVC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict</t>
+          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict (SRSG-CAAC)</t>
+          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict (SRSG-SVC)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -7961,17 +8259,17 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/</t>
+          <t>https://www.un.org/sexualviolenceinconflict/</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_for_Children_and_Armed_Conflict</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Sexual_Violence_in_Conflict</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/news/</t>
+          <t>https://www.un.org/sexualviolenceinconflict/news/</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
@@ -8012,7 +8310,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/virtual-library/?wpv-document-type%5B%5D=annual-reports&amp;wpv_aux_current_post_id=2680&amp;wpv_aux_parent_post_id=2680&amp;wpv_view_count=110467</t>
+          <t>https://www.un.org/sexualviolenceinconflict/digital-library/reports/</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -8027,21 +8325,24 @@
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SRSG-SVC</t>
+          <t>SRSG-VAC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict</t>
+          <t>Office of the Special Representative of the Secretary-General on Violence against Children</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict (SRSG-SVC)</t>
+          <t>Office of the Special Representative of the Secretary-General on Violence against Children (SRSG-VAC)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -8049,17 +8350,17 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/</t>
+          <t>https://violenceagainstchildren.un.org/</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Sexual_Violence_in_Conflict</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Violence_against_Children</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/news/</t>
+          <t>https://violenceagainstchildren.un.org/news</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
@@ -8100,7 +8401,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/digital-library/reports/</t>
+          <t>https://violenceagainstchildren.un.org/en/publications?search_api_fulltext=</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -8115,21 +8416,24 @@
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SRSG-VAC</t>
+          <t>SWEO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Violence against Children</t>
+          <t>United Nations Sustainable Development Group System-Wide Evaluation Office</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Violence against Children (SRSG-VAC)</t>
+          <t>United Nations Sustainable Development Group System-Wide Evaluation Office (SWEO)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8137,17 +8441,17 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/</t>
+          <t>https://www.un.org/system-wide-evaluation-office/</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Violence_against_Children</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
@@ -8162,11 +8466,7 @@
           <t>Secretariat</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
-        </is>
-      </c>
+      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="b">
         <v>0</v>
@@ -8188,7 +8488,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/en/publications?search_api_fulltext=</t>
+          <t>https://www.un.org/system-wide-evaluation-office/en/document-library</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -8203,21 +8503,24 @@
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SWEO</t>
+          <t>Second Committee</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>United Nations Sustainable Development Group System-Wide Evaluation Office</t>
+          <t>Economic and Financial Committee</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>United Nations Sustainable Development Group System-Wide Evaluation Office (SWEO)</t>
+          <t>Economic and Financial Committee (Second Committee)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -8225,19 +8528,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.un.org/system-wide-evaluation-office/</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+          <t>https://www.un.org/en/ga/second/index.shtml</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
@@ -8247,61 +8542,50 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="b">
-        <v>0</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Main Committees</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>https://www.un.org/system-wide-evaluation-office/en/document-library</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Second Committee</t>
+          <t>Sixth Committee</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Economic and Financial Committee</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Economic and Financial Committee (Second Committee)</t>
+          <t>Legal (Sixth Committee)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -8309,7 +8593,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/second/index.shtml</t>
+          <t>https://www.un.org/en/ga/sixth/index.shtml</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -8349,21 +8633,24 @@
       <c r="AD91" t="inlineStr"/>
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sixth Committee</t>
+          <t>StatCom</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>United Nations Statistical Commission</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Legal (Sixth Committee)</t>
+          <t>United Nations Statistical Commission (StatCom)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8371,7 +8658,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/sixth/index.shtml</t>
+          <t>https://unstats.un.org/UNSDWebsite/statcom/</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -8385,19 +8672,15 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Main Committees</t>
-        </is>
-      </c>
+          <t>Functional Commissions</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
@@ -8411,21 +8694,24 @@
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>StatCom</t>
+          <t>TDB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>United Nations Statistical Commission</t>
+          <t>Trade and Development Board</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>United Nations Statistical Commission (StatCom)</t>
+          <t>Trade and Development Board (TDB)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -8433,7 +8719,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/UNSDWebsite/statcom/</t>
+          <t>https://unctad.org/about/trade-and-development-board</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -8447,15 +8733,19 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Functional Commissions</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr"/>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
@@ -8469,21 +8759,24 @@
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TDB</t>
+          <t>Third Committee</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Trade and Development Board</t>
+          <t>Social, Humanitarian &amp; Cultural Issues</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Trade and Development Board (TDB)</t>
+          <t>Social, Humanitarian &amp; Cultural Issues (Third Committee)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -8491,7 +8784,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://unctad.org/about/trade-and-development-board</t>
+          <t>https://www.un.org/en/ga/third/index.shtml</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -8515,7 +8808,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Boards</t>
+          <t>Main Committees</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -8531,107 +8824,147 @@
       <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Third Committee</t>
+          <t>UN Tourism</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Social, Humanitarian &amp; Cultural Issues</t>
+          <t>World Tourism Organization</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Social, Humanitarian &amp; Cultural Issues (Third Committee)</t>
+          <t>World Tourism Organization (UN Tourism)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/third/index.shtml</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+          <t>https://www.untourism.int/</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_World_Tourism_Organization</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://www.unwto.org/news</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Main Committees</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr"/>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="b">
+        <v>1</v>
+      </c>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
-      <c r="AB95" t="inlineStr"/>
-      <c r="AC95" t="inlineStr"/>
-      <c r="AD95" t="inlineStr"/>
-      <c r="AE95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>https://www.e-unwto.org/</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unwto/</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>https://x.com/UNWTO</t>
+        </is>
+      </c>
       <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UN Tourism</t>
+          <t>UN Youth</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>World Tourism Organization</t>
+          <t>United Nations Youth Office</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>World Tourism Organization (UN Tourism)</t>
+          <t>United Nations Youth Office (UN Youth)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.untourism.int/</t>
+          <t>https://www.un.org/youthaffairs/</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_World_Tourism_Organization</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Youth_Office</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.unwto.org/news</t>
+          <t>https://www.un.org/youthaffairs/news</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -8640,30 +8973,26 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Madrid, Spain</t>
-        </is>
-      </c>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -8676,7 +9005,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>https://www.e-unwto.org/</t>
+          <t>https://www.un.org/youthaffairs/en/youth2030/progress-report</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -8686,48 +9015,57 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unwto/</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>https://x.com/UNWTO</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/un-youth-affairs</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UN Youth</t>
+          <t>UN-Habitat</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>United Nations Youth Office</t>
+          <t>United Nations Human Settlements Programme</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>United Nations Youth Office (UN Youth)</t>
+          <t>United Nations Human Settlements Programme (UN-Habitat)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>UN-Habitat works for a better urban future. Based in over 90 countries, we promote the development of socially and environmentally sustainable cities, towns &amp; communities. UN-Habitat strives for adequate shelter with better living standards for all.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- The secretariat of this entity is part of the United Nations Secretariat.
+</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/</t>
+          <t>https://unhabitat.org/</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Youth_Office</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Human_Settlements_Programme</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/news</t>
+          <t>https://unhabitat.org/news</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -8736,20 +9074,24 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Nairobi, Kenya</t>
+        </is>
+      </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
@@ -8758,17 +9100,17 @@
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unhabitat.org/sites/default/files/2025/02/briefing_on_monitoring_of_strategic_plan_2026-2029.pdf</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unhabitat.org/about-us/our-strategy</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/en/youth2030/progress-report</t>
+          <t>https://unhabitat.org/knowledge/research-and-publications</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -8778,67 +9120,62 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-youth-affairs</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/un-habitat/</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>https://x.com/UNHABITAT</t>
+        </is>
+      </c>
       <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>UN-Habitat</t>
+          <t>UN-Habitat Assembly</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>United Nations Human Settlements Programme</t>
+          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>United Nations Human Settlements Programme (UN-Habitat)</t>
+          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UN-Habitat works for a better urban future. Based in over 90 countries, we promote the development of socially and environmentally sustainable cities, towns &amp; communities. UN-Habitat strives for adequate shelter with better living standards for all.</t>
+          <t>On 20 December 2018, the General Assembly of the United Nations in its resolution A/RES/73/239 decided to dissolve the Governing Council of the United Nations Human Settlements Programme and to replace it with a United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly). UN-Habitat Assembly is a universal body composed of the 193 member states of the United Nations and convenes every four years (A/RES/73/239).</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- The secretariat of this entity is part of the United Nations Secretariat.
+          <t xml:space="preserve">- Current governing body of UN-Habitat (since 2019)
+- Formerly: "Governing Council of the United Nations Human Settlements Programme" (1978–2019)
 </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Human_Settlements_Programme</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/news</t>
-        </is>
-      </c>
+          <t>https://unhabitat.org/governance/un-habitat-assembly</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Nairobi, Kenya</t>
-        </is>
-      </c>
+      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -8846,86 +9183,65 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="b">
-        <v>1</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Assemblies and Councils</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/sites/default/files/2025/02/briefing_on_monitoring_of_strategic_plan_2026-2029.pdf</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/about-us/our-strategy</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/knowledge/research-and-publications</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/un-habitat/</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>https://x.com/UNHABITAT</t>
-        </is>
-      </c>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>UN-Habitat Assembly</t>
+          <t>UN-OHRLLS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme</t>
+          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly)</t>
+          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States (UN-OHRLLS)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>On 20 December 2018, the General Assembly of the United Nations in its resolution A/RES/73/239 decided to dissolve the Governing Council of the United Nations Human Settlements Programme and to replace it with a United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly). UN-Habitat Assembly is a universal body composed of the 193 member states of the United Nations and convenes every four years (A/RES/73/239).</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Current governing body of UN-Habitat (since 2019)
-- Formerly: "Governing Council of the United Nations Human Settlements Programme" (1978–2019)
-</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/governance/un-habitat-assembly</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+          <t>https://www.un.org/ohrlls/</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_of_the_High_Representative_for_the_Least_Developed_Countries,_Landlocked_Developing_Countries_and_Small_Island_Developing_States</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://www.un.org/ohrlls/news</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
@@ -8935,278 +9251,317 @@
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>Assemblies and Councils</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr"/>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="b">
+        <v>0</v>
+      </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>https://open.unwomen.org/en/global-results/overview</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>https://www.un.org/ohrlls/sites/www.un.org.ohrlls/files/dpoa_roadmap_2024_draft.pdf</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>https://www.un.org/ohrlls/content/resources</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/un-ohrlls/</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>https://x.com/UNOHRLLS</t>
+        </is>
+      </c>
       <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UN-OHRLLS</t>
+          <t>UN-Women</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States</t>
+          <t>United Nations Entity for Gender Equality and the Empowerment of Women</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States (UN-OHRLLS)</t>
+          <t>United Nations Entity for Gender Equality and the Empowerment of Women (UN-Women)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>UN Women is the global champion for gender equality, working to develop and uphold standards and create an environment in which every woman and girl can exercise her human rights and live up to her full potential. We are trusted partners for advocates and decision-makers from all walks of life, and a leader in the effort to achieve gender equality.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/</t>
+          <t>https://www.unwomen.org/</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_of_the_High_Representative_for_the_Least_Developed_Countries,_Landlocked_Developing_Countries_and_Small_Island_Developing_States</t>
+          <t>https://en.wikipedia.org/wiki/UN_Women</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/news</t>
+          <t>https://www.unwomen.org/en/news</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://data.unwomen.org/</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>New York City, USA</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Other Entities</t>
         </is>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>https://www.unwomen.org/sites/default/files/2025-08/unw_org_chart_internal_20250806.pdf</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>https://www.unwomen.org/en/executive-board/strategic-plan-review/financial-resources</t>
+        </is>
+      </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>https://open.unwomen.org/en/global-results/overview</t>
+          <t>https://www.unwomen.org/sites/default/files/2025-10/un-women-strategic-plan-2026-2029-integrated-results-and-resources-framework-en.pdf</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/sites/www.un.org.ohrlls/files/dpoa_roadmap_2024_draft.pdf</t>
+          <t>https://www.unwomen.org/sites/default/files/2022-05/UN%20Women%20SP%20IRRF%202022-2025.pdf</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/content/resources</t>
+          <t>https://www.unwomen.org/en/digital-library/annual-report</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://data.unwomen.org/data-portal</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-ohrlls/</t>
+          <t>https://www.linkedin.com/company/un-women/</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>https://x.com/UNOHRLLS</t>
+          <t>https://x.com/UN_Women</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UN-Women</t>
+          <t>UNAIDS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>United Nations Entity for Gender Equality and the Empowerment of Women</t>
+          <t>Joint United Nations Programme on HIV/AIDS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>United Nations Entity for Gender Equality and the Empowerment of Women (UN-Women)</t>
+          <t>Joint United Nations Programme on HIV/AIDS (UNAIDS)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UN Women is the global champion for gender equality, working to develop and uphold standards and create an environment in which every woman and girl can exercise her human rights and live up to her full potential. We are trusted partners for advocates and decision-makers from all walks of life, and a leader in the effort to achieve gender equality.</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+          <t>UNAIDS brings together the efforts and resources of 10 UN system organizations to help prevent new HIV infections, care for people living with HIV and mitigate the impact of the epidemic.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/</t>
+          <t>https://www.unaids.org/en</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UN_Women</t>
+          <t>https://en.wikipedia.org/wiki/Joint_United_Nations_Programme_on_HIV/AIDS</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/news</t>
+          <t>https://www.unaids.org/en/news</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>https://data.unwomen.org/</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>New York City, USA</t>
+          <t>Geneva, Switzerland</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Other Bodies</t>
         </is>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>https://www.unwomen.org/sites/default/files/2025-08/unw_org_chart_internal_20250806.pdf</t>
-        </is>
-      </c>
+      <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/executive-board/strategic-plan-review/financial-resources</t>
+          <t>https://www.unaids.org/en/topic/resources</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/sites/default/files/2025-10/un-women-strategic-plan-2026-2029-integrated-results-and-resources-framework-en.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/sites/default/files/2022-05/UN%20Women%20SP%20IRRF%202022-2025.pdf</t>
+          <t>https://www.unaids.org/sites/default/files/media_asset/global-AIDS-strategy-2021-2026_en.pdf</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/digital-library/annual-report</t>
+          <t>https://www.unaids.org/en/topics/resources/publications</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>https://data.unwomen.org/data-portal</t>
+          <t>https://open.unaids.org/</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-women/</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>https://x.com/UN_Women</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/unaids/</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>UNAIDS</t>
+          <t>UNAMA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Joint United Nations Programme on HIV/AIDS</t>
+          <t>United Nations Assistance Mission in Afghanistan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Joint United Nations Programme on HIV/AIDS (UNAIDS)</t>
+          <t>United Nations Assistance Mission in Afghanistan (UNAMA)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UNAIDS brings together the efforts and resources of 10 UN system organizations to help prevent new HIV infections, care for people living with HIV and mitigate the impact of the epidemic.</t>
+          <t>UNAMA’s mission is to support the people and institutions of Afghanistan in achieving peace and stability, in line with the rights and obligations enshrined in the Afghan constitution.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en</t>
+          <t>https://unama.unmissions.org/</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Joint_United_Nations_Programme_on_HIV/AIDS</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Assistance_Mission_in_Afghanistan</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en/news</t>
+          <t>https://unama.unmissions.org/news</t>
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
@@ -9215,19 +9570,15 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Other Bodies</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S102" t="inlineStr"/>
@@ -9238,11 +9589,7 @@
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>https://www.unaids.org/en/topic/resources</t>
-        </is>
-      </c>
+      <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -9250,63 +9597,66 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/sites/default/files/media_asset/global-AIDS-strategy-2021-2026_en.pdf</t>
+          <t>https://unama.unmissions.org/sites/default/files/unsf_afghanistan_formatted_20230629.pdf</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en/topics/resources/publications</t>
+          <t>https://unama.unmissions.org/secretary-general-reports</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>https://open.unaids.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unaids/</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr"/>
       <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UNAMA</t>
+          <t>UNAOC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>United Nations Assistance Mission in Afghanistan</t>
+          <t>United Nations Alliance of Civilizations</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>United Nations Assistance Mission in Afghanistan (UNAMA)</t>
+          <t>United Nations Alliance of Civilizations (UNAOC)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UNAMA’s mission is to support the people and institutions of Afghanistan in achieving peace and stability, in line with the rights and obligations enshrined in the Afghan constitution.</t>
+          <t>UNAOC aims to bridge divides, and promote harmony among the nations, all with a view toward preventing conflict and promoting social cohesion.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/</t>
+          <t>https://www.unaoc.org/</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Assistance_Mission_in_Afghanistan</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Alliance_of_Civilizations</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/news</t>
+          <t>https://www.unaoc.org/category/news/</t>
         </is>
       </c>
       <c r="J103" t="inlineStr"/>
@@ -9318,14 +9668,10 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>Special Political Missions and Other Political Presences</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="b">
         <v>0</v>
@@ -9342,12 +9688,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/sites/default/files/unsf_afghanistan_formatted_20230629.pdf</t>
+          <t>https://www.unaoc.org/wp-content/uploads/UNAOC-Action-Plan-POA-2024-2026-250203_web.pdf</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/secretary-general-reports</t>
+          <t>https://www.unaoc.org/resource-type/unaoc-annual-reports/</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -9357,50 +9703,41 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/united-nations-alliance-of-civilizations/</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UNAOC</t>
+          <t>UNCCD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>United Nations Alliance of Civilizations</t>
+          <t>United Nations Convention to Combat Desertification</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>United Nations Alliance of Civilizations (UNAOC)</t>
+          <t>United Nations Convention to Combat Desertification (UNCCD)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>UNAOC aims to bridge divides, and promote harmony among the nations, all with a view toward preventing conflict and promoting social cohesion.</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.unaoc.org/</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Alliance_of_Civilizations</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>https://www.unaoc.org/category/news/</t>
-        </is>
-      </c>
+          <t>https://www.unccd.int/</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -9415,64 +9752,54 @@
       </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
-      <c r="T104" t="b">
-        <v>0</v>
-      </c>
+      <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>https://www.unaoc.org/wp-content/uploads/UNAOC-Action-Plan-POA-2024-2026-250203_web.pdf</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>https://www.unaoc.org/resource-type/unaoc-annual-reports/</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-alliance-of-civilizations/</t>
-        </is>
-      </c>
+          <t>https://www.unccd.int/convention/governance/strategic-framework-2018-2030</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UNCCD</t>
+          <t>UNCDF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>United Nations Convention to Combat Desertification</t>
+          <t>United Nations Capital Development Fund</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>United Nations Convention to Combat Desertification (UNCCD)</t>
+          <t>United Nations Capital Development Fund (UNCDF)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>The United Nations Capital Development Fund's mission is to contribute to job creation, sustained economic growth and equitable prosperity in almost 80 developing countries and nearly all LDCs.
+We do so by crowding in capital through the deployment of risk-absorbing financial instruments, mechanisms and structuring advisory. In partnership with UN entities and development partners, UNCDF operates with speed and agility to deliver scalable, blended finance solutions to drive systemic change and pave the way for commercial finance and scale up by development finance institutions and multilateral development banks.</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.unccd.int/</t>
+          <t>https://www.uncdf.org/</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -9486,12 +9813,18 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
       <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
+      <c r="T105" t="b">
+        <v>0</v>
+      </c>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
@@ -9500,7 +9833,7 @@
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>https://www.unccd.int/convention/governance/strategic-framework-2018-2030</t>
+          <t>https://www.uncdf.org/article/3208/making-finance-work-for-inclusion-uncdf-presents-new-four-year-strategic-framework-to-its-board</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -9508,34 +9841,32 @@
       <c r="AD105" t="inlineStr"/>
       <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UNCDF</t>
+          <t>UNCITRAL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>United Nations Capital Development Fund</t>
+          <t>United Nations Commission on International Trade Law</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>United Nations Capital Development Fund (UNCDF)</t>
+          <t>United Nations Commission on International Trade Law (UNCITRAL)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>The United Nations Capital Development Fund's mission is to contribute to job creation, sustained economic growth and equitable prosperity in almost 80 developing countries and nearly all LDCs.
-We do so by crowding in capital through the deployment of risk-absorbing financial instruments, mechanisms and structuring advisory. In partnership with UN entities and development partners, UNCDF operates with speed and agility to deliver scalable, blended finance solutions to drive systemic change and pave the way for commercial finance and scale up by development finance institutions and multilateral development banks.</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.uncdf.org/</t>
+          <t>https://uncitral.un.org/</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -9554,56 +9885,75 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="b">
-        <v>0</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>https://www.uncdf.org/article/3208/making-finance-work-for-inclusion-uncdf-presents-new-four-year-strategic-framework-to-its-board</t>
-        </is>
-      </c>
+      <c r="AA106" t="inlineStr"/>
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr"/>
       <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UNCITRAL</t>
+          <t>UNCTAD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>United Nations Commission on International Trade Law</t>
+          <t>United Nations Conference on Trade and Development</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>United Nations Commission on International Trade Law (UNCITRAL)</t>
+          <t>United Nations Conference on Trade and Development (UNCTAD)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>UNCTAD supports developing countries to access the benefits of a globalized economy more fairly and effectively and helps equip them to deal with the potential drawbacks of greater economic integration.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- The secretariat of this entity is part of the United Nations Secretariat.
+</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://uncitral.un.org/</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+          <t>https://unctad.org/</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Conference_on_Trade_and_Development</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://unctad.org/news</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
@@ -9618,72 +9968,75 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr"/>
+          <t>Other Entities</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="b">
+        <v>1</v>
+      </c>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
-      <c r="AB107" t="inlineStr"/>
-      <c r="AC107" t="inlineStr"/>
-      <c r="AD107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>https://unctad.org/dmfas/our_Strategic_Plan</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>https://unctad.org/publications-search?Operator=and&amp;keys=annual</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unctad/</t>
+        </is>
+      </c>
       <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UNCTAD</t>
+          <t>UNDC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United Nations Conference on Trade and Development</t>
+          <t>Disarmament Commission</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>United Nations Conference on Trade and Development (UNCTAD)</t>
+          <t>Disarmament Commission (UNDC)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>UNCTAD supports developing countries to access the benefits of a globalized economy more fairly and effectively and helps equip them to deal with the potential drawbacks of greater economic integration.</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- The secretariat of this entity is part of the United Nations Secretariat.
-</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://unctad.org/</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Conference_on_Trade_and_Development</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>https://unctad.org/news</t>
-        </is>
-      </c>
+          <t>https://disarmament.unoda.org/en/united-nations-disarmament-commission</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
@@ -9698,60 +10051,45 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Other Entities</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="b">
-        <v>1</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>https://unctad.org/dmfas/our_Strategic_Plan</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>https://unctad.org/publications-search?Operator=and&amp;keys=annual</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unctad/</t>
-        </is>
-      </c>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UNDC</t>
+          <t>UNDEF</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Disarmament Commission</t>
+          <t>United Nations Democracy Fund</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Disarmament Commission (UNDC)</t>
+          <t>United Nations Democracy Fund (UNDEF)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -9759,7 +10097,7 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://disarmament.unoda.org/en/united-nations-disarmament-commission</t>
+          <t>https://www.un.org/democracyfund/</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -9773,19 +10111,11 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
@@ -9799,33 +10129,48 @@
       <c r="AD109" t="inlineStr"/>
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UNDEF</t>
+          <t>UNDOF</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Nations Democracy Fund</t>
+          <t>United Nations Disengagement Observer Force</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>United Nations Democracy Fund (UNDEF)</t>
+          <t>United Nations Disengagement Observer Force (UNDOF)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>The UNDOF assists in maintaining the ceasefire between Israel and Syria, supervising the disengagement of Israeli and Syrian forces; as well as the areas of separation and limitation, as provided in the May 1974 Agreement on Disengagement.</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.un.org/democracyfund/</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+          <t>https://undof.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Disengagement_Observer_Force</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://undof.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
@@ -9835,177 +10180,209 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
+          <t>Security Council</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Peacekeeping Operations</t>
+        </is>
+      </c>
       <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
+      <c r="T110" t="b">
+        <v>0</v>
+      </c>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr"/>
-      <c r="AB110" t="inlineStr"/>
-      <c r="AC110" t="inlineStr"/>
-      <c r="AD110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>https://undof.unmissions.org/reports-statements</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UNDOF</t>
+          <t>UNDP</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force</t>
+          <t>United Nations Development Programme</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force (UNDOF)</t>
+          <t>United Nations Development Programme (UNDP)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>The UNDOF assists in maintaining the ceasefire between Israel and Syria, supervising the disengagement of Israeli and Syrian forces; as well as the areas of separation and limitation, as provided in the May 1974 Agreement on Disengagement.</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
+          <t>The UNDP helps build inclusive, sustainable and resilient societies and provides expert advice, training and financial support. Special attention is paid to the needs of the Least Developed Countries and countries emerging from conflict.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
+</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://undof.unmissions.org/</t>
+          <t>https://www.undp.org/</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Disengagement_Observer_Force</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Programme</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://undof.unmissions.org/news</t>
+          <t>https://www.undp.org/news</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
+      <c r="N111" t="b">
+        <v>1</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>https://jobs.undp.org/</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>New York City, USA</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Peacekeeping Operations</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/organizational-chart</t>
+        </is>
+      </c>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://rolhr.undp.org/annualreport/2023/results-framework.html</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://strategicplan.undp.org/</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>https://undof.unmissions.org/reports-statements</t>
+          <t>https://annualreport.undp.org/</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://open.undp.org/</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE111" t="inlineStr"/>
-      <c r="AF111" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/united-nations-development-programme/</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>https://x.com/UNDP</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/undp/</t>
+        </is>
+      </c>
+      <c r="AG111" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>UNDP UNFPA UNOPS EB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>United Nations Development Programme</t>
+          <t>Executive Board of UNDP, UNFPA and UNOPS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>United Nations Development Programme (UNDP)</t>
+          <t>Executive Board of UNDP, UNFPA and UNOPS (UNDP UNFPA UNOPS EB)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>The UNDP helps build inclusive, sustainable and resilient societies and provides expert advice, training and financial support. Special attention is paid to the needs of the Least Developed Countries and countries emerging from conflict.</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
-</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.undp.org/</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Programme</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/news</t>
-        </is>
-      </c>
+          <t>https://www.unfpa.org/executive-board</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="b">
-        <v>1</v>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>https://jobs.undp.org/</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>New York City, USA</t>
-        </is>
-      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -10013,56 +10390,29 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="b">
-        <v>1</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/organizational-chart</t>
-        </is>
-      </c>
+      <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>https://rolhr.undp.org/annualreport/2023/results-framework.html</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>https://strategicplan.undp.org/</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>https://annualreport.undp.org/</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>https://open.undp.org/</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-development-programme/</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>https://x.com/UNDP</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/undp/</t>
-        </is>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -10156,6 +10506,9 @@
         </is>
       </c>
       <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10223,6 +10576,9 @@
       <c r="AD114" t="inlineStr"/>
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10333,6 +10689,9 @@
         </is>
       </c>
       <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10443,6 +10802,9 @@
         </is>
       </c>
       <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10501,6 +10863,9 @@
       <c r="AD117" t="inlineStr"/>
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10597,6 +10962,9 @@
         </is>
       </c>
       <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10708,6 +11076,9 @@
         </is>
       </c>
       <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10804,6 +11175,9 @@
       </c>
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10892,6 +11266,9 @@
       </c>
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10980,6 +11357,9 @@
       </c>
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11085,6 +11465,9 @@
       </c>
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11200,6 +11583,9 @@
         </is>
       </c>
       <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11262,6 +11648,9 @@
       <c r="AD125" t="inlineStr"/>
       <c r="AE125" t="inlineStr"/>
       <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11328,6 +11717,9 @@
       <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11432,6 +11824,9 @@
         </is>
       </c>
       <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11542,6 +11937,9 @@
         </is>
       </c>
       <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11636,6 +12034,9 @@
       </c>
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11732,6 +12133,9 @@
         </is>
       </c>
       <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11838,6 +12242,9 @@
         </is>
       </c>
       <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11900,6 +12307,9 @@
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12005,6 +12415,9 @@
         </is>
       </c>
       <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12106,6 +12519,9 @@
         </is>
       </c>
       <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12198,6 +12614,9 @@
       </c>
       <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12295,6 +12714,9 @@
       </c>
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12392,6 +12814,9 @@
       </c>
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12491,6 +12916,9 @@
         </is>
       </c>
       <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12581,6 +13009,9 @@
       </c>
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12669,6 +13100,9 @@
       </c>
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12759,6 +13193,9 @@
       </c>
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12824,6 +13261,9 @@
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12929,6 +13369,9 @@
       </c>
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12989,6 +13432,9 @@
       <c r="AD144" t="inlineStr"/>
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13079,6 +13525,9 @@
       </c>
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13180,6 +13629,9 @@
       </c>
       <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13234,6 +13686,9 @@
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13292,6 +13747,9 @@
       <c r="AD148" t="inlineStr"/>
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13389,6 +13847,9 @@
       </c>
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13457,6 +13918,9 @@
       <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13564,6 +14028,9 @@
       </c>
       <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13657,6 +14124,9 @@
       </c>
       <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13749,6 +14219,9 @@
       </c>
       <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13843,6 +14316,9 @@
       </c>
       <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13907,6 +14383,9 @@
       <c r="AD155" t="inlineStr"/>
       <c r="AE155" t="inlineStr"/>
       <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14013,6 +14492,9 @@
         </is>
       </c>
       <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14067,6 +14549,9 @@
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr"/>
       <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14159,6 +14644,9 @@
       </c>
       <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14256,6 +14744,9 @@
       </c>
       <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14362,6 +14853,9 @@
         </is>
       </c>
       <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14424,6 +14918,9 @@
       <c r="AD161" t="inlineStr"/>
       <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14522,6 +15019,9 @@
         <is>
           <t>https://www.instagram.com/unvolunteers/</t>
         </is>
+      </c>
+      <c r="AG162" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -14615,6 +15115,9 @@
       </c>
       <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14727,6 +15230,9 @@
         </is>
       </c>
       <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14846,6 +15352,9 @@
         </is>
       </c>
       <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14908,6 +15417,9 @@
       <c r="AD166" t="inlineStr"/>
       <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15040,6 +15552,9 @@
         </is>
       </c>
       <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15152,6 +15667,9 @@
         </is>
       </c>
       <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15264,6 +15782,9 @@
         </is>
       </c>
       <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15373,6 +15894,9 @@
         </is>
       </c>
       <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15489,6 +16013,9 @@
         </is>
       </c>
       <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/un-entities.xlsx
+++ b/public/un-entities.xlsx
@@ -7858,30 +7858,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PBSO</t>
+          <t>PBC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Peacebuilding Support Office</t>
+          <t>Peacebuilding Commission</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Peacebuilding Support Office (PBSO)</t>
+          <t>Peacebuilding Commission (PBC)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>As part of the Department of Political and Peacebuilding Affairs (DPPA), the Peacebuilding Support Office (PBSO) serves as a facilitator to enhance coherence and collaboration across the UN system and with partners in support of nationally owned efforts to build and sustain peace. Established in 2005, PBSO draws together expertise to advance impactful system-wide action, policies and guidance and fosters an integrated and inclusive approach to prevention and sustaining peace.
-The Office comprises the Peacebuilding Commission Support Branch, the Financing for Peacebuilding Branch and the Peacebuilding Strategy and Partnerships Branch. Led by Assistant Secretary-General, Elizabeth Spehar, PBSO assists and supports the Peacebuilding Commission (PBC) with strategic advice and policy guidance, manages the Peacebuilding Fund (PBF) on behalf of the Secretary-General, and works to enhance system-wide coherence and partnerships with UN and non-UN actors in support of building and sustaining peace in partner countries.</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.un.org/peacebuilding/</t>
+          <t>https://www.un.org/peacebuilding/commission</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -7895,14 +7890,12 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>['General Assembly', 'Security Council']</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
-      <c r="T82" t="b">
-        <v>0</v>
-      </c>
+      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
@@ -7916,31 +7909,36 @@
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SASG-PGRP</t>
+          <t>PBSO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect</t>
+          <t>Peacebuilding Support Office</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect (SASG-PGRP)</t>
+          <t>Peacebuilding Support Office (PBSO)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>As part of the Department of Political and Peacebuilding Affairs (DPPA), the Peacebuilding Support Office (PBSO) serves as a facilitator to enhance coherence and collaboration across the UN system and with partners in support of nationally owned efforts to build and sustain peace. Established in 2005, PBSO draws together expertise to advance impactful system-wide action, policies and guidance and fosters an integrated and inclusive approach to prevention and sustaining peace.
+The Office comprises the Peacebuilding Commission Support Branch, the Financing for Peacebuilding Branch and the Peacebuilding Strategy and Partnerships Branch. Led by Assistant Secretary-General, Elizabeth Spehar, PBSO assists and supports the Peacebuilding Commission (PBC) with strategic advice and policy guidance, manages the Peacebuilding Fund (PBF) on behalf of the Secretary-General, and works to enhance system-wide coherence and partnerships with UN and non-UN actors in support of building and sustaining peace in partner countries.</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/genocide-prevention/</t>
+          <t>https://www.un.org/peacebuilding/</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -7957,11 +7955,7 @@
           <t>Secretariat</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
-        </is>
-      </c>
+      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="b">
         <v>0</v>
@@ -7976,11 +7970,7 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>https://x.com/UNOSAPG</t>
-        </is>
-      </c>
+      <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
@@ -7989,17 +7979,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SASG-SID</t>
+          <t>SASG-PGRP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement</t>
+          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement (SASG-SID)</t>
+          <t>Office of the Special Advisers to the Secretary-General on the Prevention of Genocide and the Responsibility to Protect (SASG-PGRP)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8007,7 +7997,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/solutions-to-internal-displacement</t>
+          <t>https://www.un.org/en/genocide-prevention/</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -8030,7 +8020,9 @@
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
+      <c r="T84" t="b">
+        <v>0</v>
+      </c>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
@@ -8041,50 +8033,42 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr"/>
-      <c r="AE84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>https://x.com/UNOSAPG</t>
+        </is>
+      </c>
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SESG-GL</t>
+          <t>SASG-SID</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region</t>
+          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region (SESG-GL)</t>
+          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement (SASG-SID)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>The Special Envoy leads, coordinates and assesses implementation of the PSC Framework, to address the root causes of conflict and end recurring violence in eastern DRC and the Great Lakes.</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://ungreatlakes.unmissions.org/</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Special_Envoy_for_the_Great_Lakes_Region</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>https://ungreatlakes.unmissions.org/en/news</t>
-        </is>
-      </c>
+          <t>https://www.un.org/en/solutions-to-internal-displacement</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
@@ -8094,53 +8078,26 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
         </is>
       </c>
       <c r="S85" t="inlineStr"/>
-      <c r="T85" t="b">
-        <v>0</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://ungreatlakes.unmissions.org/en/ungreatlakes/un-great-lakes-mandate
-</t>
-        </is>
-      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>https://ungreatlakes.unmissions.org/secretary-generals-reports</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
@@ -8150,35 +8107,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SRSG-CAAC</t>
+          <t>SESG-GL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict</t>
+          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict (SRSG-CAAC)</t>
+          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region (SESG-GL)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>The Special Envoy leads, coordinates and assesses implementation of the PSC Framework, to address the root causes of conflict and end recurring violence in eastern DRC and the Great Lakes.</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/</t>
+          <t>https://ungreatlakes.unmissions.org/</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_for_Children_and_Armed_Conflict</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Special_Envoy_for_the_Great_Lakes_Region</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/news/</t>
+          <t>https://ungreatlakes.unmissions.org/en/news</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
@@ -8190,19 +8151,24 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="b">
         <v>0</v>
       </c>
-      <c r="U86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://ungreatlakes.unmissions.org/en/ungreatlakes/un-great-lakes-mandate
+</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
@@ -8219,7 +8185,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/virtual-library/?wpv-document-type%5B%5D=annual-reports&amp;wpv_aux_current_post_id=2680&amp;wpv_aux_parent_post_id=2680&amp;wpv_view_count=110467</t>
+          <t>https://ungreatlakes.unmissions.org/secretary-generals-reports</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -8241,17 +8207,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SRSG-SVC</t>
+          <t>SRSG-CAAC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict</t>
+          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict (SRSG-SVC)</t>
+          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict (SRSG-CAAC)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -8259,17 +8225,17 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/</t>
+          <t>https://childrenandarmedconflict.un.org/</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Sexual_Violence_in_Conflict</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_for_Children_and_Armed_Conflict</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/news/</t>
+          <t>https://childrenandarmedconflict.un.org/news/</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
@@ -8310,7 +8276,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/digital-library/reports/</t>
+          <t>https://childrenandarmedconflict.un.org/virtual-library/?wpv-document-type%5B%5D=annual-reports&amp;wpv_aux_current_post_id=2680&amp;wpv_aux_parent_post_id=2680&amp;wpv_view_count=110467</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -8332,17 +8298,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SRSG-VAC</t>
+          <t>SRSG-SVC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Violence against Children</t>
+          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Violence against Children (SRSG-VAC)</t>
+          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict (SRSG-SVC)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -8350,17 +8316,17 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/</t>
+          <t>https://www.un.org/sexualviolenceinconflict/</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Violence_against_Children</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Sexual_Violence_in_Conflict</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/news</t>
+          <t>https://www.un.org/sexualviolenceinconflict/news/</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
@@ -8401,7 +8367,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/en/publications?search_api_fulltext=</t>
+          <t>https://www.un.org/sexualviolenceinconflict/digital-library/reports/</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -8423,17 +8389,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SWEO</t>
+          <t>SRSG-VAC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>United Nations Sustainable Development Group System-Wide Evaluation Office</t>
+          <t>Office of the Special Representative of the Secretary-General on Violence against Children</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>United Nations Sustainable Development Group System-Wide Evaluation Office (SWEO)</t>
+          <t>Office of the Special Representative of the Secretary-General on Violence against Children (SRSG-VAC)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8441,17 +8407,17 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.un.org/system-wide-evaluation-office/</t>
+          <t>https://violenceagainstchildren.un.org/</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Violence_against_Children</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://violenceagainstchildren.un.org/news</t>
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
@@ -8466,7 +8432,11 @@
           <t>Secretariat</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="b">
         <v>0</v>
@@ -8488,7 +8458,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>https://www.un.org/system-wide-evaluation-office/en/document-library</t>
+          <t>https://violenceagainstchildren.un.org/en/publications?search_api_fulltext=</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -8504,23 +8474,23 @@
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Second Committee</t>
+          <t>SWEO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Economic and Financial Committee</t>
+          <t>United Nations Sustainable Development Group System-Wide Evaluation Office</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Economic and Financial Committee (Second Committee)</t>
+          <t>United Nations Sustainable Development Group System-Wide Evaluation Office (SWEO)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -8528,11 +8498,19 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/second/index.shtml</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+          <t>https://www.un.org/system-wide-evaluation-office/</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
@@ -8542,30 +8520,44 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>Main Committees</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr"/>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="b">
+        <v>0</v>
+      </c>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
-      <c r="AC90" t="inlineStr"/>
-      <c r="AD90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>https://www.un.org/system-wide-evaluation-office/en/document-library</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
@@ -8575,17 +8567,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sixth Committee</t>
+          <t>Second Committee</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Economic and Financial Committee</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Legal (Sixth Committee)</t>
+          <t>Economic and Financial Committee (Second Committee)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -8593,7 +8585,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/sixth/index.shtml</t>
+          <t>https://www.un.org/en/ga/second/index.shtml</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -8640,17 +8632,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>StatCom</t>
+          <t>Sixth Committee</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>United Nations Statistical Commission</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>United Nations Statistical Commission (StatCom)</t>
+          <t>Legal (Sixth Committee)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8658,7 +8650,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/UNSDWebsite/statcom/</t>
+          <t>https://www.un.org/en/ga/sixth/index.shtml</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -8672,15 +8664,19 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Functional Commissions</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr"/>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Main Committees</t>
+        </is>
+      </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
@@ -8695,23 +8691,23 @@
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TDB</t>
+          <t>StatCom</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Trade and Development Board</t>
+          <t>United Nations Statistical Commission</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Trade and Development Board (TDB)</t>
+          <t>United Nations Statistical Commission (StatCom)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -8719,7 +8715,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://unctad.org/about/trade-and-development-board</t>
+          <t>https://unstats.un.org/UNSDWebsite/statcom/</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -8733,19 +8729,15 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
+          <t>Functional Commissions</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
@@ -8760,23 +8752,23 @@
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Third Committee</t>
+          <t>TDB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Social, Humanitarian &amp; Cultural Issues</t>
+          <t>Trade and Development Board</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Social, Humanitarian &amp; Cultural Issues (Third Committee)</t>
+          <t>Trade and Development Board (TDB)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -8784,7 +8776,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/third/index.shtml</t>
+          <t>https://unctad.org/about/trade-and-development-board</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -8808,7 +8800,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Main Committees</t>
+          <t>Boards</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -8831,140 +8823,106 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>UN Tourism</t>
+          <t>Third Committee</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>World Tourism Organization</t>
+          <t>Social, Humanitarian &amp; Cultural Issues</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>World Tourism Organization (UN Tourism)</t>
+          <t>Social, Humanitarian &amp; Cultural Issues (Third Committee)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.untourism.int/</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_World_Tourism_Organization</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>https://www.unwto.org/news</t>
-        </is>
-      </c>
+          <t>https://www.un.org/en/ga/third/index.shtml</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Madrid, Spain</t>
-        </is>
-      </c>
+      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="b">
-        <v>1</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Main Committees</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>https://www.e-unwto.org/</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unwto/</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>https://x.com/UNWTO</t>
-        </is>
-      </c>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UN Youth</t>
+          <t>UN Tourism</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>United Nations Youth Office</t>
+          <t>World Tourism Organization</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>United Nations Youth Office (UN Youth)</t>
+          <t>World Tourism Organization (UN Tourism)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/</t>
+          <t>https://www.untourism.int/</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Youth_Office</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_World_Tourism_Organization</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/news</t>
+          <t>https://www.unwto.org/news</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -8973,26 +8931,30 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
       <c r="Z96" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -9005,7 +8967,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/en/youth2030/progress-report</t>
+          <t>https://www.e-unwto.org/</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -9015,10 +8977,14 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-youth-affairs</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/unwto/</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>https://x.com/UNWTO</t>
+        </is>
+      </c>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>1</v>
@@ -9027,45 +8993,35 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UN-Habitat</t>
+          <t>UN Youth</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>United Nations Human Settlements Programme</t>
+          <t>United Nations Youth Office</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>United Nations Human Settlements Programme (UN-Habitat)</t>
+          <t>United Nations Youth Office (UN Youth)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>UN-Habitat works for a better urban future. Based in over 90 countries, we promote the development of socially and environmentally sustainable cities, towns &amp; communities. UN-Habitat strives for adequate shelter with better living standards for all.</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- The secretariat of this entity is part of the United Nations Secretariat.
-</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/</t>
+          <t>https://www.un.org/youthaffairs/</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Human_Settlements_Programme</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Youth_Office</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/news</t>
+          <t>https://www.un.org/youthaffairs/news</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -9074,24 +9030,20 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Nairobi, Kenya</t>
-        </is>
-      </c>
+      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
         </is>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
@@ -9100,17 +9052,17 @@
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/sites/default/files/2025/02/briefing_on_monitoring_of_strategic_plan_2026-2029.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/about-us/our-strategy</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/knowledge/research-and-publications</t>
+          <t>https://www.un.org/youthaffairs/en/youth2030/progress-report</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -9120,14 +9072,10 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-habitat/</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>https://x.com/UNHABITAT</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/un-youth-affairs</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>1</v>
@@ -9136,46 +9084,58 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>UN-Habitat Assembly</t>
+          <t>UN-Habitat</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme</t>
+          <t>United Nations Human Settlements Programme</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly)</t>
+          <t>United Nations Human Settlements Programme (UN-Habitat)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>On 20 December 2018, the General Assembly of the United Nations in its resolution A/RES/73/239 decided to dissolve the Governing Council of the United Nations Human Settlements Programme and to replace it with a United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly). UN-Habitat Assembly is a universal body composed of the 193 member states of the United Nations and convenes every four years (A/RES/73/239).</t>
+          <t>UN-Habitat works for a better urban future. Based in over 90 countries, we promote the development of socially and environmentally sustainable cities, towns &amp; communities. UN-Habitat strives for adequate shelter with better living standards for all.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Current governing body of UN-Habitat (since 2019)
-- Formerly: "Governing Council of the United Nations Human Settlements Programme" (1978–2019)
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- The secretariat of this entity is part of the United Nations Secretariat.
 </t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/governance/un-habitat-assembly</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+          <t>https://unhabitat.org/</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Human_Settlements_Programme</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://unhabitat.org/news</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Nairobi, Kenya</t>
+        </is>
+      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -9183,65 +9143,89 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>Assemblies and Councils</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr"/>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="b">
+        <v>1</v>
+      </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
-      <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="inlineStr"/>
-      <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>https://unhabitat.org/sites/default/files/2025/02/briefing_on_monitoring_of_strategic_plan_2026-2029.pdf</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>https://unhabitat.org/about-us/our-strategy</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>https://unhabitat.org/knowledge/research-and-publications</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/un-habitat/</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>https://x.com/UNHABITAT</t>
+        </is>
+      </c>
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>UN-OHRLLS</t>
+          <t>UN-Habitat Assembly</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States</t>
+          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States (UN-OHRLLS)</t>
+          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>On 20 December 2018, the General Assembly of the United Nations in its resolution A/RES/73/239 decided to dissolve the Governing Council of the United Nations Human Settlements Programme and to replace it with a United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly). UN-Habitat Assembly is a universal body composed of the 193 member states of the United Nations and convenes every four years (A/RES/73/239).</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Current governing body of UN-Habitat (since 2019)
+- Formerly: "Governing Council of the United Nations Human Settlements Programme" (1978–2019)
+</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_of_the_High_Representative_for_the_Least_Developed_Countries,_Landlocked_Developing_Countries_and_Small_Island_Developing_States</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>https://www.un.org/ohrlls/news</t>
-        </is>
-      </c>
+          <t>https://unhabitat.org/governance/un-habitat-assembly</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
@@ -9251,171 +9235,124 @@
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="b">
-        <v>0</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Assemblies and Councils</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>https://open.unwomen.org/en/global-results/overview</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>https://www.un.org/ohrlls/sites/www.un.org.ohrlls/files/dpoa_roadmap_2024_draft.pdf</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>https://www.un.org/ohrlls/content/resources</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/un-ohrlls/</t>
-        </is>
-      </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>https://x.com/UNOHRLLS</t>
-        </is>
-      </c>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UN-Women</t>
+          <t>UN-OHRLLS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>United Nations Entity for Gender Equality and the Empowerment of Women</t>
+          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>United Nations Entity for Gender Equality and the Empowerment of Women (UN-Women)</t>
+          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States (UN-OHRLLS)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>UN Women is the global champion for gender equality, working to develop and uphold standards and create an environment in which every woman and girl can exercise her human rights and live up to her full potential. We are trusted partners for advocates and decision-makers from all walks of life, and a leader in the effort to achieve gender equality.</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/</t>
+          <t>https://www.un.org/ohrlls/</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UN_Women</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_of_the_High_Representative_for_the_Least_Developed_Countries,_Landlocked_Developing_Countries_and_Small_Island_Developing_States</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/news</t>
+          <t>https://www.un.org/ohrlls/news</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>https://data.unwomen.org/</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>New York City, USA</t>
-        </is>
-      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
         </is>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>https://www.unwomen.org/sites/default/files/2025-08/unw_org_chart_internal_20250806.pdf</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>https://www.unwomen.org/en/executive-board/strategic-plan-review/financial-resources</t>
-        </is>
-      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/sites/default/files/2025-10/un-women-strategic-plan-2026-2029-integrated-results-and-resources-framework-en.pdf</t>
+          <t>https://open.unwomen.org/en/global-results/overview</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/sites/default/files/2022-05/UN%20Women%20SP%20IRRF%202022-2025.pdf</t>
+          <t>https://www.un.org/ohrlls/sites/www.un.org.ohrlls/files/dpoa_roadmap_2024_draft.pdf</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/digital-library/annual-report</t>
+          <t>https://www.un.org/ohrlls/content/resources</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>https://data.unwomen.org/data-portal</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-women/</t>
+          <t>https://www.linkedin.com/company/un-ohrlls/</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>https://x.com/UN_Women</t>
+          <t>https://x.com/UNOHRLLS</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr"/>
@@ -9426,101 +9363,118 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UNAIDS</t>
+          <t>UN-Women</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Joint United Nations Programme on HIV/AIDS</t>
+          <t>United Nations Entity for Gender Equality and the Empowerment of Women</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Joint United Nations Programme on HIV/AIDS (UNAIDS)</t>
+          <t>United Nations Entity for Gender Equality and the Empowerment of Women (UN-Women)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UNAIDS brings together the efforts and resources of 10 UN system organizations to help prevent new HIV infections, care for people living with HIV and mitigate the impact of the epidemic.</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>UN Women is the global champion for gender equality, working to develop and uphold standards and create an environment in which every woman and girl can exercise her human rights and live up to her full potential. We are trusted partners for advocates and decision-makers from all walks of life, and a leader in the effort to achieve gender equality.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en</t>
+          <t>https://www.unwomen.org/</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Joint_United_Nations_Programme_on_HIV/AIDS</t>
+          <t>https://en.wikipedia.org/wiki/UN_Women</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en/news</t>
+          <t>https://www.unwomen.org/en/news</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://data.unwomen.org/</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Geneva, Switzerland</t>
+          <t>New York City, USA</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Other Bodies</t>
+          <t>Other Entities</t>
         </is>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>https://www.unwomen.org/sites/default/files/2025-08/unw_org_chart_internal_20250806.pdf</t>
+        </is>
+      </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en/topic/resources</t>
+          <t>https://www.unwomen.org/en/executive-board/strategic-plan-review/financial-resources</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unwomen.org/sites/default/files/2025-10/un-women-strategic-plan-2026-2029-integrated-results-and-resources-framework-en.pdf</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/sites/default/files/media_asset/global-AIDS-strategy-2021-2026_en.pdf</t>
+          <t>https://www.unwomen.org/sites/default/files/2022-05/UN%20Women%20SP%20IRRF%202022-2025.pdf</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en/topics/resources/publications</t>
+          <t>https://www.unwomen.org/en/digital-library/annual-report</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>https://open.unaids.org/</t>
+          <t>https://data.unwomen.org/data-portal</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unaids/</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/un-women/</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>https://x.com/UN_Women</t>
+        </is>
+      </c>
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>1</v>
@@ -9529,39 +9483,39 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>UNAMA</t>
+          <t>UNAIDS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>United Nations Assistance Mission in Afghanistan</t>
+          <t>Joint United Nations Programme on HIV/AIDS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>United Nations Assistance Mission in Afghanistan (UNAMA)</t>
+          <t>Joint United Nations Programme on HIV/AIDS (UNAIDS)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UNAMA’s mission is to support the people and institutions of Afghanistan in achieving peace and stability, in line with the rights and obligations enshrined in the Afghan constitution.</t>
+          <t>UNAIDS brings together the efforts and resources of 10 UN system organizations to help prevent new HIV infections, care for people living with HIV and mitigate the impact of the epidemic.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/</t>
+          <t>https://www.unaids.org/en</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Assistance_Mission_in_Afghanistan</t>
+          <t>https://en.wikipedia.org/wiki/Joint_United_Nations_Programme_on_HIV/AIDS</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/news</t>
+          <t>https://www.unaids.org/en/news</t>
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
@@ -9570,15 +9524,19 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland</t>
+        </is>
+      </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Other Bodies</t>
         </is>
       </c>
       <c r="S102" t="inlineStr"/>
@@ -9589,7 +9547,11 @@
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>https://www.unaids.org/en/topic/resources</t>
+        </is>
+      </c>
       <c r="Z102" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -9597,22 +9559,22 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/sites/default/files/unsf_afghanistan_formatted_20230629.pdf</t>
+          <t>https://www.unaids.org/sites/default/files/media_asset/global-AIDS-strategy-2021-2026_en.pdf</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/secretary-general-reports</t>
+          <t>https://www.unaids.org/en/topics/resources/publications</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://open.unaids.org/</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/unaids/</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr"/>
@@ -9624,39 +9586,39 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UNAOC</t>
+          <t>UNAMA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>United Nations Alliance of Civilizations</t>
+          <t>United Nations Assistance Mission in Afghanistan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>United Nations Alliance of Civilizations (UNAOC)</t>
+          <t>United Nations Assistance Mission in Afghanistan (UNAMA)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UNAOC aims to bridge divides, and promote harmony among the nations, all with a view toward preventing conflict and promoting social cohesion.</t>
+          <t>UNAMA’s mission is to support the people and institutions of Afghanistan in achieving peace and stability, in line with the rights and obligations enshrined in the Afghan constitution.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.unaoc.org/</t>
+          <t>https://unama.unmissions.org/</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Alliance_of_Civilizations</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Assistance_Mission_in_Afghanistan</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://www.unaoc.org/category/news/</t>
+          <t>https://unama.unmissions.org/news</t>
         </is>
       </c>
       <c r="J103" t="inlineStr"/>
@@ -9668,10 +9630,14 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr"/>
+          <t>Security Council</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Special Political Missions and Other Political Presences</t>
+        </is>
+      </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="b">
         <v>0</v>
@@ -9688,12 +9654,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>https://www.unaoc.org/wp-content/uploads/UNAOC-Action-Plan-POA-2024-2026-250203_web.pdf</t>
+          <t>https://unama.unmissions.org/sites/default/files/unsf_afghanistan_formatted_20230629.pdf</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>https://www.unaoc.org/resource-type/unaoc-annual-reports/</t>
+          <t>https://unama.unmissions.org/secretary-general-reports</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -9703,41 +9669,53 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-alliance-of-civilizations/</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UNCCD</t>
+          <t>UNAOC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>United Nations Convention to Combat Desertification</t>
+          <t>United Nations Alliance of Civilizations</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>United Nations Convention to Combat Desertification (UNCCD)</t>
+          <t>United Nations Alliance of Civilizations (UNAOC)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>UNAOC aims to bridge divides, and promote harmony among the nations, all with a view toward preventing conflict and promoting social cohesion.</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.unccd.int/</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+          <t>https://www.unaoc.org/</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Alliance_of_Civilizations</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://www.unaoc.org/category/news/</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -9752,21 +9730,39 @@
       </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
+      <c r="T104" t="b">
+        <v>0</v>
+      </c>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>https://www.unccd.int/convention/governance/strategic-framework-2018-2030</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr"/>
-      <c r="AC104" t="inlineStr"/>
-      <c r="AD104" t="inlineStr"/>
+          <t>https://www.unaoc.org/wp-content/uploads/UNAOC-Action-Plan-POA-2024-2026-250203_web.pdf</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>https://www.unaoc.org/resource-type/unaoc-annual-reports/</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/united-nations-alliance-of-civilizations/</t>
+        </is>
+      </c>
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
@@ -9776,30 +9772,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UNCDF</t>
+          <t>UNCCD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>United Nations Capital Development Fund</t>
+          <t>United Nations Convention to Combat Desertification</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>United Nations Capital Development Fund (UNCDF)</t>
+          <t>United Nations Convention to Combat Desertification (UNCCD)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>The United Nations Capital Development Fund's mission is to contribute to job creation, sustained economic growth and equitable prosperity in almost 80 developing countries and nearly all LDCs.
-We do so by crowding in capital through the deployment of risk-absorbing financial instruments, mechanisms and structuring advisory. In partnership with UN entities and development partners, UNCDF operates with speed and agility to deliver scalable, blended finance solutions to drive systemic change and pave the way for commercial finance and scale up by development finance institutions and multilateral development banks.</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.uncdf.org/</t>
+          <t>https://www.unccd.int/</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -9813,18 +9804,12 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
-      <c r="T105" t="b">
-        <v>0</v>
-      </c>
+      <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
@@ -9833,7 +9818,7 @@
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>https://www.uncdf.org/article/3208/making-finance-work-for-inclusion-uncdf-presents-new-four-year-strategic-framework-to-its-board</t>
+          <t>https://www.unccd.int/convention/governance/strategic-framework-2018-2030</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -9842,31 +9827,36 @@
       <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UNCITRAL</t>
+          <t>UNCDF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>United Nations Commission on International Trade Law</t>
+          <t>United Nations Capital Development Fund</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>United Nations Commission on International Trade Law (UNCITRAL)</t>
+          <t>United Nations Capital Development Fund (UNCDF)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>The United Nations Capital Development Fund's mission is to contribute to job creation, sustained economic growth and equitable prosperity in almost 80 developing countries and nearly all LDCs.
+We do so by crowding in capital through the deployment of risk-absorbing financial instruments, mechanisms and structuring advisory. In partnership with UN entities and development partners, UNCDF operates with speed and agility to deliver scalable, blended finance solutions to drive systemic change and pave the way for commercial finance and scale up by development finance institutions and multilateral development banks.</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://uncitral.un.org/</t>
+          <t>https://www.uncdf.org/</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -9885,22 +9875,24 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr"/>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="b">
+        <v>0</v>
+      </c>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>https://www.uncdf.org/article/3208/making-finance-work-for-inclusion-uncdf-presents-new-four-year-strategic-framework-to-its-board</t>
+        </is>
+      </c>
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr"/>
@@ -9913,47 +9905,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UNCTAD</t>
+          <t>UNCITRAL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>United Nations Conference on Trade and Development</t>
+          <t>United Nations Commission on International Trade Law</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>United Nations Conference on Trade and Development (UNCTAD)</t>
+          <t>United Nations Commission on International Trade Law (UNCITRAL)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>UNCTAD supports developing countries to access the benefits of a globalized economy more fairly and effectively and helps equip them to deal with the potential drawbacks of greater economic integration.</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- The secretariat of this entity is part of the United Nations Secretariat.
-</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://unctad.org/</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Conference_on_Trade_and_Development</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>https://unctad.org/news</t>
-        </is>
-      </c>
+          <t>https://uncitral.un.org/</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
@@ -9968,43 +9942,25 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Other Entities</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="b">
-        <v>1</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>https://unctad.org/dmfas/our_Strategic_Plan</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>https://unctad.org/publications-search?Operator=and&amp;keys=annual</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unctad/</t>
-        </is>
-      </c>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
       <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
@@ -10014,29 +9970,47 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UNDC</t>
+          <t>UNCTAD</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Disarmament Commission</t>
+          <t>United Nations Conference on Trade and Development</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Disarmament Commission (UNDC)</t>
+          <t>United Nations Conference on Trade and Development (UNCTAD)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>UNCTAD supports developing countries to access the benefits of a globalized economy more fairly and effectively and helps equip them to deal with the potential drawbacks of greater economic integration.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- The secretariat of this entity is part of the United Nations Secretariat.
+</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://disarmament.unoda.org/en/united-nations-disarmament-commission</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+          <t>https://unctad.org/</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Conference_on_Trade_and_Development</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://unctad.org/news</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
@@ -10051,25 +10025,43 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr"/>
+          <t>Other Entities</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="b">
+        <v>1</v>
+      </c>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
-      <c r="AB108" t="inlineStr"/>
-      <c r="AC108" t="inlineStr"/>
-      <c r="AD108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>https://unctad.org/dmfas/our_Strategic_Plan</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>https://unctad.org/publications-search?Operator=and&amp;keys=annual</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unctad/</t>
+        </is>
+      </c>
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
@@ -10079,17 +10071,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UNDEF</t>
+          <t>UNDC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>United Nations Democracy Fund</t>
+          <t>Disarmament Commission</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>United Nations Democracy Fund (UNDEF)</t>
+          <t>Disarmament Commission (UNDC)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -10097,7 +10089,7 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.un.org/democracyfund/</t>
+          <t>https://disarmament.unoda.org/en/united-nations-disarmament-commission</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -10111,11 +10103,19 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
@@ -10130,47 +10130,35 @@
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UNDOF</t>
+          <t>UNDEF</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force</t>
+          <t>United Nations Democracy Fund</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force (UNDOF)</t>
+          <t>United Nations Democracy Fund (UNDEF)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>The UNDOF assists in maintaining the ceasefire between Israel and Syria, supervising the disengagement of Israeli and Syrian forces; as well as the areas of separation and limitation, as provided in the May 1974 Agreement on Disengagement.</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://undof.unmissions.org/</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Disengagement_Observer_Force</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>https://undof.unmissions.org/news</t>
-        </is>
-      </c>
+          <t>https://www.un.org/democracyfund/</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
@@ -10180,172 +10168,119 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>Peacekeeping Operations</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
-      <c r="T110" t="b">
-        <v>0</v>
-      </c>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>https://undof.unmissions.org/reports-statements</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
       <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>UNDOF</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>United Nations Development Programme</t>
+          <t>United Nations Disengagement Observer Force</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>United Nations Development Programme (UNDP)</t>
+          <t>United Nations Disengagement Observer Force (UNDOF)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>The UNDP helps build inclusive, sustainable and resilient societies and provides expert advice, training and financial support. Special attention is paid to the needs of the Least Developed Countries and countries emerging from conflict.</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
-</t>
-        </is>
-      </c>
+          <t>The UNDOF assists in maintaining the ceasefire between Israel and Syria, supervising the disengagement of Israeli and Syrian forces; as well as the areas of separation and limitation, as provided in the May 1974 Agreement on Disengagement.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.undp.org/</t>
+          <t>https://undof.unmissions.org/</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Programme</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Disengagement_Observer_Force</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.undp.org/news</t>
+          <t>https://undof.unmissions.org/news</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="b">
-        <v>1</v>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>https://jobs.undp.org/</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>New York City, USA</t>
-        </is>
-      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
+          <t>Peacekeeping Operations</t>
         </is>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/organizational-chart</t>
-        </is>
-      </c>
+      <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>https://rolhr.undp.org/annualreport/2023/results-framework.html</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>https://strategicplan.undp.org/</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>https://annualreport.undp.org/</t>
+          <t>https://undof.unmissions.org/reports-statements</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>https://open.undp.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-development-programme/</t>
-        </is>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>https://x.com/UNDP</t>
-        </is>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/undp/</t>
-        </is>
-      </c>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>1</v>
       </c>
@@ -10353,36 +10288,63 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UNDP UNFPA UNOPS EB</t>
+          <t>UNDP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Executive Board of UNDP, UNFPA and UNOPS</t>
+          <t>United Nations Development Programme</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Executive Board of UNDP, UNFPA and UNOPS (UNDP UNFPA UNOPS EB)</t>
+          <t>United Nations Development Programme (UNDP)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>The UNDP helps build inclusive, sustainable and resilient societies and provides expert advice, training and financial support. Special attention is paid to the needs of the Least Developed Countries and countries emerging from conflict.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
+</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/executive-board</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+          <t>https://www.undp.org/</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Programme</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/news</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="N112" t="b">
+        <v>1</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>https://jobs.undp.org/</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>New York City, USA</t>
+        </is>
+      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -10390,69 +10352,87 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr"/>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="b">
+        <v>1</v>
+      </c>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/organizational-chart</t>
+        </is>
+      </c>
       <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr"/>
-      <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="inlineStr"/>
-      <c r="AE112" t="inlineStr"/>
-      <c r="AF112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>https://rolhr.undp.org/annualreport/2023/results-framework.html</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>https://strategicplan.undp.org/</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>https://annualreport.undp.org/</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>https://open.undp.org/</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/united-nations-development-programme/</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>https://x.com/UNDP</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/undp/</t>
+        </is>
+      </c>
       <c r="AG112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UNDRR</t>
+          <t>UNDP UNFPA UNOPS EB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>United Nations Office for Disaster Risk Reduction</t>
+          <t>Executive Board of UNDP, UNFPA and UNOPS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>United Nations Office for Disaster Risk Reduction (UNDRR)</t>
+          <t>Executive Board of UNDP, UNFPA and UNOPS (UNDP UNFPA UNOPS EB)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>UNDRR brings governments, partners, and communities together to reduce disaster risk and losses and to ensure a safer, sustainable future.</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.undrr.org/</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Disaster_Risk_Reduction</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>https://www.undrr.org/news</t>
-        </is>
-      </c>
+          <t>https://www.unfpa.org/executive-board</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
@@ -10462,85 +10442,74 @@
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="b">
-        <v>0</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>https://www.undrr.org/media/49267/download</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>https://www.undrr.org/publications?text=Annual%20Report</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-office-for-disaster-risk-reduction-undrr/</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>https://x.com/UNDRR</t>
-        </is>
-      </c>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UNEA</t>
+          <t>UNDRR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>United Nations Environment Assembly</t>
+          <t>United Nations Office for Disaster Risk Reduction</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>United Nations Environment Assembly (UNEA)</t>
+          <t>United Nations Office for Disaster Risk Reduction (UNDRR)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Also referred to as "United Nations Environment Assembly of the United Nations Environment Programme (UNEP)"
-</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>UNDRR brings governments, partners, and communities together to reduce disaster risk and losses and to ensure a safer, sustainable future.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.unep.org/environmentassembly/</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+          <t>https://www.undrr.org/</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Disaster_Risk_Reduction</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://www.undrr.org/news</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
@@ -10550,91 +10519,92 @@
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>Assemblies and Councils</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr"/>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="b">
+        <v>0</v>
+      </c>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
-      <c r="AB114" t="inlineStr"/>
-      <c r="AC114" t="inlineStr"/>
-      <c r="AD114" t="inlineStr"/>
-      <c r="AE114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>https://www.undrr.org/media/49267/download</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>https://www.undrr.org/publications?text=Annual%20Report</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/united-nations-office-for-disaster-risk-reduction-undrr/</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>https://x.com/UNDRR</t>
+        </is>
+      </c>
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UNEP</t>
+          <t>UNEA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>United Nations Environment Programme</t>
+          <t>United Nations Environment Assembly</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>United Nations Environment Programme (UNEP)</t>
+          <t>United Nations Environment Assembly (UNEA)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>The global authority for the environment with programmes focusing on climate, nature, pollution, sustainable development and more.</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
-- The secretariat of this entity is part of the United Nations Secretariat.
+          <t xml:space="preserve">- Also referred to as "United Nations Environment Assembly of the United Nations Environment Programme (UNEP)"
 </t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.unep.org/</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Environment_Programme</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>https://www.unep.org/news</t>
-        </is>
-      </c>
+          <t>https://www.unep.org/environmentassembly/</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Nairobi, Kenya</t>
-        </is>
-      </c>
+      <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -10642,99 +10612,73 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="b">
-        <v>1</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Assemblies and Councils</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>https://www.unep.org/resources/programme-work-and-budget</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>https://wedocs.unep.org/bitstream/handle/20.500.11822/42683/medium_term_strategy_2022.pdf?sequence=1&amp;isAllowed=y</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>https://www.unep.org/annualreport/2021/index.php</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>https://open.unep.org/</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/un-environment-programme/</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>https://x.com/UNEP</t>
-        </is>
-      </c>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>UNEP</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>United Nations Educational, Scientific and Cultural Organization</t>
+          <t>United Nations Environment Programme</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>United Nations Educational, Scientific and Cultural Organization (UNESCO)</t>
+          <t>United Nations Environment Programme (UNEP)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UNESCO contributes to peace and security by promoting collaboration among nations through education, science and culture.</t>
+          <t>The global authority for the environment with programmes focusing on climate, nature, pollution, sustainable development and more.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
+- The secretariat of this entity is part of the United Nations Secretariat.
 </t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/</t>
+          <t>https://www.unep.org/</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UNESCO</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Environment_Programme</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/news</t>
+          <t>https://www.unep.org/news</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -10745,15 +10689,19 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="b">
         <v>1</v>
@@ -10761,14 +10709,10 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>https://unesdoc.unesco.org/archives/organization-charts</t>
-        </is>
-      </c>
+      <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/budget-strategy</t>
+          <t>https://www.unep.org/resources/programme-work-and-budget</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
@@ -10778,27 +10722,27 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>https://unesdoc.unesco.org/ark:/48223/pf0000378083_eng</t>
+          <t>https://wedocs.unep.org/bitstream/handle/20.500.11822/42683/medium_term_strategy_2022.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/budget-strategy</t>
+          <t>https://www.unep.org/annualreport/2021/index.php</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>https://core.unesco.org/</t>
+          <t>https://open.unep.org/</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unesco/</t>
+          <t>https://www.linkedin.com/company/un-environment-programme/</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>https://x.com/UNESCO</t>
+          <t>https://x.com/UNEP</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr"/>
@@ -10809,59 +10753,111 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UNFF</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>United Nations Forum on Forests</t>
+          <t>United Nations Educational, Scientific and Cultural Organization</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>United Nations Forum on Forests (UNFF)</t>
+          <t>United Nations Educational, Scientific and Cultural Organization (UNESCO)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>UNESCO contributes to peace and security by promoting collaboration among nations through education, science and culture.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.un.org/esa/forests/</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+          <t>https://www.unesco.org/</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/UNESCO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://www.unesco.org/en/news</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>Functional Commissions</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
+      <c r="T117" t="b">
+        <v>1</v>
+      </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
-      <c r="AB117" t="inlineStr"/>
-      <c r="AC117" t="inlineStr"/>
-      <c r="AD117" t="inlineStr"/>
-      <c r="AE117" t="inlineStr"/>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>https://unesdoc.unesco.org/archives/organization-charts</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>https://www.unesco.org/en/budget-strategy</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>https://unesdoc.unesco.org/ark:/48223/pf0000378083_eng</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>https://www.unesco.org/en/budget-strategy</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>https://core.unesco.org/</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unesco/</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>https://x.com/UNESCO</t>
+        </is>
+      </c>
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>1</v>
@@ -10870,41 +10866,29 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UNFICYP</t>
+          <t>UNFF</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>United Nations Peacekeeping Force in Cyprus</t>
+          <t>United Nations Forum on Forests</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>United Nations Peacekeeping Force in Cyprus (UNFICYP)</t>
+          <t>United Nations Forum on Forests (UNFF)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>UNFICYP has remained on the island to supervise ceasefire lines, maintain a buffer zone, undertake humanitarian activities and support the good offices mission of the Secretary-General.</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://unficyp.unmissions.org/</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Peacekeeping_Force_in_Cyprus</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>https://unficyp.unmissions.org/news</t>
-        </is>
-      </c>
+          <t>https://www.un.org/esa/forests/</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
@@ -10914,53 +10898,27 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Peacekeeping Operations</t>
+          <t>Functional Commissions</t>
         </is>
       </c>
       <c r="S118" t="inlineStr"/>
-      <c r="T118" t="b">
-        <v>0</v>
-      </c>
+      <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>https://www.securitycouncilreport.org/un-documents/cyprus/</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>https://x.com/UN_CYPRUS</t>
-        </is>
-      </c>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>1</v>
@@ -10969,110 +10927,95 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UNFPA</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>United Nations Population Fund</t>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>United Nations Population Fund (UNFPA)</t>
+          <t>United Nations Peacekeeping Force in Cyprus (UNFICYP)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UNFPA is the United Nations sexual and reproductive health agency. Our mission is to deliver a world where every pregnancy is wanted, every childbirth is safe and every young person's potential is fulfilled.</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+          <t>UNFICYP has remained on the island to supervise ceasefire lines, maintain a buffer zone, undertake humanitarian activities and support the good offices mission of the Secretary-General.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/</t>
+          <t>https://unficyp.unmissions.org/</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Population_Fund</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Peacekeeping_Force_in_Cyprus</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/news</t>
+          <t>https://unficyp.unmissions.org/news</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="b">
-        <v>1</v>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>New York City, USA</t>
-        </is>
-      </c>
+      <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
+          <t>Peacekeeping Operations</t>
         </is>
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>https://www.unfpa.org/finance-and-budget-policies</t>
-        </is>
-      </c>
+      <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/results-based-management-unfpa</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/sites/default/files/board-documents/DP.FPA_.2025.9%20-%20Strategic%20Plan%202026-2029%20-%20Annex%201%20-%20IRRF%20-%20FINAL%20-%2018Jul25.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/annual-report</t>
+          <t>https://www.securitycouncilreport.org/un-documents/cyprus/</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/data/transparency-portal</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-population-fund-unfpa/</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>https://x.com/UNFPA</t>
+          <t>https://x.com/UN_CYPRUS</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr"/>
@@ -11083,153 +11026,176 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UNGC</t>
+          <t>UNFPA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>United Nations Global Compact</t>
+          <t>United Nations Population Fund</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>United Nations Global Compact (UNGC)</t>
+          <t>United Nations Population Fund (UNFPA)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>The United Nations Global Compact is a voluntary initiative based on CEO commitments to implement universal sustainability principles and to undertake partnerships in support of UN goals.</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
+          <t>UNFPA is the United Nations sexual and reproductive health agency. Our mission is to deliver a world where every pregnancy is wanted, every childbirth is safe and every young person's potential is fulfilled.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://unglobalcompact.org/</t>
+          <t>https://www.unfpa.org/</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Global_Compact</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Population_Fund</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://unglobalcompact.org/news</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
-        </is>
-      </c>
+          <t>https://www.unfpa.org/news</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
-        </is>
-      </c>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" t="b">
+        <v>1</v>
+      </c>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>New York City, USA</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr"/>
-      <c r="Y120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>https://www.unfpa.org/finance-and-budget-policies</t>
+        </is>
+      </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unfpa.org/results-based-management-unfpa</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>https://unglobalcompact.org/what-is-gc/strategy</t>
+          <t>https://www.unfpa.org/sites/default/files/board-documents/DP.FPA_.2025.9%20-%20Strategic%20Plan%202026-2029%20-%20Annex%201%20-%20IRRF%20-%20FINAL%20-%2018Jul25.pdf</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>https://unglobalcompact.org/library</t>
+          <t>https://www.unfpa.org/annual-report</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.unfpa.org/data/transparency-portal</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-global-compact/</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/united-nations-population-fund-unfpa/</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>https://x.com/UNFPA</t>
+        </is>
+      </c>
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UNGEGN</t>
+          <t>UNGC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>United Nations Group of Experts on Geographical Names</t>
+          <t>United Nations Global Compact</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>United Nations Group of Experts on Geographical Names (UNGEGN)</t>
+          <t>United Nations Global Compact (UNGC)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>The United Nations Global Compact is a voluntary initiative based on CEO commitments to implement universal sustainability principles and to undertake partnerships in support of UN goals.</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/unsd/ungegn</t>
+          <t>https://unglobalcompact.org/</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Group_of_Experts_on_Geographical_Names</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Global_Compact</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
+          <t>https://unglobalcompact.org/news</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>Other Bodies</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="b">
         <v>0</v>
@@ -11246,12 +11212,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/unsd/ungegn/sessions/2nd_session_2021/documents/UNGEGN_Strategic_Plan_final_5May2021.pdf</t>
+          <t>https://unglobalcompact.org/what-is-gc/strategy</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/unsd/ungegn/sessions/</t>
+          <t>https://unglobalcompact.org/library</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -11261,29 +11227,29 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/united-nations-global-compact/</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UNGGIM</t>
+          <t>UNGEGN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Committee of Experts on Global Geospatial Information Management</t>
+          <t>United Nations Group of Experts on Geographical Names</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Committee of Experts on Global Geospatial Information Management (UNGGIM)</t>
+          <t>United Nations Group of Experts on Geographical Names (UNGEGN)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -11291,12 +11257,12 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://ggim.un.org/</t>
+          <t>https://unstats.un.org/unsd/ungegn</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Committee_of_Experts_on_Global_Geospatial_Information_Management</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Group_of_Experts_on_Geographical_Names</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11337,12 +11303,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unstats.un.org/unsd/ungegn/sessions/2nd_session_2021/documents/UNGEGN_Strategic_Plan_final_5May2021.pdf</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>https://ggim.un.org/meetings/Sessions/</t>
+          <t>https://unstats.un.org/unsd/ungegn/sessions/</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -11364,44 +11330,35 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UNHCR</t>
+          <t>UNGGIM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Office of the United Nations High Commissioner for Refugees</t>
+          <t>Committee of Experts on Global Geospatial Information Management</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Office of the United Nations High Commissioner for Refugees (UNHCR)</t>
+          <t>Committee of Experts on Global Geospatial Information Management (UNGGIM)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>The work of the Office of the UNHCR is humanitarian and non-political. Its principal functions are to provide international protection to refugees and other persons of concern, and to seek durable solutions for them.</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/</t>
+          <t>https://ggim.un.org/</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_High_Commissioner_for_Refugees</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Committee_of_Experts_on_Global_Geospatial_Information_Management</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -11410,57 +11367,49 @@
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
+      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Other Bodies</t>
         </is>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr"/>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>https://www.unhcr.org/us/budget-and-expenditure</t>
-        </is>
-      </c>
+      <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/media/unhcrs-results-areas</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022-2026.pdfhttps://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022--2026.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/cgi-bin/texis/vtx/search?page=&amp;comid=3b4f07fd4&amp;cid=49aea93a20&amp;scid=49aea93a16&amp;keywords=UNHCR%20Annual%20Reports%20General%20Assembly</t>
+          <t>https://ggim.un.org/meetings/Sessions/</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>https://reporting.unhcr.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unhcr/</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr"/>
@@ -11472,23 +11421,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNICEF</t>
+          <t>UNHCR</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>United Nations Children's Fund</t>
+          <t>Office of the United Nations High Commissioner for Refugees</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>United Nations Children's Fund (UNICEF)</t>
+          <t>Office of the United Nations High Commissioner for Refugees (UNHCR)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UNICEF works in the world’s toughest places to reach the most disadvantaged children and to protect the rights of every child, everywhere.</t>
+          <t>The work of the Office of the UNHCR is humanitarian and non-political. Its principal functions are to provide international protection to refugees and other persons of concern, and to seek durable solutions for them.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -11499,30 +11448,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/</t>
+          <t>https://www.unhcr.org/</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UNICEF</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_High_Commissioner_for_Refugees</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/press-releases</t>
+          <t>https://www.unhcr.org/news</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="b">
-        <v>1</v>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>New York City, USA</t>
+          <t>Geneva, Switzerland</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -11532,7 +11479,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
+          <t>Other Entities</t>
         </is>
       </c>
       <c r="S124" t="inlineStr"/>
@@ -11542,46 +11489,38 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>https://www.unicef.org/executiveboard/media/21691/file/Integrated-Budget-MTR-Annexes.pdf</t>
-        </is>
-      </c>
+      <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/documents/unicef-integrated-budget-2026-2029-srs-2025</t>
+          <t>https://www.unhcr.org/us/budget-and-expenditure</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/media/32061/file/2025-29-Add1-SP-2026-2029-IRRF-EN-2025-07-21.pdf</t>
+          <t>https://www.unhcr.org/media/unhcrs-results-areas</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/documents/unicef-strategic-plan-2026-2029-draft-review-as-2025</t>
+          <t>https://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022-2026.pdfhttps://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022--2026.pdf</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/topics/annual-report</t>
+          <t>https://www.unhcr.org/cgi-bin/texis/vtx/search?page=&amp;comid=3b4f07fd4&amp;cid=49aea93a20&amp;scid=49aea93a16&amp;keywords=UNHCR%20Annual%20Reports%20General%20Assembly</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>https://open.unicef.org/</t>
+          <t>https://reporting.unhcr.org/</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unicef/</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>https://x.com/UNICEF</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/unhcr/</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>1</v>
@@ -11590,36 +11529,59 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UNICEF EB</t>
+          <t>UNICEF</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Executive Board of the United Nations Children's Fund</t>
+          <t>United Nations Children's Fund</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Executive Board of the United Nations Children's Fund (UNICEF EB)</t>
+          <t>United Nations Children's Fund (UNICEF)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>UNICEF works in the world’s toughest places to reach the most disadvantaged children and to protect the rights of every child, everywhere.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+          <t>https://www.unicef.org/</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/UNICEF</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/press-releases</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" t="b">
+        <v>1</v>
+      </c>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>New York City, USA</t>
+        </is>
+      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -11627,45 +11589,75 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr"/>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="b">
+        <v>1</v>
+      </c>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
-      <c r="AB125" t="inlineStr"/>
-      <c r="AC125" t="inlineStr"/>
-      <c r="AD125" t="inlineStr"/>
-      <c r="AE125" t="inlineStr"/>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/executiveboard/media/21691/file/Integrated-Budget-MTR-Annexes.pdf</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/executiveboard/documents/unicef-integrated-budget-2026-2029-srs-2025</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/executiveboard/media/32061/file/2025-29-Add1-SP-2026-2029-IRRF-EN-2025-07-21.pdf</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/executiveboard/documents/unicef-strategic-plan-2026-2029-draft-review-as-2025</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/topics/annual-report</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>https://open.unicef.org/</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unicef/</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>https://x.com/UNICEF</t>
+        </is>
+      </c>
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UNICRI</t>
+          <t>UNICEF EB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>United Nations Interregional Crime and Justice Research Institute</t>
+          <t>Executive Board of the United Nations Children's Fund</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>United Nations Interregional Crime and Justice Research Institute (UNICRI)</t>
+          <t>Executive Board of the United Nations Children's Fund (UNICEF EB)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -11673,7 +11665,7 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://unicri.org/</t>
+          <t>https://www.unicef.org/executiveboard/</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -11682,97 +11674,79 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="b">
-        <v>1</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Research and Training</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="b">
-        <v>0</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>https://unicri.org/sites/default/files/2020-07/UNICRI_AI_CentreStrategicPlan.pdf</t>
-        </is>
-      </c>
+      <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr"/>
       <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>UNIDIR</t>
+          <t>UNICRI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>United Nations Institute for Disarmament Research</t>
+          <t>United Nations Interregional Crime and Justice Research Institute</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>United Nations Institute for Disarmament Research (UNIDIR)</t>
+          <t>United Nations Interregional Crime and Justice Research Institute (UNICRI)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>The UNIDIR is an autonomous body of the UN, established by the General Assembly to carry out independent research on disarmament and related international security issues.</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.unidir.org/</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Disarmament_Research</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>https://www.unidir.org/news</t>
-        </is>
-      </c>
+          <t>https://unicri.org/</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="b">
+        <v>1</v>
+      </c>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
+      <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11788,41 +11762,17 @@
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>https://unidir.org/who-we-are/funding-and-support/</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>https://unidir.org/report-of-the-director</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unidir</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>https://x.com/UNIDIR</t>
-        </is>
-      </c>
+          <t>https://unicri.org/sites/default/files/2020-07/UNICRI_AI_CentreStrategicPlan.pdf</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr"/>
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>1</v>
@@ -11831,45 +11781,39 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>UNIDO</t>
+          <t>UNIDIR</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>United Nations Industrial Development Organization</t>
+          <t>United Nations Institute for Disarmament Research</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>United Nations Industrial Development Organization (UNIDO)</t>
+          <t>United Nations Institute for Disarmament Research (UNIDIR)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UNIDO's objective is the promotion and acceleration of industrial development in developing countries and countries with economies in transition and the promotion of international industrial cooperation.</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+          <t>The UNIDIR is an autonomous body of the UN, established by the General Assembly to carry out independent research on disarmament and related international security issues.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.unido.org/</t>
+          <t>https://www.unidir.org/</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Industrial_Development_Organization</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Disarmament_Research</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://www.unido.org/news</t>
+          <t>https://www.unidir.org/news</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -11880,30 +11824,30 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Vienna, Austria</t>
+          <t>Geneva, Switzerland</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Research and Training</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>https://www.unido.org/sites/default/files/unido-publications/2025-04/ANNUAL%20REPORT%202024.pdf</t>
-        </is>
-      </c>
+      <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>https://www.unido.org/resources/policymaking-organs/programme-and-budget-committee/reports-programme-and-budget-committee</t>
+          <t>https://unidir.org/who-we-are/funding-and-support/</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
@@ -11913,27 +11857,27 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>https://www.unido.org/publications/key-policy-documents</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>https://www.unido.org/annualreport</t>
+          <t>https://unidir.org/report-of-the-director</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>https://open.unido.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unido/</t>
+          <t>https://www.linkedin.com/company/unidir</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>https://x.com/UNIDO</t>
+          <t>https://x.com/UNIDIR</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr"/>
@@ -11944,69 +11888,81 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>UNIDO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
+          <t>United Nations Industrial Development Organization</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon (UNIFIL)</t>
+          <t>United Nations Industrial Development Organization (UNIDO)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UNIFIL was created to confirm Israeli withdrawal from Lebanon, restore international peace and security and assist the Lebanese Government in restoring its effective authority in the area.</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
+          <t>UNIDO's objective is the promotion and acceleration of industrial development in developing countries and countries with economies in transition and the promotion of international industrial cooperation.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://unifil.unmissions.org/</t>
+          <t>https://www.unido.org/</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Force_in_Lebanon</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Industrial_Development_Organization</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://unifil.unmissions.org/news</t>
+          <t>https://www.unido.org/news</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="b">
-        <v>1</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Vienna, Austria</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>Peacekeeping Operations</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr"/>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>https://www.unido.org/sites/default/files/unido-publications/2025-04/ANNUAL%20REPORT%202024.pdf</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>https://www.unido.org/resources/policymaking-organs/programme-and-budget-committee/reports-programme-and-budget-committee</t>
+        </is>
+      </c>
       <c r="Z129" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -12014,25 +11970,29 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unido.org/publications/key-policy-documents</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>https://unifil.unmissions.org/unifil-documents</t>
+          <t>https://www.unido.org/annualreport</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://open.unido.org/</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/unido/</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>https://x.com/UNIDO</t>
+        </is>
+      </c>
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>1</v>
@@ -12041,46 +12001,48 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UNISFA</t>
+          <t>UNIFIL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei</t>
+          <t>United Nations Interim Force in Lebanon</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei (UNISFA)</t>
+          <t>United Nations Interim Force in Lebanon (UNIFIL)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>UNISFA enhances the peace and stability, through operations to ensure that the Abyei Area is weapons-free and reducing intercommunal tensions by employing conflict prevention measures and promoting dialogue.</t>
+          <t>UNIFIL was created to confirm Israeli withdrawal from Lebanon, restore international peace and security and assist the Lebanese Government in restoring its effective authority in the area.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://unisfa.unmissions.org/</t>
+          <t>https://unifil.unmissions.org/</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Security_Force_for_Abyei</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Force_in_Lebanon</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://unisfa.unmissions.org/en/news</t>
+          <t>https://unifil.unmissions.org/news</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="b">
+        <v>1</v>
+      </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
@@ -12114,7 +12076,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>https://digitallibrary.un.org/search?ln=en&amp;cc=Reports&amp;p=%22UN+Interim+Security+Force+for+Abyei%22+OR+UNISFA&amp;f=&amp;action_search=Search&amp;rm=&amp;ln=en&amp;sf=year&amp;so=d&amp;rg=50&amp;c=Reports&amp;c=&amp;of=hb&amp;fti=0&amp;fti=0</t>
+          <t>https://unifil.unmissions.org/unifil-documents</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -12127,11 +12089,7 @@
           <t>Not found.</t>
         </is>
       </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>https://x.com/UNISFA_1</t>
-        </is>
-      </c>
+      <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>1</v>
@@ -12140,62 +12098,56 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UNITAR</t>
+          <t>UNISFA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>United Nations Institute for Training and Research</t>
+          <t>United Nations Interim Security Force for Abyei</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>United Nations Institute for Training and Research (UNITAR)</t>
+          <t>United Nations Interim Security Force for Abyei (UNISFA)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>The United Nations Institute for Training and Research (UNITAR) provides innovative learning solutions to individuals, organizations and institutions to enhance global decision-making and support country-level action for shaping a better future.</t>
+          <t>UNISFA enhances the peace and stability, through operations to ensure that the Abyei Area is weapons-free and reducing intercommunal tensions by employing conflict prevention measures and promoting dialogue.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://unitar.org/</t>
+          <t>https://unisfa.unmissions.org/</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Training_and_Research</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Security_Force_for_Abyei</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://unitar.org/news-events</t>
+          <t>https://unisfa.unmissions.org/en/news</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="b">
-        <v>1</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Research and Training</t>
+          <t>Peacekeeping Operations</t>
         </is>
       </c>
       <c r="S131" t="inlineStr"/>
@@ -12206,24 +12158,20 @@
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>https://unitar.org/about/programme-budget</t>
-        </is>
-      </c>
+      <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>https://unitar.org/results-evidence-learning/results-reports-and-other-reports</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>https://unitar.org/sites/default/files/media/publication/doc/UNITAR_Strategic%20Framework_2022-2025.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>https://unitar.org/about/unitar/governance/board-trustees/board-reports</t>
+          <t>https://digitallibrary.un.org/search?ln=en&amp;cc=Reports&amp;p=%22UN+Interim+Security+Force+for+Abyei%22+OR+UNISFA&amp;f=&amp;action_search=Search&amp;rm=&amp;ln=en&amp;sf=year&amp;so=d&amp;rg=50&amp;c=Reports&amp;c=&amp;of=hb&amp;fti=0&amp;fti=0</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -12233,12 +12181,12 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unitar</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>https://x.com/UNITAR</t>
+          <t>https://x.com/UNISFA_1</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr"/>
@@ -12249,36 +12197,54 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UNJSPB</t>
+          <t>UNITAR</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>United Nations Joint Staff Pension Board</t>
+          <t>United Nations Institute for Training and Research</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>United Nations Joint Staff Pension Board (UNJSPB)</t>
+          <t>United Nations Institute for Training and Research (UNITAR)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>The United Nations Institute for Training and Research (UNITAR) provides innovative learning solutions to individuals, organizations and institutions to enhance global decision-making and support country-level action for shaping a better future.</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.unjspf.org/governance/</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+          <t>https://unitar.org/</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Training_and_Research</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://unitar.org/news-events</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="b">
+        <v>1</v>
+      </c>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -12286,69 +12252,83 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr"/>
+          <t>Research and Training</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="b">
+        <v>0</v>
+      </c>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr"/>
-      <c r="Y132" t="inlineStr"/>
-      <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr"/>
-      <c r="AB132" t="inlineStr"/>
-      <c r="AC132" t="inlineStr"/>
-      <c r="AD132" t="inlineStr"/>
-      <c r="AE132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>https://unitar.org/about/programme-budget</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>https://unitar.org/results-evidence-learning/results-reports-and-other-reports</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>https://unitar.org/sites/default/files/media/publication/doc/UNITAR_Strategic%20Framework_2022-2025.pdf</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>https://unitar.org/about/unitar/governance/board-trustees/board-reports</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unitar</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>https://x.com/UNITAR</t>
+        </is>
+      </c>
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNMIK</t>
+          <t>UNJSPB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>United Nations Interim Administration Mission in Kosovo</t>
+          <t>United Nations Joint Staff Pension Board</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>United Nations Interim Administration Mission in Kosovo (UNMIK)</t>
+          <t>United Nations Joint Staff Pension Board (UNJSPB)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Following the declaration of independence by the Kosovo authorities in 2008, the UNMIK has been mandated to focus primarily on the promotion of security, stability and respect for human rights in Kosovo</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://unmik.unmissions.org/</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Administration_Mission_in_Kosovo</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>https://unmik.unmissions.org/news</t>
-        </is>
-      </c>
+          <t>https://www.unjspf.org/governance/</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
@@ -12358,103 +12338,72 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Peacekeeping Operations</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="b">
-        <v>0</v>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unmik.unmissions.org/mandate&gt;
-</t>
-        </is>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>https://unmik.unmissions.org/united-nations-resolution-1244</t>
-        </is>
-      </c>
+      <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>https://unmik.unmissions.org/sg-reports</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unmik</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>https://x.com/UNMIKosovo</t>
-        </is>
-      </c>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNMISS</t>
+          <t>UNMIK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan</t>
+          <t>United Nations Interim Administration Mission in Kosovo</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan (UNMISS)</t>
+          <t>United Nations Interim Administration Mission in Kosovo (UNMIK)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>UNMISS' efforts in South Sudan focus on the protection of civilians, delivering humanitarian assistance, supporting the implementation of the revitalized agreement and the peace process, and monitoring and investigating human rights</t>
+          <t>Following the declaration of independence by the Kosovo authorities in 2008, the UNMIK has been mandated to focus primarily on the promotion of security, stability and respect for human rights in Kosovo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://unmiss.unmissions.org/</t>
+          <t>https://unmik.unmissions.org/</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Mission_in_South_Sudan</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Administration_Mission_in_Kosovo</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://unmiss.unmissions.org/news</t>
+          <t>https://unmik.unmissions.org/news</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -12480,13 +12429,17 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;https://unmiss.unmissions.org/mandate&gt;
+          <t xml:space="preserve">&lt;https://unmik.unmissions.org/mandate&gt;
 </t>
         </is>
       </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>https://unmik.unmissions.org/united-nations-resolution-1244</t>
+        </is>
+      </c>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr">
         <is>
@@ -12500,7 +12453,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>https://unmiss.unmissions.org/documents</t>
+          <t>https://unmik.unmissions.org/sg-reports</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -12510,12 +12463,12 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unmiss/</t>
+          <t>https://www.linkedin.com/company/unmik</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>https://x.com/unmissmedia</t>
+          <t>https://x.com/UNMIKosovo</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr"/>
@@ -12526,39 +12479,39 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UNMOGIP</t>
+          <t>UNMISS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>United Nations Military Observer Group in India and Pakistan</t>
+          <t>United Nations Mission in South Sudan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>United Nations Military Observer Group in India and Pakistan (UNMOGIP)</t>
+          <t>United Nations Mission in South Sudan (UNMISS)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>UNMOGIP supervises, in the State of Jammu and Kashmir, the ceasefire between India and Pakistan, and assists the Military Adviser to the United Nations Commission for India and Pakistan</t>
+          <t>UNMISS' efforts in South Sudan focus on the protection of civilians, delivering humanitarian assistance, supporting the implementation of the revitalized agreement and the peace process, and monitoring and investigating human rights</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://unmogip.unmissions.org/</t>
+          <t>https://unmiss.unmissions.org/</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Military_Observer_Group_in_India_and_Pakistan</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Mission_in_South_Sudan</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://unmiss.unmissions.org/news</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -12582,7 +12535,12 @@
       <c r="T135" t="b">
         <v>0</v>
       </c>
-      <c r="U135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unmiss.unmissions.org/mandate&gt;
+</t>
+        </is>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
@@ -12599,7 +12557,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>https://unmogip.unmissions.org/reports</t>
+          <t>https://unmiss.unmissions.org/documents</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -12609,10 +12567,14 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/unmiss/</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>https://x.com/unmissmedia</t>
+        </is>
+      </c>
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>1</v>
@@ -12621,39 +12583,39 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UNOAU</t>
+          <t>UNMOGIP</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>United Nations Office to the African Union</t>
+          <t>United Nations Military Observer Group in India and Pakistan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>United Nations Office to the African Union (UNOAU)</t>
+          <t>United Nations Military Observer Group in India and Pakistan (UNMOGIP)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>UNOAU is mandated to enhance the partnership between the United Nations and the African Union in the area of peace and security and provide United Nations advice to the African Union on both long-term capacity-building and short-term operational support</t>
+          <t>UNMOGIP supervises, in the State of Jammu and Kashmir, the ceasefire between India and Pakistan, and assists the Military Adviser to the United Nations Commission for India and Pakistan</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://unoau.unmissions.org/</t>
+          <t>https://unmogip.unmissions.org/</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_to_the_African_Union</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Military_Observer_Group_in_India_and_Pakistan</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://unoau.unmissions.org/en/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -12670,19 +12632,14 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Peacekeeping Operations</t>
         </is>
       </c>
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="b">
         <v>0</v>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unoau.unmissions.org/mandate&gt;
-</t>
-        </is>
-      </c>
+      <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
@@ -12699,7 +12656,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>https://unoau.unmissions.org/documents</t>
+          <t>https://unmogip.unmissions.org/reports</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -12721,39 +12678,39 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UNOCA</t>
+          <t>UNOAU</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>United Nations Regional Office for Central Africa</t>
+          <t>United Nations Office to the African Union</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>United Nations Regional Office for Central Africa (UNOCA)</t>
+          <t>United Nations Office to the African Union (UNOAU)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>UNOCA has a regional mandate to help prevent conflict and consolidate peace in Central Africa and provides assistance to support preventive diplomacy and mediation in situations of tension or potential conflict.</t>
+          <t>UNOAU is mandated to enhance the partnership between the United Nations and the African Union in the area of peace and security and provide United Nations advice to the African Union on both long-term capacity-building and short-term operational support</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://unoca.unmissions.org/</t>
+          <t>https://unoau.unmissions.org/</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Regional_Office_for_Central_Africa</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_to_the_African_Union</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://unoca.unmissions.org/en/news</t>
+          <t>https://unoau.unmissions.org/en/news</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -12779,7 +12736,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;https://unoca.unmissions.org/en/mandate-and-missions&gt;
+          <t xml:space="preserve">&lt;https://unoau.unmissions.org/mandate&gt;
 </t>
         </is>
       </c>
@@ -12799,7 +12756,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>https://unoca.unmissions.org/rapports-du-s%C3%A9cr%C3%A9taire-g%C3%A9n%C3%A9ral</t>
+          <t>https://unoau.unmissions.org/documents</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -12821,83 +12778,85 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UNODC</t>
+          <t>UNOCA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>United Nations Office on Drugs and Crime</t>
+          <t>United Nations Regional Office for Central Africa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>United Nations Office on Drugs and Crime (UNODC)</t>
+          <t>United Nations Regional Office for Central Africa (UNOCA)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>The UNODC is the secretariat of the Conference of the Parties to the UN Convention against Transnational Organized Crime and of the Conference of the States Parties to the UN Convention against Corruption.</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+          <t>UNOCA has a regional mandate to help prevent conflict and consolidate peace in Central Africa and provides assistance to support preventive diplomacy and mediation in situations of tension or potential conflict.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.unodc.org/</t>
+          <t>https://unoca.unmissions.org/</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_on_Drugs_and_Crime</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Regional_Office_for_Central_Africa</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://www.unodc.org/unodc/en/press/releases.html</t>
+          <t>https://unoca.unmissions.org/en/news</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="b">
-        <v>1</v>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr"/>
+          <t>Security Council</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Special Political Missions and Other Political Presences</t>
+        </is>
+      </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="b">
-        <v>1</v>
-      </c>
-      <c r="U138" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unoca.unmissions.org/en/mandate-and-missions&gt;
+</t>
+        </is>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>https://www.unodc.org/unodc/en/evaluation/reports.html</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>https://www.unodc.org/unodc/en/strategy/index.html</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>https://www.unodc.org/unodc/en/about-unodc/annual-report.html</t>
+          <t>https://unoca.unmissions.org/rapports-du-s%C3%A9cr%C3%A9taire-g%C3%A9n%C3%A9ral</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -12907,14 +12866,10 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-office-on-drugs-and-crime-unodc/</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>https://x.com/UNODC</t>
-        </is>
-      </c>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>1</v>
@@ -12923,39 +12878,44 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UNOG</t>
+          <t>UNODC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>United Nations Office at Geneva</t>
+          <t>United Nations Office on Drugs and Crime</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>United Nations Office at Geneva (UNOG)</t>
+          <t>United Nations Office on Drugs and Crime (UNODC)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>The UNOG services more than 8,000 meetings every year, making it one of the busiest conference centres in the world. With more than 1,600 staff, it is the biggest duty stations outside of United Nations headquarters in New York.</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
+          <t>The UNODC is the secretariat of the Conference of the Parties to the UN Convention against Transnational Organized Crime and of the Conference of the States Parties to the UN Convention against Corruption.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.ungeneva.org/</t>
+          <t>https://www.unodc.org/</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Geneva</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_on_Drugs_and_Crime</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://www.ungeneva.org/en/news-media</t>
+          <t>https://www.unodc.org/unodc/en/press/releases.html</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
@@ -12975,7 +12935,7 @@
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
@@ -12984,17 +12944,17 @@
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unodc.org/unodc/en/evaluation/reports.html</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unodc.org/unodc/en/strategy/index.html</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>https://sites.ungeneva.org/annualreport/2021/</t>
+          <t>https://www.unodc.org/unodc/en/about-unodc/annual-report.html</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -13004,10 +12964,14 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-office-at-geneva/</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/united-nations-office-on-drugs-and-crime-unodc/</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>https://x.com/UNODC</t>
+        </is>
+      </c>
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>1</v>
@@ -13016,42 +12980,48 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNOMS</t>
+          <t>UNOG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Office of the United Nations Ombudsman and Mediation Services</t>
+          <t>United Nations Office at Geneva</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Office of the United Nations Ombudsman and Mediation Services (UNOMS)</t>
+          <t>United Nations Office at Geneva (UNOG)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>The UNOG services more than 8,000 meetings every year, making it one of the busiest conference centres in the world. With more than 1,600 staff, it is the biggest duty stations outside of United Nations headquarters in New York.</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.un.org/ombudsman/</t>
+          <t>https://www.ungeneva.org/</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Ombudsman_and_Mediation_Services</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Geneva</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.ungeneva.org/en/news-media</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="b">
+        <v>1</v>
+      </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
@@ -13059,11 +13029,7 @@
           <t>Secretariat</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
-        </is>
-      </c>
+      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="b">
         <v>0</v>
@@ -13085,7 +13051,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>https://www.un.org/ombudsman/resources/annual-reports</t>
+          <t>https://sites.ungeneva.org/annualreport/2021/</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -13095,7 +13061,7 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/united-nations-office-at-geneva/</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr"/>
@@ -13107,48 +13073,42 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UNON</t>
+          <t>UNOMS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>United Nations Office at Nairobi</t>
+          <t>Office of the United Nations Ombudsman and Mediation Services</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>United Nations Office at Nairobi (UNON)</t>
+          <t>Office of the United Nations Ombudsman and Mediation Services (UNOMS)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>The UNON performs representation and liaison functions and facilitates cooperation between with permanent missions, the host-country and other Governments, and intergovernmental and non-governmental organizations in Nairobi.</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.unon.org/</t>
+          <t>https://www.un.org/ombudsman/</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Nairobi</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Ombudsman_and_Mediation_Services</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://www.unon.org/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="b">
-        <v>1</v>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr">
@@ -13156,7 +13116,11 @@
           <t>Secretariat</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+        </is>
+      </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="b">
         <v>0</v>
@@ -13178,7 +13142,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>No annual report</t>
+          <t>https://www.un.org/ombudsman/resources/annual-reports</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -13188,7 +13152,7 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-office-at-nairobi-unon/</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr"/>
@@ -13200,39 +13164,48 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>UNOP</t>
+          <t>UNON</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>United Nations Office for Partnerships</t>
+          <t>United Nations Office at Nairobi</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>United Nations Office for Partnerships (UNOP)</t>
+          <t>United Nations Office at Nairobi (UNON)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- The United Nations Office for Partnerships is the focal point vis-a-vis the United Nations Foundation, Inc.
-</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>The UNON performs representation and liaison functions and facilitates cooperation between with permanent missions, the host-country and other Governments, and intergovernmental and non-governmental organizations in Nairobi.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://unpartnerships.un.org/</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+          <t>https://www.unon.org/</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Nairobi</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://www.unon.org/news</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="b">
+        <v>1</v>
+      </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
@@ -13249,16 +13222,32 @@
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>https://mptf.undp.org/participating-organizations/unop</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
-      <c r="AB142" t="inlineStr"/>
-      <c r="AC142" t="inlineStr"/>
-      <c r="AD142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>No annual report</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/united-nations-office-at-nairobi-unon/</t>
+        </is>
+      </c>
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
@@ -13268,105 +13257,65 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>UNOPS</t>
+          <t>UNOP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>United Nations Office for Project Services</t>
+          <t>United Nations Office for Partnerships</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>United Nations Office for Project Services (UNOPS)</t>
+          <t>United Nations Office for Partnerships (UNOP)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>UNOPS' mission is to expand the capacity of the UN system and its partners to implement peace building, humanitarian and development operations that matter for people in need.</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+          <t xml:space="preserve">- The United Nations Office for Partnerships is the focal point vis-a-vis the United Nations Foundation, Inc.
 </t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.unops.org/</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Project_Services</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>https://www.unops.org/news-and-stories</t>
-        </is>
-      </c>
+          <t>https://unpartnerships.un.org/</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Copenhagen, Denmark</t>
-        </is>
-      </c>
+      <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>Other Entities</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>https://content.unops.org/documents/libraries/policies-2020/executive-office-directives-and-instructions/organizational-principles-and-governance-model/en/UNOPS-organigramme_EN.pdf</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>https://docs.un.org/en/DP/OPS/2025/9</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>https://www.unops.org/about/governance/executive-board/executive-board-documents</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>https://data.unops.org/</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unops/</t>
-        </is>
-      </c>
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>https://mptf.undp.org/participating-organizations/unop</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
@@ -13376,36 +13325,57 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UNOSSC</t>
+          <t>UNOPS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>United Nations Office for South-South Cooperation</t>
+          <t>United Nations Office for Project Services</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>United Nations Office for South-South Cooperation (UNOSSC)</t>
+          <t>United Nations Office for Project Services (UNOPS)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>UNOPS' mission is to expand the capacity of the UN system and its partners to implement peace building, humanitarian and development operations that matter for people in need.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://unsouthsouth.org/</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
+          <t>https://www.unops.org/</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Project_Services</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://www.unops.org/news-and-stories</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Copenhagen, Denmark</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -13413,23 +13383,47 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
+          <t>Other Entities</t>
         </is>
       </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>https://content.unops.org/documents/libraries/policies-2020/executive-office-directives-and-instructions/organizational-principles-and-governance-model/en/UNOPS-organigramme_EN.pdf</t>
+        </is>
+      </c>
       <c r="Y144" t="inlineStr"/>
-      <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
-      <c r="AB144" t="inlineStr"/>
-      <c r="AC144" t="inlineStr"/>
-      <c r="AD144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/DP/OPS/2025/9</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>https://www.unops.org/about/governance/executive-board/executive-board-documents</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>https://data.unops.org/</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unops/</t>
+        </is>
+      </c>
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
@@ -13439,56 +13433,46 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>UNOV</t>
+          <t>UNOSSC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>United Nations Office at Vienna</t>
+          <t>United Nations Office for South-South Cooperation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>United Nations Office at Vienna (UNOV)</t>
+          <t>United Nations Office for South-South Cooperation (UNOSSC)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>The UNOV performs representation and liaison functions with permanent missions to the United Nations (Vienna), the host Government and intergovernmental and non-governmental organizations in Vienna.</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.unvienna.org/</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Vienna</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>https://www.unvienna.org/unov/en/news.html</t>
-        </is>
-      </c>
+          <t>https://unsouthsouth.org/</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="b">
-        <v>1</v>
-      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Funds and Programmes</t>
+        </is>
+      </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="b">
         <v>0</v>
@@ -13498,31 +13482,11 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>No annual report (only from the SG)</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-office-at-vienna/</t>
-        </is>
-      </c>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
@@ -13532,75 +13496,64 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>UNOWAS</t>
+          <t>UNOV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>United Nations Office for West Africa and the Sahel</t>
+          <t>United Nations Office at Vienna</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>United Nations Office for West Africa and the Sahel (UNOWAS)</t>
+          <t>United Nations Office at Vienna (UNOV)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>UNOWAS has the responsibility for preventive diplomacy, good offices and political mediation and facilitation efforts in West Africa and the Sahel and works to consolidate peace and democratic governance in countries emerging from conflict or political crises.</t>
+          <t>The UNOV performs representation and liaison functions with permanent missions to the United Nations (Vienna), the host Government and intergovernmental and non-governmental organizations in Vienna.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://unowas.unmissions.org/</t>
+          <t>https://www.unvienna.org/</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_West_Africa_and_the_Sahel</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Vienna</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://unowas.unmissions.org/news</t>
+          <t>https://www.unvienna.org/unov/en/news.html</t>
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="b">
+        <v>1</v>
+      </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Special Political Missions and Other Political Presences</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="b">
         <v>0</v>
       </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unowas.unmissions.org/unowas-mandate&gt;
-</t>
-        </is>
-      </c>
+      <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>https://unowas.unmissions.org/unowas-mandate</t>
-        </is>
-      </c>
+      <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr">
         <is>
@@ -13614,7 +13567,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>https://unowas.unmissions.org/reports</t>
+          <t>No annual report (only from the SG)</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -13624,7 +13577,7 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/united-nations-office-at-vienna/</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr"/>
@@ -13636,29 +13589,41 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>UNPC</t>
+          <t>UNOWAS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Peacebuilding Commission</t>
+          <t>United Nations Office for West Africa and the Sahel</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Peacebuilding Commission (UNPC)</t>
+          <t>United Nations Office for West Africa and the Sahel (UNOWAS)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>UNOWAS has the responsibility for preventive diplomacy, good offices and political mediation and facilitation efforts in West Africa and the Sahel and works to consolidate peace and democratic governance in countries emerging from conflict or political crises.</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.un.org/peacebuilding/commission</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+          <t>https://unowas.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_West_Africa_and_the_Sahel</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://unowas.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
@@ -13668,22 +13633,57 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>['General Assembly', 'Security Council']</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr"/>
+          <t>Security Council</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Special Political Missions and Other Political Presences</t>
+        </is>
+      </c>
       <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
-      <c r="U147" t="inlineStr"/>
+      <c r="T147" t="b">
+        <v>0</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unowas.unmissions.org/unowas-mandate&gt;
+</t>
+        </is>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>https://unowas.unmissions.org/unowas-mandate</t>
+        </is>
+      </c>
       <c r="Y147" t="inlineStr"/>
-      <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
-      <c r="AB147" t="inlineStr"/>
-      <c r="AC147" t="inlineStr"/>
-      <c r="AD147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>https://unowas.unmissions.org/reports</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">

--- a/public/un-entities.xlsx
+++ b/public/un-entities.xlsx
@@ -1113,7 +1113,11 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.ohchr.org/en/treaty-bodies/cescr</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1215,23 +1219,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Committee for Programme and Coordination</t>
+          <t>United Nations Commission on Population and Development</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Committee for Programme and Coordination (CPC)</t>
+          <t>United Nations Commission on Population and Development (CPD)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.un.org/development/desa/pd/content/CPD</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Other Bodies and Committees</t>
+          <t>Functional Commissions</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1266,23 +1274,23 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CSTD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>United Nations Commission on Population and Development</t>
+          <t>United Nations Commission on Science and Technology for Development</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>United Nations Commission on Population and Development (CPD)</t>
+          <t>United Nations Commission on Science and Technology for Development (CSTD)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1290,7 +1298,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.un.org/development/desa/pd/content/CPD</t>
+          <t>https://unctad.org/topic/commission-on-science-and-technology-for-development</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1333,17 +1341,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CSTD</t>
+          <t>CSW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>United Nations Commission on Science and Technology for Development</t>
+          <t>United Nations Commission on the Status of Women</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>United Nations Commission on Science and Technology for Development (CSTD)</t>
+          <t>United Nations Commission on the Status of Women (CSW)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1351,7 +1359,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://unctad.org/topic/commission-on-science-and-technology-for-development</t>
+          <t>https://www.unwomen.org/en/how-we-work/commission-on-the-status-of-women</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1394,17 +1402,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CSW</t>
+          <t>CSocD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United Nations Commission on the Status of Women</t>
+          <t>United Nations Commission for Social Development</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>United Nations Commission on the Status of Women (CSW)</t>
+          <t>United Nations Commission for Social Development (CSocD)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1412,7 +1420,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/how-we-work/commission-on-the-status-of-women</t>
+          <t>https://social.desa.un.org/csocd</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1455,58 +1463,99 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CSocD</t>
+          <t>CTBTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United Nations Commission for Social Development</t>
+          <t>Preparatory Commission for the Comprehensive Nuclear-Test-Ban Treaty Organization</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>United Nations Commission for Social Development (CSocD)</t>
+          <t>Preparatory Commission for the Comprehensive Nuclear-Test-Ban Treaty Organization (CTBTO)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The CTBTO Preparatory Commission is mandated to carry out the necessary preparations for the entry into force and effective implementation of the Comprehensive Nuclear-Test-Ban Treaty (CTBT).</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://social.desa.un.org/csocd</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>https://www.ctbto.org/</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Comprehensive_Nuclear-Test-Ban_Treaty_Organization_Preparatory_Commission</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.ctbto.org/press-centre/news</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vienna, Austria</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Functional Commissions</t>
-        </is>
-      </c>
+          <t>Related Organizations</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>https://www.ctbto.org/publications/annual-reports/</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ctbto/</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
@@ -1516,99 +1565,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CTBTO</t>
+          <t>CTC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Preparatory Commission for the Comprehensive Nuclear-Test-Ban Treaty Organization</t>
+          <t>Counter-Terrorism Committee</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Preparatory Commission for the Comprehensive Nuclear-Test-Ban Treaty Organization (CTBTO)</t>
+          <t>Counter-Terrorism Committee (CTC)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>The CTBTO Preparatory Commission is mandated to carry out the necessary preparations for the entry into force and effective implementation of the Comprehensive Nuclear-Test-Ban Treaty (CTBT).</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.ctbto.org/</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Comprehensive_Nuclear-Test-Ban_Treaty_Organization_Preparatory_Commission</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>https://www.ctbto.org/press-centre/news</t>
-        </is>
-      </c>
+          <t>https://www.un.org/securitycouncil/ctc/</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Vienna, Austria</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Related Organizations</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+          <t>Security Council</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Committees</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>https://www.ctbto.org/publications/annual-reports/</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/ctbto/</t>
-        </is>
-      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
@@ -1618,17 +1626,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CTC</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Counter-Terrorism Committee</t>
+          <t>Development Account</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Counter-Terrorism Committee (CTC)</t>
+          <t>Development Account (DA)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1636,11 +1644,19 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.un.org/securitycouncil/ctc/</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>https://da.desa.un.org/</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Account</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1650,64 +1666,94 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Committees</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>https://da.desa.un.org/static-official-public</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>https://da.desa.un.org/project-view-public</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>DCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Development Account</t>
+          <t xml:space="preserve">Development Coordination Office </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Development Account (DA)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+          <t>Development Coordination Office  (DCO)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>The Resident Coordinator System (RCS) is the backbone around which the United Nations development entities are taking steps to strengthen support to the 2030 Agenda.</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://da.desa.un.org/</t>
+          <t>https://un-dco.org/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Account</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Coordination_Office</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://un-dco.org/news</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1728,14 +1774,18 @@
         <v>0</v>
       </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://mandates.un.org/entity/RCS</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://un-dco.org/</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -1748,12 +1798,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://da.desa.un.org/static-official-public</t>
+          <t>https://unsdg.un.org/resources/unsdg-chair-reports</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://da.desa.un.org/project-view-public</t>
+          <t>https://unsdg.un.org/SPTF</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -1764,49 +1814,45 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DCO</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Development Coordination Office </t>
+          <t>Department of Economic and Social Affairs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Development Coordination Office  (DCO)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>RCS</t>
-        </is>
-      </c>
+          <t>Department of Economic and Social Affairs (DESA)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The Resident Coordinator System (RCS) is the backbone around which the United Nations development entities are taking steps to strengthen support to the 2030 Agenda.</t>
+          <t>UN DESA helps countries translate their global commitments into national action in the economic, social and environmental spheres.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://un-dco.org/</t>
+          <t>https://www.un.org/development/desa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Coordination_Office</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Economic_and_Social_Affairs</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://un-dco.org/news</t>
+          <t>https://www.un.org/development/desa/en/news.html</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1827,18 +1873,18 @@
         <v>0</v>
       </c>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>https://mandates.un.org/entity/RCS</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://un-dco.org/</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>https://www.un.org/development/desa/en/about/organigramme</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -1851,20 +1897,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>https://unsdg.un.org/resources/unsdg-chair-reports</t>
+          <t>https://desapublications.un.org/?keywords=un+desa+annual+highlights&amp;sort_by=date&amp;sort_order=DESC</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://unsdg.un.org/SPTF</t>
+          <t>https://open.un.org/un-secretariat-financials/expenses</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/united-nations-department-of-economic-and-social-affairs</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>https://x.com/UNDESA</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>1</v>
@@ -1873,46 +1923,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>DGACM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Department of Economic and Social Affairs</t>
+          <t>Department for General Assembly and Conference Management</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Department of Economic and Social Affairs (DESA)</t>
+          <t>Department for General Assembly and Conference Management (DGACM)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UN DESA helps countries translate their global commitments into national action in the economic, social and environmental spheres.</t>
+          <t>The DGACM enhances dialogue and cooperation among Member States and, by doing so, to contributes to the realization of the objectives of the United Nations and of the Millennium Development Goals.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.un.org/development/desa</t>
+          <t>https://www.un.org/dgacm/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Economic_and_Social_Affairs</t>
+          <t>https://en.wikipedia.org/wiki/Department_for_General_Assembly_and_Conference_Management</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.un.org/development/desa/en/news.html</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
@@ -1930,7 +1982,7 @@
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.un.org/development/desa/en/about/organigramme</t>
+          <t>https://www.un.org/dgacm/en/content/structure</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -1950,7 +2002,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>https://desapublications.un.org/?keywords=un+desa+annual+highlights&amp;sort_by=date&amp;sort_order=DESC</t>
+          <t>No annual report</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -1960,12 +2012,12 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-department-of-economic-and-social-affairs</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>https://x.com/UNDESA</t>
+          <t>https://x.com/UNDGACM_EN</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr"/>
@@ -1976,34 +2028,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DGACM</t>
+          <t>DGC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Department for General Assembly and Conference Management</t>
+          <t>Department of Global Communications</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Department for General Assembly and Conference Management (DGACM)</t>
+          <t>Department of Global Communications (DGC)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The DGACM enhances dialogue and cooperation among Member States and, by doing so, to contributes to the realization of the objectives of the United Nations and of the Millennium Development Goals.</t>
+          <t>The DGC is dedicated to communicating the ideals and work of the United Nations to the world across multiple platforms, helping build support for peace, sustainable development and human rights for all.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.un.org/dgacm/</t>
+          <t>https://www.un.org/en/sections/departments/department-global-communications/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Department_for_General_Assembly_and_Conference_Management</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Global_Communications</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2015,9 +2067,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
@@ -2033,14 +2083,10 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>https://www.un.org/dgacm/en/content/structure</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://digitallibrary.un.org/record/4010720?ln=&amp;v=pdf</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2068,11 +2114,7 @@
           <t>Not found.</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>https://x.com/UNDGACM_EN</t>
-        </is>
-      </c>
+      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>1</v>
@@ -2081,34 +2123,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DGC</t>
+          <t>DMSPC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Department of Global Communications</t>
+          <t>Department of Management Strategy, Policy and Compliance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Department of Global Communications (DGC)</t>
+          <t>Department of Management Strategy, Policy and Compliance (DMSPC)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The DGC is dedicated to communicating the ideals and work of the United Nations to the world across multiple platforms, helping build support for peace, sustainable development and human rights for all.</t>
+          <t>The DMSPC serves the United Nations globally to drive organizational excellence through innovation, accountability and solutions.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/sections/departments/department-global-communications/</t>
+          <t>https://www.un.org/management/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Global_Communications</t>
+          <t>https://en.wikipedia.org/wiki/Department_of_Management_Strategy,_Policy_and_Compliance</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2139,7 +2181,7 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://digitallibrary.un.org/record/4010720?ln=&amp;v=pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -2154,7 +2196,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>No annual report</t>
+          <t>https://reform.un.org/content/management-reform</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2176,34 +2218,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DMSPC</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Department of Management Strategy, Policy and Compliance</t>
+          <t>Department of Operational Support</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Department of Management Strategy, Policy and Compliance (DMSPC)</t>
+          <t>Department of Operational Support (DOS)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The DMSPC serves the United Nations globally to drive organizational excellence through innovation, accountability and solutions.</t>
+          <t>The DOS provides operational support to UN Secretariat entities, including advisory, operational and transactional support services and, where needed, exercises delegated authority on behalf of clients.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.un.org/management/</t>
+          <t>https://operationalsupport.un.org/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Department_of_Management_Strategy,_Policy_and_Compliance</t>
+          <t>https://en.wikipedia.org/wiki/Department_of_Operational_Support</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2231,7 +2273,11 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>https://operationalsupport.un.org/en/organizational-structure</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -2239,17 +2285,17 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://operationalsupport.un.org/en/performance-overview</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://operationalsupport.un.org/strategic-foundations</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>https://reform.un.org/content/management-reform</t>
+          <t>https://operationalsupport.un.org/en/reports-and-resolutions</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2262,7 +2308,11 @@
           <t>Not found.</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>https://x.com/UN_OpSupport</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>1</v>
@@ -2271,46 +2321,48 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>DPO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Department of Operational Support</t>
+          <t>Department of Peace Operations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Department of Operational Support (DOS)</t>
+          <t>Department of Peace Operations (DPO)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>The DOS provides operational support to UN Secretariat entities, including advisory, operational and transactional support services and, where needed, exercises delegated authority on behalf of clients.</t>
+          <t>DPO provides political and executive direction to UN peacekeeping operations around the world and maintains contact with the Security Council, troop and financial contributors, and parties to the conflict in the implementation of Security Council mandates.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://operationalsupport.un.org/</t>
+          <t>https://peacekeeping.un.org/en/department-of-peace-operations</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Department_of_Operational_Support</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Peace_Operations</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://peacekeeping.un.org/en/news</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
@@ -2328,7 +2380,7 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://operationalsupport.un.org/en/organizational-structure</t>
+          <t>https://peacekeeping.un.org/en/department-of-peace-operations</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2338,17 +2390,17 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://operationalsupport.un.org/en/performance-overview</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>https://operationalsupport.un.org/strategic-foundations</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>https://operationalsupport.un.org/en/reports-and-resolutions</t>
+          <t>https://peacekeeping.un.org/en/reports</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2358,12 +2410,12 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/un-department-of-peace-operations/</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>https://x.com/UN_OpSupport</t>
+          <t>https://x.com/UNPeacekeeping</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr"/>
@@ -2374,48 +2426,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DPO</t>
+          <t>DPPA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Department of Peace Operations</t>
+          <t>Department of Political and Peacebuilding Affairs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Department of Peace Operations (DPO)</t>
+          <t>Department of Political and Peacebuilding Affairs (DPPA)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DPO provides political and executive direction to UN peacekeeping operations around the world and maintains contact with the Security Council, troop and financial contributors, and parties to the conflict in the implementation of Security Council mandates.</t>
+          <t>DPPA monitors and assesses global political developments with an eye to detecting potential crises before they erupt and devising effective responses.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://peacekeeping.un.org/en/department-of-peace-operations</t>
+          <t>https://dppa.un.org/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Peace_Operations</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Political_and_Peacebuilding_Affairs</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://peacekeeping.un.org/en/news</t>
+          <t>https://dppa.un.org/en/news</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="b">
-        <v>1</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
@@ -2431,11 +2481,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>https://peacekeeping.un.org/en/department-of-peace-operations</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -2443,17 +2489,17 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://dppa.un.org/en/2023-2026-results-framework</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://dppa.un.org/en/dppa-strategic-plan-2023-2026-updated</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>https://peacekeeping.un.org/en/reports</t>
+          <t>https://dppa.un.org/en/reports-and-policy-documents</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -2463,12 +2509,12 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-department-of-peace-operations/</t>
+          <t>https://www.linkedin.com/company/un-dppa/</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>https://x.com/UNPeacekeeping</t>
+          <t>https://x.com/UNDPPA</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr"/>
@@ -2479,39 +2525,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DPPA</t>
+          <t>DSS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Department of Political and Peacebuilding Affairs</t>
+          <t>Department of Safety and Security</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Department of Political and Peacebuilding Affairs (DPPA)</t>
+          <t>Department of Safety and Security (DSS)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DPPA monitors and assesses global political developments with an eye to detecting potential crises before they erupt and devising effective responses.</t>
+          <t>The UNDSS provides critical advice and rapid decision-making capacity on UNSMS policy and operational issues to UNSMS members, senior United Nations management and personnel.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://dppa.un.org/</t>
+          <t>https://www.un.org/undss/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Political_and_Peacebuilding_Affairs</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Safety_and_Security</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://dppa.un.org/en/news</t>
+          <t>https://www.un.org/undss/news</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -2534,7 +2580,11 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>https://www.un.org/safety-and-security/en/about-us/organisational-chart</t>
+        </is>
+      </c>
       <c r="Y26" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -2542,17 +2592,17 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>https://dppa.un.org/en/2023-2026-results-framework</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>https://dppa.un.org/en/dppa-strategic-plan-2023-2026-updated</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>https://dppa.un.org/en/reports-and-policy-documents</t>
+          <t>No annual report</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -2562,14 +2612,10 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-dppa/</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>https://x.com/UNDPPA</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/united-nations-department-of-safety-and-security/</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>1</v>
@@ -2578,54 +2624,65 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DSS</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Department of Safety and Security</t>
+          <t>Economic Commission for Africa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Department of Safety and Security (DSS)</t>
+          <t>Economic Commission for Africa (ECA)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The UNDSS provides critical advice and rapid decision-making capacity on UNSMS policy and operational issues to UNSMS members, senior United Nations management and personnel.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>The ECA's mandate is to promote the economic and social development of its member States, foster intra-regional integration, and promote international cooperation for Africa's development.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- The secretariat of this entity is part of the United Nations Secretariat.
+</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.un.org/undss/</t>
+          <t>https://www.uneca.org/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Department_of_Safety_and_Security</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_Commission_for_Africa</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.un.org/undss/news</t>
+          <t>https://www.uneca.org/stories</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+          <t>Economic and Social Council</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Regional Commissions</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="b">
         <v>0</v>
@@ -2633,16 +2690,8 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>https://www.un.org/safety-and-security/en/about-us/organisational-chart</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -2650,25 +2699,29 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.uneca.org/medium-term-programme-framework-%282022%E2%80%932025%29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>No annual report</t>
+          <t>https://repository.uneca.org/search?spc.page=1&amp;scope=&amp;f.entityType=Publication,equals&amp;f.flagshipPublication=Economic%20Report%20on%20Africa,equals&amp;f.dateIssued.min=2025</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>https://open.un.org/un-secretariat-financials/expenses</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-department-of-safety-and-security/</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/united-nations-economic-commission-for-africa/</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>https://x.com/ECA_OFFICIAL</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>1</v>
@@ -2677,23 +2730,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Economic Commission for Africa</t>
+          <t>Economic Commission for Europe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Economic Commission for Africa (ECA)</t>
+          <t>Economic Commission for Europe (ECE)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The ECA's mandate is to promote the economic and social development of its member States, foster intra-regional integration, and promote international cooperation for Africa's development.</t>
+          <t>As a multilateral platform, UNECE facilitates greater economic integration and cooperation among its member countries and promotes sustainable development and economic prosperity.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2704,17 +2757,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.uneca.org/</t>
+          <t>https://unece.org/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_Commission_for_Africa</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_Commission_for_Europe</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.uneca.org/stories</t>
+          <t>https://unece.org/media/news</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -2747,17 +2800,17 @@
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unece.org/evaluation-policy-0</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>https://www.uneca.org/medium-term-programme-framework-%282022%E2%80%932025%29</t>
+          <t>https://unece.org/environment-policy/public-participation/strategic-plan-2022-2030</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>https://repository.uneca.org/search?spc.page=1&amp;scope=&amp;f.entityType=Publication,equals&amp;f.flagshipPublication=Economic%20Report%20on%20Africa,equals&amp;f.dateIssued.min=2025</t>
+          <t>https://unece.org/unece-content/publications?f%5B0%5D=subprogramme%3A446</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -2767,14 +2820,10 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-economic-commission-for-africa/</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>https://x.com/ECA_OFFICIAL</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/united-nations-economic-commission-for-europe/</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>1</v>
@@ -2783,23 +2832,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ECLAC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Economic Commission for Europe</t>
+          <t>Economic Commission for Latin America and the Caribbean</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Economic Commission for Europe (ECE)</t>
+          <t>Economic Commission for Latin America and the Caribbean (ECLAC)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>As a multilateral platform, UNECE facilitates greater economic integration and cooperation among its member countries and promotes sustainable development and economic prosperity.</t>
+          <t>The ECLAC coordinates policies for the promotion of sustainable Latin American and Carriibean economic development and to foster regional and international trade.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2810,17 +2859,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://unece.org/</t>
+          <t>https://www.cepal.org/</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_Commission_for_Europe</t>
+          <t>https://en.wikipedia.org/wiki/Economic_Commission_for_Latin_America_and_the_Caribbean</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://unece.org/media/news</t>
+          <t>https://www.cepal.org/en/news</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -2846,24 +2895,29 @@
       <c r="T29" t="b">
         <v>0</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://www.cepal.org/en/about/mandate-and-mission&gt;
+</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>https://unece.org/evaluation-policy-0</t>
+          <t>https://repositorio.cepal.org/server/api/core/bitstreams/ea965022-4466-4d5c-ae96-063cbcff30f0/content</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>https://unece.org/environment-policy/public-participation/strategic-plan-2022-2030</t>
+          <t>https://caribbean.eclac.org/publications/strategic-plan-2015-2025?utm_source=chatgpt.com</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>https://unece.org/unece-content/publications?f%5B0%5D=subprogramme%3A446</t>
+          <t>https://www.cepal.org/en/publications</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -2873,10 +2927,14 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-economic-commission-for-europe/</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/eclac/</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>https://x.com/eclac_un</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>1</v>
@@ -2885,109 +2943,89 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ECLAC</t>
+          <t>EOSG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Economic Commission for Latin America and the Caribbean</t>
+          <t>Executive Office of the Secretary-General</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Economic Commission for Latin America and the Caribbean (ECLAC)</t>
+          <t>Executive Office of the Secretary-General (EOSG)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The ECLAC coordinates policies for the promotion of sustainable Latin American and Carriibean economic development and to foster regional and international trade.</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- The secretariat of this entity is part of the United Nations Secretariat.
-</t>
-        </is>
-      </c>
+          <t>The EOSG assists the Secretary-General with relations with members and organs of the United Nations and with specialized agencies and non-governmental organizations, as well as to assist with policy and coordination of the Secretariat.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.cepal.org/</t>
+          <t>https://www.un.org/sg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Economic_Commission_for_Latin_America_and_the_Caribbean</t>
+          <t>https://en.wikipedia.org/wiki/Executive_Office_of_the_Secretary-General_of_the_United_Nations</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.cepal.org/en/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="b">
-        <v>1</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Regional Commissions</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="b">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://www.cepal.org/en/about/mandate-and-mission&gt;
-</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>https://repositorio.cepal.org/server/api/core/bitstreams/ea965022-4466-4d5c-ae96-063cbcff30f0/content</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>https://caribbean.eclac.org/publications/strategic-plan-2015-2025?utm_source=chatgpt.com</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>https://www.cepal.org/en/publications</t>
-        </is>
-      </c>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://open.un.org/un-secretariat-financials/expenses</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eclac/</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>https://x.com/eclac_un</t>
-        </is>
-      </c>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>1</v>
@@ -2996,54 +3034,69 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EOSG</t>
+          <t>ESCAP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Executive Office of the Secretary-General</t>
+          <t>Economic and Social Commission for Asia and the Pacific</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Executive Office of the Secretary-General (EOSG)</t>
+          <t>Economic and Social Commission for Asia and the Pacific (ESCAP)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>The EOSG assists the Secretary-General with relations with members and organs of the United Nations and with specialized agencies and non-governmental organizations, as well as to assist with policy and coordination of the Secretariat.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>The Economic and Social Commission for Asia and the Pacific serves as the United Nations’ regional hub promoting cooperation among countries to achieve inclusive and sustainable development. It is the largest regional intergovernmental platform with 53 Member States and 9 associate members.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- The secretariat of this entity is part of the United Nations Secretariat.
+</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.un.org/sg</t>
+          <t>https://www.unescap.org/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Executive_Office_of_the_Secretary-General_of_the_United_Nations</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_and_Social_Commission_for_Asia_and_the_Pacific</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.unescap.org/news</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://data.unescap.org/</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
+          <t>Economic and Social Council</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Regional Commissions</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="b">
         <v>0</v>
@@ -3052,11 +3105,7 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -3064,21 +3113,29 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr"/>
+          <t>https://www.unescap.org/sites/default/d8files/event-documents/80_21_2400174_E_2.pdf</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>https://www.unescap.org/resources?f%5B0%5D=field_resource_type_new%3A9052</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>https://open.un.org/un-secretariat-financials/expenses</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/unescap/</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>https://x.com/UNESCAP</t>
+        </is>
+      </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>1</v>
@@ -3087,23 +3144,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ESCAP</t>
+          <t>ESCWA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Economic and Social Commission for Asia and the Pacific</t>
+          <t>Economic and Social Commission for Western Asia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Economic and Social Commission for Asia and the Pacific (ESCAP)</t>
+          <t>Economic and Social Commission for Western Asia (ESCWA)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>The Economic and Social Commission for Asia and the Pacific serves as the United Nations’ regional hub promoting cooperation among countries to achieve inclusive and sustainable development. It is the largest regional intergovernmental platform with 53 Member States and 9 associate members.</t>
+          <t>The purpose of ESCWA is to stimulate economic activity in member countries, strengthen cooperation between them and promote development.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3114,25 +3171,21 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.unescap.org/</t>
+          <t>https://www.unescwa.org/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_and_Social_Commission_for_Asia_and_the_Pacific</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_and_Social_Commission_for_Western_Asia</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.unescap.org/news</t>
+          <t>https://www.unescwa.org/news</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>https://data.unescap.org/</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="b">
@@ -3158,20 +3211,24 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://www.unescwa.org/about/services/budget</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unescwa.org/about/strategy</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>https://www.unescap.org/sites/default/d8files/event-documents/80_21_2400174_E_2.pdf</t>
+          <t>https://www.unescwa.org/about/strategy</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>https://www.unescap.org/resources?f%5B0%5D=field_resource_type_new%3A9052</t>
+          <t>https://archive.unescwa.org/recurring-publication-identifier/escwa-annual-report</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3181,12 +3238,12 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unescap/</t>
+          <t>https://www.linkedin.com/company/unescwa</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>https://x.com/UNESCAP</t>
+          <t>https://x.com/UNESCWA</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr"/>
@@ -3197,65 +3254,54 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ESCWA</t>
+          <t>Ethics Office</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Economic and Social Commission for Western Asia</t>
+          <t>United Nations Ethics Office</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Economic and Social Commission for Western Asia (ESCWA)</t>
+          <t>United Nations Ethics Office (Ethics Office)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The purpose of ESCWA is to stimulate economic activity in member countries, strengthen cooperation between them and promote development.</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- The secretariat of this entity is part of the United Nations Secretariat.
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The UN Ethics Office promotes an ethical organizational culture based on UN’s core values of integrity, professionalism and respect for diversity, and the values outlined in Standards of Conduct for the International Civil Service, which include independence, loyalty, impartiality, integrity, accountability and respect for human rights. The Ethics Office assists the Secretary-General in ensuring that all staff members perform their functions consistent with the highest standards of integrity as required by the Charter of the United Nations. </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.unescwa.org/</t>
+          <t>https://www.un.org/en/ethics/</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Economic_and_Social_Commission_for_Western_Asia</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Ethics_Office</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.unescwa.org/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="b">
-        <v>1</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Regional Commissions</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="b">
         <v>0</v>
@@ -3266,22 +3312,22 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.unescwa.org/about/services/budget</t>
+          <t>https://www.un.org/en/ethics/overview/documents-resources.shtml</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>https://www.unescwa.org/about/strategy</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>https://www.unescwa.org/about/strategy</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>https://archive.unescwa.org/recurring-publication-identifier/escwa-annual-report</t>
+          <t>https://www.un.org/en/ethics/overview/documents-resources.shtml</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -3291,243 +3337,209 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unescwa</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>https://x.com/UNESCWA</t>
-        </is>
-      </c>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ethics Office</t>
+          <t>FAO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>United Nations Ethics Office</t>
+          <t>Food and Agriculture Organization</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>United Nations Ethics Office (Ethics Office)</t>
+          <t>Food and Agriculture Organization (FAO)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">The UN Ethics Office promotes an ethical organizational culture based on UN’s core values of integrity, professionalism and respect for diversity, and the values outlined in Standards of Conduct for the International Civil Service, which include independence, loyalty, impartiality, integrity, accountability and respect for human rights. The Ethics Office assists the Secretary-General in ensuring that all staff members perform their functions consistent with the highest standards of integrity as required by the Charter of the United Nations. </t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>The FAO aims to: raise levels of nutrition and standards of living secure improvements in food production and distribution better the conditions of rural people and contribute toward an expanding world economy and ensure freedom from hunger.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ethics/</t>
+          <t>https://www.fao.org/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Ethics_Office</t>
+          <t>https://en.wikipedia.org/wiki/Food_and_Agriculture_Organization</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.fao.org/news</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rome, Italy</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>Specialized Agencies</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/about/org-chart/en/</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ethics/overview/documents-resources.shtml</t>
+          <t>https://www.fao.org/about/strategy-programme-budget/fao-budget/</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.fao.org/about/strategy-programme-budget/overview/planning-monitoring-reporting/en</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.fao.org/about/strategy-programme-budget/overview/FAO-Strategic-Framework/en</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ethics/overview/documents-resources.shtml</t>
+          <t>https://openknowledge.fao.org/home</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.fao.org/transparency/en</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/fao</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>https://x.com/FAO</t>
+        </is>
+      </c>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FAO</t>
+          <t>Fifth Committee</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Food and Agriculture Organization</t>
+          <t>Administrative and Budgetary Committee</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Food and Agriculture Organization (FAO)</t>
+          <t>Administrative and Budgetary Committee (Fifth Committee)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>The FAO aims to: raise levels of nutrition and standards of living secure improvements in food production and distribution better the conditions of rural people and contribute toward an expanding world economy and ensure freedom from hunger.</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.fao.org/</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Food_and_Agriculture_Organization</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/news</t>
-        </is>
-      </c>
+          <t>https://www.un.org/en/ga/fifth/index.shtml</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="b">
-        <v>1</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Rome, Italy</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="b">
-        <v>1</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Main Committees</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/about/org-chart/en/</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/about/strategy-programme-budget/fao-budget/</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/about/strategy-programme-budget/overview/planning-monitoring-reporting/en</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/about/strategy-programme-budget/overview/FAO-Strategic-Framework/en</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>https://openknowledge.fao.org/home</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>https://www.fao.org/transparency/en</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/fao</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>https://x.com/FAO</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fifth Committee</t>
+          <t>First Committee</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Administrative and Budgetary Committee</t>
+          <t>Disarmament and International Security</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Administrative and Budgetary Committee (Fifth Committee)</t>
+          <t>Disarmament and International Security (First Committee)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3535,7 +3547,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/fifth/index.shtml</t>
+          <t>https://www.un.org/en/ga/first/index.shtml</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -3582,17 +3594,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>First Committee</t>
+          <t>Fourth Committee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Disarmament and International Security</t>
+          <t>Special Political and Decolonization</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Disarmament and International Security (First Committee)</t>
+          <t>Special Political and Decolonization (Fourth Committee)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3600,7 +3612,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/first/index.shtml</t>
+          <t>https://www.un.org/en/ga/fourth/index.shtml</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -3647,17 +3659,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fourth Committee</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Special Political and Decolonization</t>
+          <t>Committee of Experts on the Transport of Dangerous Goods and on the Globally Harmonized System of Classification and Labelling of Chemicals</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Special Political and Decolonization (Fourth Committee)</t>
+          <t>Committee of Experts on the Transport of Dangerous Goods and on the Globally Harmonized System of Classification and Labelling of Chemicals (GHS)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3665,7 +3677,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/fourth/index.shtml</t>
+          <t>https://unece.org/transport/dangerous-goods/ecosoc-bodies-dealing-chemicals-safety</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3679,19 +3691,15 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Main Committees</t>
-        </is>
-      </c>
+          <t>Other Bodies and Committees</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
@@ -3712,25 +3720,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>HLPF</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Committee of Experts on the Transport of Dangerous Goods and on the Globally Harmonized System of Classification and Labelling of Chemicals</t>
+          <t>High-level Political Forum on Sustainable Development</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Committee of Experts on the Transport of Dangerous Goods and on the Globally Harmonized System of Classification and Labelling of Chemicals (GHS)</t>
+          <t>High-level Political Forum on Sustainable Development (HLPF)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- HLPF was established by the General Assembly. Meetings of HLPF are separately convened under the auspices of the General Assembly and of the Economic and Social Council.
+</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://unece.org/transport/dangerous-goods/ecosoc-bodies-dealing-chemicals-safety</t>
+          <t>https://hlpf.un.org/</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -3744,14 +3757,10 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Other Bodies and Committees</t>
-        </is>
-      </c>
+          <t>['General Assembly', 'Economic and Social Council']</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -3767,36 +3776,31 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HLPF</t>
+          <t>HRC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>High-level Political Forum on Sustainable Development</t>
+          <t>Human Rights Council</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High-level Political Forum on Sustainable Development (HLPF)</t>
+          <t>Human Rights Council (HRC)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- HLPF was established by the General Assembly. Meetings of HLPF are separately convened under the auspices of the General Assembly and of the Economic and Social Council.
-</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://hlpf.un.org/</t>
+          <t>https://www.ohchr.org/en/hrbodies/hrc/home</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -3810,11 +3814,19 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>['General Assembly', 'Economic and Social Council']</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Assemblies and Councils</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
@@ -3835,63 +3847,107 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HRC</t>
+          <t>IAEA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Human Rights Council</t>
+          <t>International Atomic Energy Agency</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Human Rights Council (HRC)</t>
+          <t>International Atomic Energy Agency (IAEA)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>The IAEA is the world's centre for cooperation in the nuclear field, promoting the safe, secure and peaceful use of nuclear technology. It works in a wide range of areas including energy generation, health, food and agriculture and environmental protection.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.ohchr.org/en/hrbodies/hrc/home</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+          <t>https://www.iaea.org/</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/International_Atomic_Energy_Agency</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/news</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vienna, Austria</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Assemblies and Councils</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>Related Organizations</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="b">
+        <v>1</v>
+      </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/about/overview/budget</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/about/overview/medium-term-strategy</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/Publications/Reports</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iaea</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>https://x.com/iaeaorg</t>
+        </is>
+      </c>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>1</v>
@@ -3900,23 +3956,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IAEA</t>
+          <t>ICAO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>International Atomic Energy Agency</t>
+          <t>International Civil Aviation Organization</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>International Atomic Energy Agency (IAEA)</t>
+          <t>International Civil Aviation Organization (ICAO)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>The IAEA is the world's centre for cooperation in the nuclear field, promoting the safe, secure and peaceful use of nuclear technology. It works in a wide range of areas including energy generation, health, food and agriculture and environmental protection.</t>
+          <t>The International Civil Aviation Organization (ICAO) is a United Nations agency which helps 193 countries to cooperate together and share their skies to their mutual benefit.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3928,33 +3984,35 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/</t>
+          <t>https://www.icao.int/</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Atomic_Energy_Agency</t>
+          <t>https://en.wikipedia.org/wiki/International_Civil_Aviation_Organization</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/news</t>
+          <t>https://www.icao.int/Newsroom</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vienna, Austria</t>
+          <t>Montreal, Canada</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Related Organizations</t>
+          <t>Specialized Agencies</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -3965,10 +4023,14 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>https://www.icao.int/sites/default/files/Meetings/a42/Documents/WP/wp_037_en.pdf</t>
+        </is>
+      </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/about/overview/budget</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -3978,12 +4040,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/about/overview/medium-term-strategy</t>
+          <t>https://www2023.icao.int/about-icao/Council/Pages/strategic-plan-2026-2050.aspx</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/Publications/Reports</t>
+          <t>https://www2023.icao.int/about-icao/Pages/annual-reports.aspx</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -3993,14 +4055,10 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/iaea</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>https://x.com/iaeaorg</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/international-civil-aviation-organization/</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>1</v>
@@ -4009,81 +4067,74 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ICAO</t>
+          <t>ICC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>International Civil Aviation Organization</t>
+          <t>International Criminal Court</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>International Civil Aviation Organization (ICAO)</t>
+          <t>International Criminal Court (ICC)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The International Civil Aviation Organization (ICAO) is a United Nations agency which helps 193 countries to cooperate together and share their skies to their mutual benefit.</t>
+          <t>The International Criminal Court (ICC) investigates and, where warranted, tries individuals charged with the gravest crimes of concern to the international community: genocide, war crimes, crimes against humanity and the crime of aggression.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+          <t xml:space="preserve">- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
 </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.icao.int/</t>
+          <t>https://www.icc-cpi.int/</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Civil_Aviation_Organization</t>
+          <t>https://en.wikipedia.org/wiki/International_Criminal_Court</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.icao.int/Newsroom</t>
+          <t>https://www.icc-cpi.int/news</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="b">
-        <v>1</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Montreal, Canada</t>
+          <t>The Hague, Netherlands</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
+          <t>Related Organizations</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>https://www.icao.int/sites/default/files/Meetings/a42/Documents/WP/wp_037_en.pdf</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://asp.icc-cpi.int/bureau/WorkingGroups/budget</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -4093,12 +4144,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>https://www2023.icao.int/about-icao/Council/Pages/strategic-plan-2026-2050.aspx</t>
+          <t>https://www.icc-cpi.int/sites/default/files/2023-08/2023-strategic-plan-icc-v.2.pdf</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>https://www2023.icao.int/about-icao/Pages/annual-reports.aspx</t>
+          <t>https://www.icc-cpi.int/resource-library/reports</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -4108,10 +4159,14 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/international-civil-aviation-organization/</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/international-criminal-court</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>https://x.com/IntlCrimCourt</t>
+        </is>
+      </c>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>1</v>
@@ -4120,44 +4175,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ICC</t>
+          <t>ICJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>International Criminal Court</t>
+          <t>International Court of Justice</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>International Criminal Court (ICC)</t>
+          <t>International Court of Justice (ICJ)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The International Criminal Court (ICC) investigates and, where warranted, tries individuals charged with the gravest crimes of concern to the international community: genocide, war crimes, crimes against humanity and the crime of aggression.</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+          <t>The Court’s role is to settle legal disputes submitted to it by States and to give advisory opinions on legal questions referred to it by authorized United Nations organs and specialized agencies.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.icc-cpi.int/</t>
+          <t>https://www.icj-cij.org/</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Criminal_Court</t>
+          <t>https://en.wikipedia.org/wiki/International_Court_of_Justice</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.icc-cpi.int/news</t>
+          <t>https://www.icj-cij.org/news</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -4166,17 +4216,17 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>The Hague, Netherlands</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Related Organizations</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
+          <t>International Court of Justice</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>International Court of Justice</t>
+        </is>
+      </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="b">
         <v>0</v>
@@ -4185,11 +4235,7 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>https://asp.icc-cpi.int/bureau/WorkingGroups/budget</t>
-        </is>
-      </c>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -4197,12 +4243,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>https://www.icc-cpi.int/sites/default/files/2023-08/2023-strategic-plan-icc-v.2.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>https://www.icc-cpi.int/resource-library/reports</t>
+          <t>https://www.icj-cij.org/en/publications</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -4212,14 +4258,10 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/international-criminal-court</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>https://x.com/IntlCrimCourt</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/cour-internationale-de-justice-international-court-of-justice/</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>1</v>
@@ -4228,39 +4270,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ICJ</t>
+          <t>ICSC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>International Court of Justice</t>
+          <t>International Civil Service Commission</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>International Court of Justice (ICJ)</t>
+          <t>International Civil Service Commission (ICSC)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The Court’s role is to settle legal disputes submitted to it by States and to give advisory opinions on legal questions referred to it by authorized United Nations organs and specialized agencies.</t>
+          <t>The ICSC's focus is to strengthen and maintain high standards in the international civil service, while balancing the needs and concerns of its major stakeholders.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.icj-cij.org/</t>
+          <t>https://icsc.un.org/</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Court_of_Justice</t>
+          <t>https://en.wikipedia.org/wiki/International_Civil_Service_Commission</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.icj-cij.org/news</t>
+          <t>https://icsc.un.org/News</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -4272,15 +4314,19 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>International Court of Justice</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>International Court of Justice</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
       <c r="T45" t="b">
         <v>0</v>
       </c>
@@ -4301,7 +4347,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>https://www.icj-cij.org/en/publications</t>
+          <t>https://icsc.un.org/Home/Library</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -4311,51 +4357,57 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/cour-internationale-de-justice-international-court-of-justice/</t>
+          <t>https://www.linkedin.com/company/international-civil-service-commission</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ICSC</t>
+          <t>IFAD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>International Civil Service Commission</t>
+          <t>International Fund for Agricultural Development</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>International Civil Service Commission (ICSC)</t>
+          <t>International Fund for Agricultural Development (IFAD)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>The ICSC's focus is to strengthen and maintain high standards in the international civil service, while balancing the needs and concerns of its major stakeholders.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>The IFAD is an international financial institution and UN specialised agency dedicated to eradicating poverty in rural areas of developing countries.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://icsc.un.org/</t>
+          <t>https://www.ifad.org/</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Civil_Service_Commission</t>
+          <t>https://en.wikipedia.org/wiki/International_Fund_for_Agricultural_Development</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://icsc.un.org/News</t>
+          <t>https://www.ifad.org/en/news-and-events</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -4364,103 +4416,101 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rome, Italy</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>https://www.ifad.org/documents/d/new-ifad.org/ifad-organigram</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>no budget, but annual financial statements (https://www.ifad.org/en/financial-documents)</t>
+        </is>
+      </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.ifad.org/en/results-management-framework</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.ifad.org/en/w/corporate-documents/policies/ifad-strategic-framework-2016-20251</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>https://icsc.un.org/Home/Library</t>
+          <t>https://www.ifad.org/pub/annual_report/list</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.ifad.org/en/operations-dashboard</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/international-civil-service-commission</t>
+          <t>https://www.linkedin.com/company/international-fund-for-agricultural-development/</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IFAD</t>
+          <t>IIIM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>International Fund for Agricultural Development</t>
+          <t>International, Impartial and Independent Mechanism to Assist in the Investigation and Prosecution of Persons Responsible for the Most Serious Crimes under International Law Committed in the Syrian Arab Republic since March 2011</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>International Fund for Agricultural Development (IFAD)</t>
+          <t>International, Impartial and Independent Mechanism to Assist in the Investigation and Prosecution of Persons Responsible for the Most Serious Crimes under International Law Committed in the Syrian Arab Republic since March 2011 (IIIM)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>The IFAD is an international financial institution and UN specialised agency dedicated to eradicating poverty in rural areas of developing countries.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+          <t>The Mechanism’s mandate, is “to collect, consolidate, preserve and analyse evidence of violations of international humanitarian law and human rights violations and abuses.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.ifad.org/</t>
+          <t>https://iiim.un.org/</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Fund_for_Agricultural_Development</t>
+          <t>https://en.wikipedia.org/wiki/International,_Impartial_and_Independent_Mechanism</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.ifad.org/en/news-and-events</t>
+          <t>https://iiim.un.org/news</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -4469,101 +4519,93 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Rome, Italy</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Other Mechanisms</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>https://www.ifad.org/documents/d/new-ifad.org/ifad-organigram</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>no budget, but annual financial statements (https://www.ifad.org/en/financial-documents)</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>https://www.ifad.org/en/results-management-framework</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>https://www.ifad.org/en/w/corporate-documents/policies/ifad-strategic-framework-2016-20251</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>https://www.ifad.org/pub/annual_report/list</t>
+          <t>https://iiim.un.org/documents/reports-to-general-assembly/</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>https://www.ifad.org/en/operations-dashboard</t>
+          <t>https://open.un.org/un-secretariat-financials/expenses</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/international-fund-for-agricultural-development/</t>
+          <t>https://www.linkedin.com/company/international-impartial-and-independent-mechanism-syria</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IIIM</t>
+          <t>IIMM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>International, Impartial and Independent Mechanism to Assist in the Investigation and Prosecution of Persons Responsible for the Most Serious Crimes under International Law Committed in the Syrian Arab Republic since March 2011</t>
+          <t>Independent Investigative Mechanism for Myanmar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>International, Impartial and Independent Mechanism to Assist in the Investigation and Prosecution of Persons Responsible for the Most Serious Crimes under International Law Committed in the Syrian Arab Republic since March 2011 (IIIM)</t>
+          <t>Independent Investigative Mechanism for Myanmar (IIMM)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>The Mechanism’s mandate, is “to collect, consolidate, preserve and analyse evidence of violations of international humanitarian law and human rights violations and abuses.</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://iiim.un.org/</t>
+          <t>https://iimm.un.org/</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International,_Impartial_and_Independent_Mechanism</t>
+          <t>https://en.wikipedia.org/wiki/Independent_Investigative_Mechanism_for_Myanmar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://iiim.un.org/news</t>
+          <t>https://iimm.un.org/news/</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -4603,12 +4645,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://iimm.un.org/strategic-plan</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>https://iiim.un.org/documents/reports-to-general-assembly/</t>
+          <t>https://iimm.un.org/en/annual-reports</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -4618,7 +4660,7 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/international-impartial-and-independent-mechanism-syria</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -4630,17 +4672,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IIMM</t>
+          <t>IIMP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Independent Investigative Mechanism for Myanmar</t>
+          <t>Independent Institution on Missing Persons in the Syrian Arab Republic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Independent Investigative Mechanism for Myanmar (IIMM)</t>
+          <t>Independent Institution on Missing Persons in the Syrian Arab Republic (IIMP)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4648,19 +4690,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://iimm.un.org/</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Independent_Investigative_Mechanism_for_Myanmar</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>https://iimm.un.org/news/</t>
-        </is>
-      </c>
+          <t>https://iimp.un.org/</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -4686,36 +4720,12 @@
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>https://iimm.un.org/strategic-plan</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>https://iimm.un.org/en/annual-reports</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>https://open.un.org/un-secretariat-financials/expenses</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
@@ -4725,17 +4735,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IIMP</t>
+          <t>ILC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Independent Institution on Missing Persons in the Syrian Arab Republic</t>
+          <t>International Law Commission</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Independent Institution on Missing Persons in the Syrian Arab Republic (IIMP)</t>
+          <t>International Law Commission (ILC)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4743,7 +4753,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://iimp.un.org/</t>
+          <t>https://legal.un.org/ilc/ilcintro.shtml</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -4762,13 +4772,15 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Other Mechanisms</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="b">
-        <v>0</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
@@ -4782,69 +4794,117 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ILC</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>International Law Commission</t>
+          <t>International Labor Organization</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>International Law Commission (ILC)</t>
+          <t>International Labor Organization (ILO)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>The ILO was founded in 1919, its Constitution forming part of the Treaty of Versailles. The ILO became the first specialised agency of the UN in 1946.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://legal.un.org/ilc/ilcintro.shtml</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>https://www.ilo.org/</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/International_Labour_Organization</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.ilo.org/global/about-the-ilo/newsroom/news/lang--en/index.htm</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="b">
+        <v>1</v>
+      </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>https://www.ilo.org/sites/default/files/2025-01/ILO_organizational%20chart_Jan-2025-EN.pdf</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>https://www.ilo.org/about-ilo/how-ilo-works/organizational-structure-international-labour-office/financial-management/programme-and-budget</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>https://www.ilo.org/about-ilo/how-ilo-works/results-based-management/evaluation-ilos-results-based-management-framework</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>https://www.ilo.org/resource/conference-paper/gb/352/ilo%E2%80%99s-strategic-plan-2026%E2%80%9329</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>https://www.ilo.org/publications/annual-report-2024</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/international-labour-organization/</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>https://x.com/ilo</t>
+        </is>
+      </c>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>1</v>
@@ -4853,25 +4913,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>International Labor Organization</t>
+          <t>International Monetary Fund</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>International Labor Organization (ILO)</t>
+          <t>International Monetary Fund (IMF)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>The ILO was founded in 1919, its Constitution forming part of the Treaty of Versailles. The ILO became the first specialised agency of the UN in 1946.</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
@@ -4881,17 +4937,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.ilo.org/</t>
+          <t>https://www.imf.org/</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Labour_Organization</t>
+          <t>https://en.wikipedia.org/wiki/International_Monetary_Fund</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.ilo.org/global/about-the-ilo/newsroom/news/lang--en/index.htm</t>
+          <t>https://www.imf.org/en/News</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -4902,7 +4958,7 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Geneva, Switzerland</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4920,27 +4976,27 @@
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://www.ilo.org/sites/default/files/2025-01/ILO_organizational%20chart_Jan-2025-EN.pdf</t>
+          <t>https://www.imf.org/en/About/Organization-Chart</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.ilo.org/about-ilo/how-ilo-works/organizational-structure-international-labour-office/financial-management/programme-and-budget</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>https://www.ilo.org/about-ilo/how-ilo-works/results-based-management/evaluation-ilos-results-based-management-framework</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>https://www.ilo.org/resource/conference-paper/gb/352/ilo%E2%80%99s-strategic-plan-2026%E2%80%9329</t>
+          <t>https://www.imf.org/en/Capacity-Development/strategy-policies</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>https://www.ilo.org/publications/annual-report-2024</t>
+          <t>https://www.imf.org/en/publications/search#sort=relevancy</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -4950,12 +5006,12 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/international-labour-organization/</t>
+          <t>https://www.linkedin.com/company/international-monetary-fund/</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>https://x.com/ilo</t>
+          <t>https://x.com/IMFNews</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr"/>
@@ -4966,21 +5022,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>International Monetary Fund</t>
+          <t>International Maritime Organization</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>International Monetary Fund (IMF)</t>
+          <t>International Maritime Organization (IMO)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>The IMO is responsible for the safety of life at sea, maritime security and the protection of the marine environment through prevention of sea pollution caused by ships.</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
@@ -4990,17 +5050,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.imf.org/</t>
+          <t>https://www.imo.org/</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/International_Monetary_Fund</t>
+          <t>https://en.wikipedia.org/wiki/International_Maritime_Organization</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/News</t>
+          <t>https://www.imo.org/en/MediaCentre/Pages/Default.aspx</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -5009,11 +5069,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Washington, DC, USA</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
           <t>Specialized Agencies</t>
@@ -5027,14 +5083,10 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>https://www.imf.org/en/About/Organization-Chart</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.imo.org/en/about/pages/structure.aspx</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -5044,12 +5096,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/Capacity-Development/strategy-policies</t>
+          <t>https://www.imo.org/en/about/strategy/pages/default.aspx</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>https://www.imf.org/en/publications/search#sort=relevancy</t>
+          <t>https://www.imo.org/en/OurWork/TechnicalCooperation/Pages/Default.aspx</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -5059,12 +5111,12 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/international-monetary-fund/</t>
+          <t>https://www.linkedin.com/company/international-maritime-organization/</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>https://x.com/IMFNews</t>
+          <t>https://x.com/IMOHQ</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr"/>
@@ -5075,47 +5127,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>INCB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>International Maritime Organization</t>
+          <t>International Narcotics Control Board</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>International Maritime Organization (IMO)</t>
+          <t>International Narcotics Control Board (INCB)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>The IMO is responsible for the safety of life at sea, maritime security and the protection of the marine environment through prevention of sea pollution caused by ships.</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.imo.org/</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/International_Maritime_Organization</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>https://www.imo.org/en/MediaCentre/Pages/Default.aspx</t>
-        </is>
-      </c>
+          <t>https://www.incb.org/</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -5125,56 +5159,30 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
+          <t>Economic and Social Council</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Other Bodies and Committees</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
-      <c r="T54" t="b">
-        <v>1</v>
-      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://www.imo.org/en/about/pages/structure.aspx</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>https://www.imo.org/en/about/strategy/pages/default.aspx</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>https://www.imo.org/en/OurWork/TechnicalCooperation/Pages/Default.aspx</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/international-maritime-organization/</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>https://x.com/IMOHQ</t>
-        </is>
-      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -14808,7 +14816,11 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://financing.desa.un.org/what-we-do/ECOSOC/tax-committee/tax-committee-home</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>

--- a/public/un-entities.xlsx
+++ b/public/un-entities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG176"/>
+  <dimension ref="A1:AH176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,11 @@
       <c r="AG1" t="inlineStr">
         <is>
           <t>is_on_pdf</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>review_needed</t>
         </is>
       </c>
     </row>
@@ -647,6 +652,7 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -750,6 +756,7 @@
       <c r="AG3" t="b">
         <v>1</v>
       </c>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -815,6 +822,7 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -876,6 +884,7 @@
       <c r="AG5" t="b">
         <v>1</v>
       </c>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -937,6 +946,7 @@
       <c r="AG6" t="b">
         <v>1</v>
       </c>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1031,6 +1041,9 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1093,6 +1106,7 @@
       <c r="AG8" t="b">
         <v>1</v>
       </c>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1154,6 +1168,7 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1215,6 +1230,7 @@
       <c r="AG10" t="b">
         <v>1</v>
       </c>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1276,6 +1292,7 @@
       <c r="AG11" t="b">
         <v>1</v>
       </c>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1337,6 +1354,7 @@
       <c r="AG12" t="b">
         <v>1</v>
       </c>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1398,6 +1416,7 @@
       <c r="AG13" t="b">
         <v>1</v>
       </c>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1459,6 +1478,7 @@
       <c r="AG14" t="b">
         <v>1</v>
       </c>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1561,6 +1581,7 @@
       <c r="AG15" t="b">
         <v>1</v>
       </c>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1622,6 +1643,7 @@
       <c r="AG16" t="b">
         <v>1</v>
       </c>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1713,6 +1735,9 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1816,6 +1841,7 @@
       <c r="AG18" t="b">
         <v>1</v>
       </c>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1919,6 +1945,7 @@
       <c r="AG19" t="b">
         <v>1</v>
       </c>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2024,6 +2051,7 @@
       <c r="AG20" t="b">
         <v>1</v>
       </c>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2119,6 +2147,7 @@
       <c r="AG21" t="b">
         <v>1</v>
       </c>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2214,6 +2243,7 @@
       <c r="AG22" t="b">
         <v>1</v>
       </c>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2317,6 +2347,7 @@
       <c r="AG23" t="b">
         <v>1</v>
       </c>
+      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2422,6 +2453,7 @@
       <c r="AG24" t="b">
         <v>1</v>
       </c>
+      <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2521,6 +2553,7 @@
       <c r="AG25" t="b">
         <v>1</v>
       </c>
+      <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2620,6 +2653,7 @@
       <c r="AG26" t="b">
         <v>1</v>
       </c>
+      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2726,6 +2760,7 @@
       <c r="AG27" t="b">
         <v>1</v>
       </c>
+      <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2828,6 +2863,7 @@
       <c r="AG28" t="b">
         <v>1</v>
       </c>
+      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2939,6 +2975,7 @@
       <c r="AG29" t="b">
         <v>1</v>
       </c>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3030,6 +3067,7 @@
       <c r="AG30" t="b">
         <v>1</v>
       </c>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3140,6 +3178,7 @@
       <c r="AG31" t="b">
         <v>1</v>
       </c>
+      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3250,6 +3289,7 @@
       <c r="AG32" t="b">
         <v>1</v>
       </c>
+      <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3345,6 +3385,9 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AH33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3460,6 +3503,7 @@
       <c r="AG34" t="b">
         <v>1</v>
       </c>
+      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3525,6 +3569,7 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3590,6 +3635,7 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3655,6 +3701,7 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3716,6 +3763,7 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3778,6 +3826,7 @@
       <c r="AG39" t="b">
         <v>1</v>
       </c>
+      <c r="AH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3843,6 +3892,7 @@
       <c r="AG40" t="b">
         <v>1</v>
       </c>
+      <c r="AH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3952,6 +4002,7 @@
       <c r="AG41" t="b">
         <v>1</v>
       </c>
+      <c r="AH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4063,6 +4114,7 @@
       <c r="AG42" t="b">
         <v>1</v>
       </c>
+      <c r="AH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4171,6 +4223,7 @@
       <c r="AG43" t="b">
         <v>1</v>
       </c>
+      <c r="AH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4266,6 +4319,7 @@
       <c r="AG44" t="b">
         <v>1</v>
       </c>
+      <c r="AH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4365,6 +4419,9 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AH45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4474,6 +4531,7 @@
       <c r="AG46" t="b">
         <v>1</v>
       </c>
+      <c r="AH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4573,6 +4631,7 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
+      <c r="AH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4668,6 +4727,7 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4731,6 +4791,7 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4796,6 +4857,7 @@
       <c r="AG50" t="b">
         <v>1</v>
       </c>
+      <c r="AH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4909,6 +4971,7 @@
       <c r="AG51" t="b">
         <v>1</v>
       </c>
+      <c r="AH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5018,6 +5081,7 @@
       <c r="AG52" t="b">
         <v>1</v>
       </c>
+      <c r="AH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5123,6 +5187,7 @@
       <c r="AG53" t="b">
         <v>1</v>
       </c>
+      <c r="AH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5184,6 +5249,7 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5293,6 +5359,7 @@
       <c r="AG55" t="b">
         <v>1</v>
       </c>
+      <c r="AH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5389,6 +5456,7 @@
       <c r="AG56" t="b">
         <v>1</v>
       </c>
+      <c r="AH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5450,6 +5518,7 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5557,6 +5626,7 @@
       <c r="AG58" t="b">
         <v>1</v>
       </c>
+      <c r="AH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5661,6 +5731,7 @@
       <c r="AG59" t="b">
         <v>1</v>
       </c>
+      <c r="AH59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5774,6 +5845,7 @@
       <c r="AG60" t="b">
         <v>1</v>
       </c>
+      <c r="AH60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5877,6 +5949,7 @@
       <c r="AG61" t="b">
         <v>1</v>
       </c>
+      <c r="AH61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5977,6 +6050,7 @@
       <c r="AG62" t="b">
         <v>1</v>
       </c>
+      <c r="AH62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6077,6 +6151,7 @@
       <c r="AG63" t="b">
         <v>1</v>
       </c>
+      <c r="AH63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6172,6 +6247,7 @@
       <c r="AG64" t="b">
         <v>1</v>
       </c>
+      <c r="AH64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6233,6 +6309,7 @@
       <c r="AG65" t="b">
         <v>1</v>
       </c>
+      <c r="AH65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6294,6 +6371,7 @@
       <c r="AG66" t="b">
         <v>1</v>
       </c>
+      <c r="AH66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6389,6 +6467,9 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AH67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6498,6 +6579,7 @@
       <c r="AG68" t="b">
         <v>1</v>
       </c>
+      <c r="AH68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6601,6 +6683,7 @@
       <c r="AG69" t="b">
         <v>1</v>
       </c>
+      <c r="AH69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6702,6 +6785,7 @@
       <c r="AG70" t="b">
         <v>1</v>
       </c>
+      <c r="AH70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6793,6 +6877,7 @@
       <c r="AG71" t="b">
         <v>1</v>
       </c>
+      <c r="AH71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6880,6 +6965,9 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AH72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6985,6 +7073,7 @@
       <c r="AG73" t="b">
         <v>1</v>
       </c>
+      <c r="AH73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7080,6 +7169,7 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AH74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7171,6 +7261,7 @@
       <c r="AG75" t="b">
         <v>1</v>
       </c>
+      <c r="AH75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7268,6 +7359,7 @@
       <c r="AG76" t="b">
         <v>1</v>
       </c>
+      <c r="AH76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7359,6 +7451,7 @@
       <c r="AG77" t="b">
         <v>1</v>
       </c>
+      <c r="AH77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7459,6 +7552,7 @@
       <c r="AG78" t="b">
         <v>1</v>
       </c>
+      <c r="AH78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7554,6 +7648,7 @@
       <c r="AG79" t="b">
         <v>1</v>
       </c>
+      <c r="AH79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7621,6 +7716,9 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
+      <c r="AH80" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7722,6 +7820,7 @@
       <c r="AG81" t="b">
         <v>1</v>
       </c>
+      <c r="AH81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7817,6 +7916,9 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
+      <c r="AH82" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7908,6 +8010,7 @@
       <c r="AG83" t="b">
         <v>1</v>
       </c>
+      <c r="AH83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7999,6 +8102,7 @@
       <c r="AG84" t="b">
         <v>1</v>
       </c>
+      <c r="AH84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8097,6 +8201,9 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -8155,6 +8262,7 @@
       <c r="AG86" t="b">
         <v>1</v>
       </c>
+      <c r="AH86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8218,6 +8326,9 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -8280,6 +8391,7 @@
       <c r="AG88" t="b">
         <v>1</v>
       </c>
+      <c r="AH88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8346,6 +8458,9 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -8408,6 +8523,9 @@
       <c r="AG90" t="b">
         <v>1</v>
       </c>
+      <c r="AH90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8508,6 +8626,7 @@
       <c r="AG91" t="b">
         <v>1</v>
       </c>
+      <c r="AH91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8599,6 +8718,7 @@
       <c r="AG92" t="b">
         <v>1</v>
       </c>
+      <c r="AH92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8690,6 +8810,7 @@
       <c r="AG93" t="b">
         <v>1</v>
       </c>
+      <c r="AH93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8781,6 +8902,7 @@
       <c r="AG94" t="b">
         <v>1</v>
       </c>
+      <c r="AH94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8867,6 +8989,9 @@
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -8933,6 +9058,7 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
+      <c r="AH96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8998,6 +9124,7 @@
       <c r="AG97" t="b">
         <v>0</v>
       </c>
+      <c r="AH97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9059,6 +9186,7 @@
       <c r="AG98" t="b">
         <v>1</v>
       </c>
+      <c r="AH98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9124,6 +9252,7 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
+      <c r="AH99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9189,6 +9318,7 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
+      <c r="AH100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9294,6 +9424,7 @@
       <c r="AG101" t="b">
         <v>1</v>
       </c>
+      <c r="AH101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9385,6 +9516,7 @@
       <c r="AG102" t="b">
         <v>1</v>
       </c>
+      <c r="AH102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9476,6 +9608,7 @@
       <c r="AG103" t="b">
         <v>1</v>
       </c>
+      <c r="AH103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9585,6 +9718,7 @@
       <c r="AG104" t="b">
         <v>1</v>
       </c>
+      <c r="AH104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9660,6 +9794,7 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
+      <c r="AH105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9755,6 +9890,7 @@
       <c r="AG106" t="b">
         <v>1</v>
       </c>
+      <c r="AH106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9875,6 +10011,7 @@
       <c r="AG107" t="b">
         <v>1</v>
       </c>
+      <c r="AH107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9978,6 +10115,7 @@
       <c r="AG108" t="b">
         <v>1</v>
       </c>
+      <c r="AH108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10073,6 +10211,7 @@
       <c r="AG109" t="b">
         <v>1</v>
       </c>
+      <c r="AH109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10163,6 +10302,9 @@
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -10225,6 +10367,9 @@
       <c r="AG111" t="b">
         <v>0</v>
       </c>
+      <c r="AH111" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10297,6 +10442,7 @@
       <c r="AG112" t="b">
         <v>1</v>
       </c>
+      <c r="AH112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10362,6 +10508,7 @@
       <c r="AG113" t="b">
         <v>1</v>
       </c>
+      <c r="AH113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10463,6 +10610,7 @@
       <c r="AG114" t="b">
         <v>1</v>
       </c>
+      <c r="AH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10528,6 +10676,7 @@
       <c r="AG115" t="b">
         <v>1</v>
       </c>
+      <c r="AH115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10585,6 +10734,9 @@
       <c r="AG116" t="b">
         <v>0</v>
       </c>
+      <c r="AH116" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10680,6 +10832,7 @@
       <c r="AG117" t="b">
         <v>1</v>
       </c>
+      <c r="AH117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10802,6 +10955,7 @@
       <c r="AG118" t="b">
         <v>1</v>
       </c>
+      <c r="AH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10867,6 +11021,7 @@
       <c r="AG119" t="b">
         <v>0</v>
       </c>
+      <c r="AH119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10962,6 +11117,7 @@
       <c r="AG120" t="b">
         <v>1</v>
       </c>
+      <c r="AH120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11032,6 +11188,7 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
+      <c r="AH121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11145,6 +11302,7 @@
       <c r="AG122" t="b">
         <v>1</v>
       </c>
+      <c r="AH122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11258,6 +11416,7 @@
       <c r="AG123" t="b">
         <v>1</v>
       </c>
+      <c r="AH123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11319,6 +11478,7 @@
       <c r="AG124" t="b">
         <v>1</v>
       </c>
+      <c r="AH124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11418,6 +11578,7 @@
       <c r="AG125" t="b">
         <v>1</v>
       </c>
+      <c r="AH125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11532,6 +11693,7 @@
       <c r="AG126" t="b">
         <v>1</v>
       </c>
+      <c r="AH126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11630,6 +11792,9 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AH127" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -11722,6 +11887,7 @@
       <c r="AG128" t="b">
         <v>1</v>
       </c>
+      <c r="AH128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11830,6 +11996,7 @@
       <c r="AG129" t="b">
         <v>1</v>
       </c>
+      <c r="AH129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11948,6 +12115,7 @@
       <c r="AG130" t="b">
         <v>1</v>
       </c>
+      <c r="AH130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12013,6 +12181,7 @@
       <c r="AG131" t="b">
         <v>0</v>
       </c>
+      <c r="AH131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12082,6 +12251,7 @@
       <c r="AG132" t="b">
         <v>1</v>
       </c>
+      <c r="AH132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12189,6 +12359,7 @@
       <c r="AG133" t="b">
         <v>1</v>
       </c>
+      <c r="AH133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12302,6 +12473,7 @@
       <c r="AG134" t="b">
         <v>1</v>
       </c>
+      <c r="AH134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12399,6 +12571,7 @@
       <c r="AG135" t="b">
         <v>1</v>
       </c>
+      <c r="AH135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12498,6 +12671,7 @@
       <c r="AG136" t="b">
         <v>1</v>
       </c>
+      <c r="AH136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12607,6 +12781,7 @@
       <c r="AG137" t="b">
         <v>1</v>
       </c>
+      <c r="AH137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12672,6 +12847,7 @@
       <c r="AG138" t="b">
         <v>0</v>
       </c>
+      <c r="AH138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12780,6 +12956,7 @@
       <c r="AG139" t="b">
         <v>1</v>
       </c>
+      <c r="AH139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12884,6 +13061,7 @@
       <c r="AG140" t="b">
         <v>1</v>
       </c>
+      <c r="AH140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12979,6 +13157,7 @@
       <c r="AG141" t="b">
         <v>1</v>
       </c>
+      <c r="AH141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13079,6 +13258,7 @@
       <c r="AG142" t="b">
         <v>1</v>
       </c>
+      <c r="AH142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13179,6 +13359,7 @@
       <c r="AG143" t="b">
         <v>1</v>
       </c>
+      <c r="AH143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13281,6 +13462,7 @@
       <c r="AG144" t="b">
         <v>1</v>
       </c>
+      <c r="AH144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13374,6 +13556,7 @@
       <c r="AG145" t="b">
         <v>1</v>
       </c>
+      <c r="AH145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13465,6 +13648,9 @@
       <c r="AG146" t="b">
         <v>1</v>
       </c>
+      <c r="AH146" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13558,6 +13744,7 @@
       <c r="AG147" t="b">
         <v>1</v>
       </c>
+      <c r="AH147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13626,6 +13813,7 @@
       <c r="AG148" t="b">
         <v>1</v>
       </c>
+      <c r="AH148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13734,6 +13922,7 @@
       <c r="AG149" t="b">
         <v>1</v>
       </c>
+      <c r="AH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13797,6 +13986,9 @@
       <c r="AG150" t="b">
         <v>1</v>
       </c>
+      <c r="AH150" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13890,6 +14082,7 @@
       <c r="AG151" t="b">
         <v>1</v>
       </c>
+      <c r="AH151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13994,6 +14187,7 @@
       <c r="AG152" t="b">
         <v>1</v>
       </c>
+      <c r="AH152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14094,6 +14288,7 @@
       <c r="AG153" t="b">
         <v>1</v>
       </c>
+      <c r="AH153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14165,6 +14360,7 @@
       <c r="AG154" t="b">
         <v>1</v>
       </c>
+      <c r="AH154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14275,6 +14471,7 @@
       <c r="AG155" t="b">
         <v>1</v>
       </c>
+      <c r="AH155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14371,6 +14568,9 @@
       <c r="AG156" t="b">
         <v>1</v>
       </c>
+      <c r="AH156" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14466,6 +14666,7 @@
       <c r="AG157" t="b">
         <v>1</v>
       </c>
+      <c r="AH157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14563,6 +14764,7 @@
       <c r="AG158" t="b">
         <v>1</v>
       </c>
+      <c r="AH158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14630,6 +14832,7 @@
       <c r="AG159" t="b">
         <v>1</v>
       </c>
+      <c r="AH159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14739,6 +14942,7 @@
       <c r="AG160" t="b">
         <v>1</v>
       </c>
+      <c r="AH160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14796,6 +15000,9 @@
       <c r="AG161" t="b">
         <v>0</v>
       </c>
+      <c r="AH161" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14857,6 +15064,7 @@
       <c r="AG162" t="b">
         <v>0</v>
       </c>
+      <c r="AH162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14952,6 +15160,7 @@
       <c r="AG163" t="b">
         <v>1</v>
       </c>
+      <c r="AH163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15052,6 +15261,9 @@
       <c r="AG164" t="b">
         <v>1</v>
       </c>
+      <c r="AH164" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15161,6 +15373,7 @@
       <c r="AG165" t="b">
         <v>1</v>
       </c>
+      <c r="AH165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15226,6 +15439,7 @@
       <c r="AG166" t="b">
         <v>0</v>
       </c>
+      <c r="AH166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15328,6 +15542,7 @@
       <c r="AG167" t="b">
         <v>1</v>
       </c>
+      <c r="AH167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15423,6 +15638,7 @@
       <c r="AG168" t="b">
         <v>1</v>
       </c>
+      <c r="AH168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15538,6 +15754,7 @@
       <c r="AG169" t="b">
         <v>1</v>
       </c>
+      <c r="AH169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15660,6 +15877,7 @@
       <c r="AG170" t="b">
         <v>1</v>
       </c>
+      <c r="AH170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15725,6 +15943,7 @@
       <c r="AG171" t="b">
         <v>0</v>
       </c>
+      <c r="AH171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15860,6 +16079,7 @@
       <c r="AG172" t="b">
         <v>1</v>
       </c>
+      <c r="AH172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -15975,6 +16195,7 @@
       <c r="AG173" t="b">
         <v>1</v>
       </c>
+      <c r="AH173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16090,6 +16311,7 @@
       <c r="AG174" t="b">
         <v>1</v>
       </c>
+      <c r="AH174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16202,6 +16424,7 @@
       <c r="AG175" t="b">
         <v>1</v>
       </c>
+      <c r="AH175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16321,6 +16544,7 @@
       <c r="AG176" t="b">
         <v>1</v>
       </c>
+      <c r="AH176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/un-entities.xlsx
+++ b/public/un-entities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH175"/>
+  <dimension ref="A1:AH170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8138,17 +8138,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PBSO</t>
+          <t>PBPSO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Peacebuilding Support Office</t>
+          <t>Peacebuilding and Peace Support Office</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Peacebuilding Support Office (PBSO)</t>
+          <t>Peacebuilding and Peace Support Office (PBPSO)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -8337,29 +8337,41 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SASG-SID</t>
+          <t>SESG-GL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement</t>
+          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Office of the Special Adviser to the Secretary-General on Solutions to Internal Displacement (SASG-SID)</t>
+          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region (SESG-GL)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>The Special Envoy leads, coordinates and assesses implementation of the PSC Framework, to address the root causes of conflict and end recurring violence in eastern DRC and the Great Lakes.</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/solutions-to-internal-displacement</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+          <t>https://ungreatlakes.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Special_Envoy_for_the_Great_Lakes_Region</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>https://ungreatlakes.unmissions.org/en/news</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -8369,71 +8381,92 @@
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
+      <c r="T89" t="b">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://ungreatlakes.unmissions.org/en/ungreatlakes/un-great-lakes-mandate
+</t>
+        </is>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
-      <c r="AC89" t="inlineStr"/>
-      <c r="AD89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>https://ungreatlakes.unmissions.org/secretary-generals-reports</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>1</v>
       </c>
-      <c r="AH89" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SESG-GL</t>
+          <t>SRSG-CAAC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region</t>
+          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Office of the Special Envoy of the Secretary-General for the Great Lakes Region (SESG-GL)</t>
+          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict (SRSG-CAAC)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>The Special Envoy leads, coordinates and assesses implementation of the PSC Framework, to address the root causes of conflict and end recurring violence in eastern DRC and the Great Lakes.</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://ungreatlakes.unmissions.org/</t>
+          <t>https://childrenandarmedconflict.un.org/</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Special_Envoy_for_the_Great_Lakes_Region</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_for_Children_and_Armed_Conflict</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://ungreatlakes.unmissions.org/en/news</t>
+          <t>https://childrenandarmedconflict.un.org/news/</t>
         </is>
       </c>
       <c r="J90" t="inlineStr"/>
@@ -8445,24 +8478,19 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
         </is>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="b">
         <v>0</v>
       </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://ungreatlakes.unmissions.org/en/ungreatlakes/un-great-lakes-mandate
-</t>
-        </is>
-      </c>
+      <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
@@ -8479,7 +8507,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>https://ungreatlakes.unmissions.org/secretary-generals-reports</t>
+          <t>https://childrenandarmedconflict.un.org/virtual-library/?wpv-document-type%5B%5D=annual-reports&amp;wpv_aux_current_post_id=2680&amp;wpv_aux_parent_post_id=2680&amp;wpv_view_count=110467</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -8502,17 +8530,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SRSG-CAAC</t>
+          <t>SRSG-SVC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict</t>
+          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General for Children and Armed Conflict (SRSG-CAAC)</t>
+          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict (SRSG-SVC)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -8520,17 +8548,17 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/</t>
+          <t>https://www.un.org/sexualviolenceinconflict/</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_for_Children_and_Armed_Conflict</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Sexual_Violence_in_Conflict</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/news/</t>
+          <t>https://www.un.org/sexualviolenceinconflict/news/</t>
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
@@ -8571,7 +8599,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>https://childrenandarmedconflict.un.org/virtual-library/?wpv-document-type%5B%5D=annual-reports&amp;wpv_aux_current_post_id=2680&amp;wpv_aux_parent_post_id=2680&amp;wpv_view_count=110467</t>
+          <t>https://www.un.org/sexualviolenceinconflict/digital-library/reports/</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -8594,17 +8622,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SRSG-SVC</t>
+          <t>SRSG-VAC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict</t>
+          <t>Office of the Special Representative of the Secretary-General on Violence against Children</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Sexual Violence in Conflict (SRSG-SVC)</t>
+          <t>Office of the Special Representative of the Secretary-General on Violence against Children (SRSG-VAC)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8612,17 +8640,17 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/</t>
+          <t>https://violenceagainstchildren.un.org/</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Sexual_Violence_in_Conflict</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Violence_against_Children</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/news/</t>
+          <t>https://violenceagainstchildren.un.org/news</t>
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
@@ -8663,7 +8691,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>https://www.un.org/sexualviolenceinconflict/digital-library/reports/</t>
+          <t>https://violenceagainstchildren.un.org/en/publications?search_api_fulltext=</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -8686,17 +8714,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SRSG-VAC</t>
+          <t>SWEO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Violence against Children</t>
+          <t>United Nations Sustainable Development Group System-Wide Evaluation Office</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Office of the Special Representative of the Secretary-General on Violence against Children (SRSG-VAC)</t>
+          <t>United Nations Sustainable Development Group System-Wide Evaluation Office (SWEO)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -8704,17 +8732,17 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/</t>
+          <t>https://www.un.org/system-wide-evaluation-office/</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_Special_Representative_of_the_Secretary-General_on_Violence_against_Children</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
@@ -8729,11 +8757,7 @@
           <t>Secretariat</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
-        </is>
-      </c>
+      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="b">
         <v>0</v>
@@ -8755,7 +8779,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>https://violenceagainstchildren.un.org/en/publications?search_api_fulltext=</t>
+          <t>https://www.un.org/system-wide-evaluation-office/en/document-library</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -8771,24 +8795,26 @@
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH93" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH93" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SWEO</t>
+          <t>Second Committee</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>United Nations Sustainable Development Group System-Wide Evaluation Office</t>
+          <t>Economic and Financial Committee</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>United Nations Sustainable Development Group System-Wide Evaluation Office (SWEO)</t>
+          <t>Economic and Financial Committee (Second Committee)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -8796,19 +8822,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.un.org/system-wide-evaluation-office/</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+          <t>https://www.un.org/en/ga/second/index.shtml</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
@@ -8818,67 +8836,51 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="b">
-        <v>0</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Main Committees</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>https://www.un.org/system-wide-evaluation-office/en/document-library</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
-      <c r="AH94" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Second Committee</t>
+          <t>Sixth Committee</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Economic and Financial Committee</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Economic and Financial Committee (Second Committee)</t>
+          <t>Legal (Sixth Committee)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -8886,7 +8888,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/second/index.shtml</t>
+          <t>https://www.un.org/en/ga/sixth/index.shtml</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -8934,17 +8936,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sixth Committee</t>
+          <t>StatCom</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>United Nations Statistical Commission</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Legal (Sixth Committee)</t>
+          <t>United Nations Statistical Commission (StatCom)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -8952,7 +8954,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/sixth/index.shtml</t>
+          <t>https://unstats.un.org/UNSDWebsite/statcom/</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -8966,19 +8968,15 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Main Committees</t>
-        </is>
-      </c>
+          <t>Functional Commissions</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
@@ -8993,24 +8991,24 @@
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>StatCom</t>
+          <t>TDB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>United Nations Statistical Commission</t>
+          <t>Trade and Development Board</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>United Nations Statistical Commission (StatCom)</t>
+          <t>Trade and Development Board (TDB)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -9018,7 +9016,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/UNSDWebsite/statcom/</t>
+          <t>https://unctad.org/about/trade-and-development-board</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -9032,15 +9030,19 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Functional Commissions</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr"/>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
@@ -9055,24 +9057,24 @@
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TDB</t>
+          <t>Third Committee</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Trade and Development Board</t>
+          <t>Social, Humanitarian &amp; Cultural Issues</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Trade and Development Board (TDB)</t>
+          <t>Social, Humanitarian &amp; Cultural Issues (Third Committee)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -9080,7 +9082,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://unctad.org/about/trade-and-development-board</t>
+          <t>https://www.un.org/en/ga/third/index.shtml</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -9104,7 +9106,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Boards</t>
+          <t>Main Committees</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9128,107 +9130,141 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Third Committee</t>
+          <t>UN Tourism</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Social, Humanitarian &amp; Cultural Issues</t>
+          <t>World Tourism Organization</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Social, Humanitarian &amp; Cultural Issues (Third Committee)</t>
+          <t>World Tourism Organization (UN Tourism)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.un.org/en/ga/third/index.shtml</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+          <t>https://www.untourism.int/</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_World_Tourism_Organization</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://www.unwto.org/news</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>Main Committees</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr"/>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="b">
+        <v>1</v>
+      </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>https://www.e-unwto.org/</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unwto/</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>https://x.com/UNWTO</t>
+        </is>
+      </c>
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UN Tourism</t>
+          <t>UN Youth</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>World Tourism Organization</t>
+          <t>United Nations Youth Office</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>World Tourism Organization (UN Tourism)</t>
+          <t>United Nations Youth Office (UN Youth)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.untourism.int/</t>
+          <t>https://www.un.org/youthaffairs/</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_World_Tourism_Organization</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Youth_Office</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.unwto.org/news</t>
+          <t>https://www.un.org/youthaffairs/news</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
@@ -9237,30 +9273,26 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Madrid, Spain</t>
-        </is>
-      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+        </is>
+      </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -9273,7 +9305,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>https://www.e-unwto.org/</t>
+          <t>https://www.un.org/youthaffairs/en/youth2030/progress-report</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -9283,14 +9315,10 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unwto/</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>https://x.com/UNWTO</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/un-youth-affairs</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>1</v>
@@ -9300,17 +9328,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UN Youth</t>
+          <t>UN-GGIM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>United Nations Youth Office</t>
+          <t>Committee of Experts on Global Geospatial Information Management</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>United Nations Youth Office (UN Youth)</t>
+          <t>Committee of Experts on Global Geospatial Information Management (UN-GGIM)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -9318,17 +9346,17 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/</t>
+          <t>https://ggim.un.org/</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Youth_Office</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Committee_of_Experts_on_Global_Geospatial_Information_Management</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
@@ -9340,12 +9368,12 @@
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Other Bodies and Committees</t>
         </is>
       </c>
       <c r="S101" t="inlineStr"/>
@@ -9369,7 +9397,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>https://www.un.org/youthaffairs/en/youth2030/progress-report</t>
+          <t>https://ggim.un.org/meetings/Sessions/</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -9379,7 +9407,7 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-youth-affairs</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr"/>
@@ -9392,35 +9420,45 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>UN-GGIM</t>
+          <t>UN-Habitat</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Committee of Experts on Global Geospatial Information Management</t>
+          <t>United Nations Human Settlements Programme</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Committee of Experts on Global Geospatial Information Management (UN-GGIM)</t>
+          <t>United Nations Human Settlements Programme (UN-Habitat)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>UN-Habitat works for a better urban future. Based in over 90 countries, we promote the development of socially and environmentally sustainable cities, towns &amp; communities. UN-Habitat strives for adequate shelter with better living standards for all.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- The secretariat of this entity is part of the United Nations Secretariat.
+</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://ggim.un.org/</t>
+          <t>https://unhabitat.org/</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Committee_of_Experts_on_Global_Geospatial_Information_Management</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Human_Settlements_Programme</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://unhabitat.org/news</t>
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
@@ -9429,20 +9467,24 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Nairobi, Kenya</t>
+        </is>
+      </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Other Bodies and Committees</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
@@ -9451,17 +9493,17 @@
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unhabitat.org/sites/default/files/2025/02/briefing_on_monitoring_of_strategic_plan_2026-2029.pdf</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unhabitat.org/about-us/our-strategy</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>https://ggim.un.org/meetings/Sessions/</t>
+          <t>https://unhabitat.org/knowledge/research-and-publications</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -9471,10 +9513,14 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/un-habitat/</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>https://x.com/UNHABITAT</t>
+        </is>
+      </c>
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>1</v>
@@ -9484,58 +9530,46 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UN-Habitat</t>
+          <t>UN-Habitat Assembly</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>United Nations Human Settlements Programme</t>
+          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>United Nations Human Settlements Programme (UN-Habitat)</t>
+          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UN-Habitat works for a better urban future. Based in over 90 countries, we promote the development of socially and environmentally sustainable cities, towns &amp; communities. UN-Habitat strives for adequate shelter with better living standards for all.</t>
+          <t>On 20 December 2018, the General Assembly of the United Nations in its resolution A/RES/73/239 decided to dissolve the Governing Council of the United Nations Human Settlements Programme and to replace it with a United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly). UN-Habitat Assembly is a universal body composed of the 193 member states of the United Nations and convenes every four years (A/RES/73/239).</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- The secretariat of this entity is part of the United Nations Secretariat.
+          <t xml:space="preserve">- Current governing body of UN-Habitat (since 2019)
+- Formerly: "Governing Council of the United Nations Human Settlements Programme" (1978–2019)
 </t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Human_Settlements_Programme</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/news</t>
-        </is>
-      </c>
+          <t>https://unhabitat.org/governance/un-habitat-assembly</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Nairobi, Kenya</t>
-        </is>
-      </c>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -9543,90 +9577,66 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="b">
-        <v>1</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Assemblies and Councils</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/sites/default/files/2025/02/briefing_on_monitoring_of_strategic_plan_2026-2029.pdf</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/about-us/our-strategy</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>https://unhabitat.org/knowledge/research-and-publications</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/un-habitat/</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>https://x.com/UNHABITAT</t>
-        </is>
-      </c>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UN-Habitat Assembly</t>
+          <t>UN-OHRLLS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme</t>
+          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly)</t>
+          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States (UN-OHRLLS)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>On 20 December 2018, the General Assembly of the United Nations in its resolution A/RES/73/239 decided to dissolve the Governing Council of the United Nations Human Settlements Programme and to replace it with a United Nations Habitat Assembly of the United Nations Human Settlements Programme (UN-Habitat Assembly). UN-Habitat Assembly is a universal body composed of the 193 member states of the United Nations and convenes every four years (A/RES/73/239).</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Current governing body of UN-Habitat (since 2019)
-- Formerly: "Governing Council of the United Nations Human Settlements Programme" (1978–2019)
-</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://unhabitat.org/governance/un-habitat-assembly</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+          <t>https://www.un.org/ohrlls/</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_of_the_High_Representative_for_the_Least_Developed_Countries,_Landlocked_Developing_Countries_and_Small_Island_Developing_States</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://www.un.org/ohrlls/news</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -9636,125 +9646,172 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>Assemblies and Councils</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr"/>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="b">
+        <v>0</v>
+      </c>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
-      <c r="AB104" t="inlineStr"/>
-      <c r="AC104" t="inlineStr"/>
-      <c r="AD104" t="inlineStr"/>
-      <c r="AE104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>https://open.unwomen.org/en/global-results/overview</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>https://www.un.org/ohrlls/sites/www.un.org.ohrlls/files/dpoa_roadmap_2024_draft.pdf</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>https://www.un.org/ohrlls/content/resources</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/un-ohrlls/</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>https://x.com/UNOHRLLS</t>
+        </is>
+      </c>
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UN-OHRLLS</t>
+          <t>UN-Women</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States</t>
+          <t>United Nations Entity for Gender Equality and the Empowerment of Women</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Office of the High Representative for the Least Developed Countries, Landlocked Developing Countries and Small Island Developing States (UN-OHRLLS)</t>
+          <t>United Nations Entity for Gender Equality and the Empowerment of Women (UN-Women)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>UN Women is the global champion for gender equality, working to develop and uphold standards and create an environment in which every woman and girl can exercise her human rights and live up to her full potential. We are trusted partners for advocates and decision-makers from all walks of life, and a leader in the effort to achieve gender equality.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/</t>
+          <t>https://www.unwomen.org/</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_of_the_High_Representative_for_the_Least_Developed_Countries,_Landlocked_Developing_Countries_and_Small_Island_Developing_States</t>
+          <t>https://en.wikipedia.org/wiki/UN_Women</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/news</t>
+          <t>https://www.unwomen.org/en/news</t>
         </is>
       </c>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://data.unwomen.org/</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>New York City, USA</t>
+        </is>
+      </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Other Entities</t>
         </is>
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>https://www.unwomen.org/sites/default/files/2025-08/unw_org_chart_internal_20250806.pdf</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>https://www.unwomen.org/en/executive-board/strategic-plan-review/financial-resources</t>
+        </is>
+      </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>https://open.unwomen.org/en/global-results/overview</t>
+          <t>https://www.unwomen.org/sites/default/files/2025-10/un-women-strategic-plan-2026-2029-integrated-results-and-resources-framework-en.pdf</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/sites/www.un.org.ohrlls/files/dpoa_roadmap_2024_draft.pdf</t>
+          <t>https://www.unwomen.org/sites/default/files/2022-05/UN%20Women%20SP%20IRRF%202022-2025.pdf</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>https://www.un.org/ohrlls/content/resources</t>
+          <t>https://www.unwomen.org/en/digital-library/annual-report</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://data.unwomen.org/data-portal</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-ohrlls/</t>
+          <t>https://www.linkedin.com/company/un-women/</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>https://x.com/UNOHRLLS</t>
+          <t>https://x.com/UN_Women</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr"/>
@@ -9766,118 +9823,101 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UN-Women</t>
+          <t>UNAIDS PCB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>United Nations Entity for Gender Equality and the Empowerment of Women</t>
+          <t>Joint United Nations Programme on HIV/AIDS Programme Coordinating Board</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>United Nations Entity for Gender Equality and the Empowerment of Women (UN-Women)</t>
+          <t>Joint United Nations Programme on HIV/AIDS Programme Coordinating Board (UNAIDS PCB)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UN Women is the global champion for gender equality, working to develop and uphold standards and create an environment in which every woman and girl can exercise her human rights and live up to her full potential. We are trusted partners for advocates and decision-makers from all walks of life, and a leader in the effort to achieve gender equality.</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+          <t>UNAIDS brings together the efforts and resources of 10 UN system organizations to help prevent new HIV infections, care for people living with HIV and mitigate the impact of the epidemic.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/</t>
+          <t>https://www.unaids.org/en</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UN_Women</t>
+          <t>https://en.wikipedia.org/wiki/Joint_United_Nations_Programme_on_HIV/AIDS</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/news</t>
+          <t>https://www.unaids.org/en/news</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>https://data.unwomen.org/</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>New York City, USA</t>
+          <t>Geneva, Switzerland</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Other Bodies and Committees</t>
         </is>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>https://www.unwomen.org/sites/default/files/2025-08/unw_org_chart_internal_20250806.pdf</t>
-        </is>
-      </c>
+      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/executive-board/strategic-plan-review/financial-resources</t>
+          <t>https://www.unaids.org/en/topic/resources</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/sites/default/files/2025-10/un-women-strategic-plan-2026-2029-integrated-results-and-resources-framework-en.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/sites/default/files/2022-05/UN%20Women%20SP%20IRRF%202022-2025.pdf</t>
+          <t>https://www.unaids.org/sites/default/files/media_asset/global-AIDS-strategy-2021-2026_en.pdf</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>https://www.unwomen.org/en/digital-library/annual-report</t>
+          <t>https://www.unaids.org/en/topics/resources/publications</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>https://data.unwomen.org/data-portal</t>
+          <t>https://open.unaids.org/</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-women/</t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>https://x.com/UN_Women</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/unaids/</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>1</v>
@@ -9887,39 +9927,39 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UNAIDS</t>
+          <t>UNAMA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Joint United Nations Programme on HIV/AIDS</t>
+          <t>United Nations Assistance Mission in Afghanistan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Joint United Nations Programme on HIV/AIDS (UNAIDS)</t>
+          <t>United Nations Assistance Mission in Afghanistan (UNAMA)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>UNAIDS brings together the efforts and resources of 10 UN system organizations to help prevent new HIV infections, care for people living with HIV and mitigate the impact of the epidemic.</t>
+          <t>UNAMA’s mission is to support the people and institutions of Afghanistan in achieving peace and stability, in line with the rights and obligations enshrined in the Afghan constitution.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en</t>
+          <t>https://unama.unmissions.org/</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Joint_United_Nations_Programme_on_HIV/AIDS</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Assistance_Mission_in_Afghanistan</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en/news</t>
+          <t>https://unama.unmissions.org/news</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -9928,19 +9968,15 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Other Bodies and Committees</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S107" t="inlineStr"/>
@@ -9951,11 +9987,7 @@
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>https://www.unaids.org/en/topic/resources</t>
-        </is>
-      </c>
+      <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -9963,22 +9995,22 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/sites/default/files/media_asset/global-AIDS-strategy-2021-2026_en.pdf</t>
+          <t>https://unama.unmissions.org/sites/default/files/unsf_afghanistan_formatted_20230629.pdf</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>https://www.unaids.org/en/topics/resources/publications</t>
+          <t>https://unama.unmissions.org/secretary-general-reports</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>https://open.unaids.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unaids/</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr"/>
@@ -9991,41 +10023,34 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UNAMA</t>
+          <t>UNCDF</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United Nations Assistance Mission in Afghanistan</t>
+          <t>United Nations Capital Development Fund</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>United Nations Assistance Mission in Afghanistan (UNAMA)</t>
+          <t>United Nations Capital Development Fund (UNCDF)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UNAMA’s mission is to support the people and institutions of Afghanistan in achieving peace and stability, in line with the rights and obligations enshrined in the Afghan constitution.</t>
+          <t>The United Nations Capital Development Fund's mission is to contribute to job creation, sustained economic growth and equitable prosperity in almost 80 developing countries and nearly all LDCs.
+We do so by crowding in capital through the deployment of risk-absorbing financial instruments, mechanisms and structuring advisory. In partnership with UN entities and development partners, UNCDF operates with speed and agility to deliver scalable, blended finance solutions to drive systemic change and pave the way for commercial finance and scale up by development finance institutions and multilateral development banks.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Assistance_Mission_in_Afghanistan</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>https://unama.unmissions.org/news</t>
-        </is>
-      </c>
+          <t>https://www.uncdf.org/</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
@@ -10035,12 +10060,12 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S108" t="inlineStr"/>
@@ -10052,31 +10077,15 @@
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="Z108" t="inlineStr"/>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>https://unama.unmissions.org/sites/default/files/unsf_afghanistan_formatted_20230629.pdf</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>https://unama.unmissions.org/secretary-general-reports</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+          <t>https://www.uncdf.org/article/3208/making-finance-work-for-inclusion-uncdf-presents-new-four-year-strategic-framework-to-its-board</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
@@ -10087,41 +10096,29 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UNAOC</t>
+          <t>UNCITRAL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>United Nations Alliance of Civilizations</t>
+          <t>United Nations Commission on International Trade Law</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>United Nations Alliance of Civilizations (UNAOC)</t>
+          <t>United Nations Commission on International Trade Law (UNCITRAL)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>UNAOC aims to bridge divides, and promote harmony among the nations, all with a view toward preventing conflict and promoting social cohesion.</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.unaoc.org/</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Alliance_of_Civilizations</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>https://www.unaoc.org/category/news/</t>
-        </is>
-      </c>
+          <t>https://uncitral.un.org/</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
@@ -10131,79 +10128,81 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="b">
-        <v>0</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>https://www.unaoc.org/wp-content/uploads/UNAOC-Action-Plan-POA-2024-2026-250203_web.pdf</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>https://www.unaoc.org/resource-type/unaoc-annual-reports/</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-alliance-of-civilizations/</t>
-        </is>
-      </c>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH109" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UNCCD</t>
+          <t>UNCTAD</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>United Nations Convention to Combat Desertification</t>
+          <t>United Nations Conference on Trade and Development</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>United Nations Convention to Combat Desertification (UNCCD)</t>
+          <t>United Nations Conference on Trade and Development (UNCTAD)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>UNCTAD supports developing countries to access the benefits of a globalized economy more fairly and effectively and helps equip them to deal with the potential drawbacks of greater economic integration.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- The secretariat of this entity is part of the United Nations Secretariat.
+</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.unccd.int/</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+          <t>https://unctad.org/</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Conference_on_Trade_and_Development</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://unctad.org/news</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
@@ -10213,62 +10212,77 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Other Entities</t>
+        </is>
+      </c>
       <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
+      <c r="T110" t="b">
+        <v>1</v>
+      </c>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>https://www.unccd.int/convention/governance/strategic-framework-2018-2030</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr"/>
-      <c r="AC110" t="inlineStr"/>
-      <c r="AD110" t="inlineStr"/>
+          <t>https://unctad.org/dmfas/our_Strategic_Plan</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>https://unctad.org/publications-search?Operator=and&amp;keys=annual</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unctad/</t>
+        </is>
+      </c>
       <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH110" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UNCDF</t>
+          <t>UNDC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>United Nations Capital Development Fund</t>
+          <t>Disarmament Commission</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>United Nations Capital Development Fund (UNCDF)</t>
+          <t>Disarmament Commission (UNDC)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>The United Nations Capital Development Fund's mission is to contribute to job creation, sustained economic growth and equitable prosperity in almost 80 developing countries and nearly all LDCs.
-We do so by crowding in capital through the deployment of risk-absorbing financial instruments, mechanisms and structuring advisory. In partnership with UN entities and development partners, UNCDF operates with speed and agility to deliver scalable, blended finance solutions to drive systemic change and pave the way for commercial finance and scale up by development finance institutions and multilateral development banks.</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.uncdf.org/</t>
+          <t>https://disarmament.unoda.org/en/united-nations-disarmament-commission</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -10287,24 +10301,22 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="b">
-        <v>0</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>https://www.uncdf.org/article/3208/making-finance-work-for-inclusion-uncdf-presents-new-four-year-strategic-framework-to-its-board</t>
-        </is>
-      </c>
+      <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr"/>
       <c r="AD111" t="inlineStr"/>
@@ -10318,29 +10330,41 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UNCITRAL</t>
+          <t>UNDOF</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>United Nations Commission on International Trade Law</t>
+          <t>United Nations Disengagement Observer Force</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>United Nations Commission on International Trade Law (UNCITRAL)</t>
+          <t>United Nations Disengagement Observer Force (UNDOF)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>The UNDOF assists in maintaining the ceasefire between Israel and Syria, supervising the disengagement of Israeli and Syrian forces; as well as the areas of separation and limitation, as provided in the May 1974 Agreement on Disengagement.</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://uncitral.un.org/</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+          <t>https://undof.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Disengagement_Observer_Force</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://undof.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
@@ -10350,30 +10374,48 @@
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr"/>
+          <t>Peacekeeping Operations</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="b">
+        <v>0</v>
+      </c>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr"/>
-      <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>https://undof.unmissions.org/reports-statements</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
@@ -10384,54 +10426,63 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UNCTAD</t>
+          <t>UNDP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>United Nations Conference on Trade and Development</t>
+          <t>United Nations Development Programme</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>United Nations Conference on Trade and Development (UNCTAD)</t>
+          <t>United Nations Development Programme (UNDP)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UNCTAD supports developing countries to access the benefits of a globalized economy more fairly and effectively and helps equip them to deal with the potential drawbacks of greater economic integration.</t>
+          <t>The UNDP helps build inclusive, sustainable and resilient societies and provides expert advice, training and financial support. Special attention is paid to the needs of the Least Developed Countries and countries emerging from conflict.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- The secretariat of this entity is part of the United Nations Secretariat.
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
 </t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://unctad.org/</t>
+          <t>https://www.undp.org/</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Conference_on_Trade_and_Development</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Programme</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://unctad.org/news</t>
+          <t>https://www.undp.org/news</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
+      <c r="N113" t="b">
+        <v>1</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>https://jobs.undp.org/</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>New York City, USA</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr">
         <is>
           <t>General Assembly</t>
@@ -10439,7 +10490,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S113" t="inlineStr"/>
@@ -10449,35 +10500,47 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/organizational-chart</t>
+        </is>
+      </c>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://rolhr.undp.org/annualreport/2023/results-framework.html</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>https://unctad.org/dmfas/our_Strategic_Plan</t>
+          <t>https://strategicplan.undp.org/</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>https://unctad.org/publications-search?Operator=and&amp;keys=annual</t>
+          <t>https://annualreport.undp.org/</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://open.undp.org/</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unctad/</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr"/>
-      <c r="AF113" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/united-nations-development-programme/</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>https://x.com/UNDP</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/undp/</t>
+        </is>
+      </c>
       <c r="AG113" t="b">
         <v>1</v>
       </c>
@@ -10486,17 +10549,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UNDC</t>
+          <t>UNDP UNFPA UNOPS EB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Disarmament Commission</t>
+          <t>Executive Board of UNDP, UNFPA and UNOPS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Disarmament Commission (UNDC)</t>
+          <t>Executive Board of UNDP, UNFPA and UNOPS (UNDP UNFPA UNOPS EB)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -10504,7 +10567,7 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://disarmament.unoda.org/en/united-nations-disarmament-commission</t>
+          <t>https://www.unfpa.org/executive-board</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -10528,7 +10591,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Commissions</t>
+          <t>Boards</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -10545,36 +10608,48 @@
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UNDEF</t>
+          <t>UNDRR</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>United Nations Democracy Fund</t>
+          <t>United Nations Office for Disaster Risk Reduction</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>United Nations Democracy Fund (UNDEF)</t>
+          <t>United Nations Office for Disaster Risk Reduction (UNDRR)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>UNDRR brings governments, partners, and communities together to reduce disaster risk and losses and to ensure a safer, sustainable future.</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.un.org/democracyfund/</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+          <t>https://www.undrr.org/</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Disaster_Risk_Reduction</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://www.undrr.org/news</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
@@ -10589,64 +10664,81 @@
       </c>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
+      <c r="T115" t="b">
+        <v>0</v>
+      </c>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
-      <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
-      <c r="AB115" t="inlineStr"/>
-      <c r="AC115" t="inlineStr"/>
-      <c r="AD115" t="inlineStr"/>
-      <c r="AE115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>https://www.undrr.org/media/49267/download</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>https://www.undrr.org/publications?text=Annual%20Report</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/united-nations-office-for-disaster-risk-reduction-undrr/</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>https://x.com/UNDRR</t>
+        </is>
+      </c>
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UNDOF</t>
+          <t>UNEA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force</t>
+          <t>United Nations Environment Assembly</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force (UNDOF)</t>
+          <t>United Nations Environment Assembly (UNEA)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>The UNDOF assists in maintaining the ceasefire between Israel and Syria, supervising the disengagement of Israeli and Syrian forces; as well as the areas of separation and limitation, as provided in the May 1974 Agreement on Disengagement.</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Also referred to as "United Nations Environment Assembly of the United Nations Environment Programme (UNEP)"
+</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://undof.unmissions.org/</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Disengagement_Observer_Force</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>https://undof.unmissions.org/news</t>
-        </is>
-      </c>
+          <t>https://www.unep.org/environmentassembly/</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
@@ -10656,113 +10748,90 @@
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Peacekeeping Operations</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="b">
-        <v>0</v>
-      </c>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Assemblies and Councils</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>https://undof.unmissions.org/reports-statements</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>UNEP</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>United Nations Development Programme</t>
+          <t>United Nations Environment Programme</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>United Nations Development Programme (UNDP)</t>
+          <t>United Nations Environment Programme (UNEP)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>The UNDP helps build inclusive, sustainable and resilient societies and provides expert advice, training and financial support. Special attention is paid to the needs of the Least Developed Countries and countries emerging from conflict.</t>
+          <t>The global authority for the environment with programmes focusing on climate, nature, pollution, sustainable development and more.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
           <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
+- The secretariat of this entity is part of the United Nations Secretariat.
 </t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.undp.org/</t>
+          <t>https://www.unep.org/</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Development_Programme</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Environment_Programme</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://www.undp.org/news</t>
+          <t>https://www.unep.org/news</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="b">
-        <v>1</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>https://jobs.undp.org/</t>
-        </is>
-      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>New York City, USA</t>
+          <t>Nairobi, Kenya</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -10782,47 +10851,43 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/organizational-chart</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>https://www.unep.org/resources/programme-work-and-budget</t>
+        </is>
+      </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>https://rolhr.undp.org/annualreport/2023/results-framework.html</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>https://strategicplan.undp.org/</t>
+          <t>https://wedocs.unep.org/bitstream/handle/20.500.11822/42683/medium_term_strategy_2022.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>https://annualreport.undp.org/</t>
+          <t>https://www.unep.org/annualreport/2021/index.php</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>https://open.undp.org/</t>
+          <t>https://open.unep.org/</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-development-programme/</t>
+          <t>https://www.linkedin.com/company/un-environment-programme/</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>https://x.com/UNDP</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/undp/</t>
-        </is>
-      </c>
+          <t>https://x.com/UNEP</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>1</v>
       </c>
@@ -10831,107 +10896,143 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UNDP UNFPA UNOPS EB</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Executive Board of UNDP, UNFPA and UNOPS</t>
+          <t>United Nations Educational, Scientific and Cultural Organization</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Executive Board of UNDP, UNFPA and UNOPS (UNDP UNFPA UNOPS EB)</t>
+          <t>United Nations Educational, Scientific and Cultural Organization (UNESCO)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>UNESCO contributes to peace and security by promoting collaboration among nations through education, science and culture.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/executive-board</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+          <t>https://www.unesco.org/</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/UNESCO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://www.unesco.org/en/news</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr"/>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="b">
+        <v>1</v>
+      </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
-      <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
-      <c r="AB118" t="inlineStr"/>
-      <c r="AC118" t="inlineStr"/>
-      <c r="AD118" t="inlineStr"/>
-      <c r="AE118" t="inlineStr"/>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>https://unesdoc.unesco.org/archives/organization-charts</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>https://www.unesco.org/en/budget-strategy</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>https://unesdoc.unesco.org/ark:/48223/pf0000378083_eng</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>https://www.unesco.org/en/budget-strategy</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>https://core.unesco.org/</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unesco/</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>https://x.com/UNESCO</t>
+        </is>
+      </c>
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UNDRR</t>
+          <t>UNFF</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>United Nations Office for Disaster Risk Reduction</t>
+          <t>United Nations Forum on Forests</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>United Nations Office for Disaster Risk Reduction (UNDRR)</t>
+          <t>United Nations Forum on Forests (UNFF)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>UNDRR brings governments, partners, and communities together to reduce disaster risk and losses and to ensure a safer, sustainable future.</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.undrr.org/</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Disaster_Risk_Reduction</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>https://www.undrr.org/news</t>
-        </is>
-      </c>
+          <t>https://www.un.org/esa/forests/</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
@@ -10941,49 +11042,27 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr"/>
+          <t>Economic and Social Council</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Functional Commissions</t>
+        </is>
+      </c>
       <c r="S119" t="inlineStr"/>
-      <c r="T119" t="b">
-        <v>0</v>
-      </c>
+      <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>https://www.undrr.org/media/49267/download</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>https://www.undrr.org/publications?text=Annual%20Report</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-office-for-disaster-risk-reduction-undrr/</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>https://x.com/UNDRR</t>
-        </is>
-      </c>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>1</v>
@@ -10993,34 +11072,41 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UNEA</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>United Nations Environment Assembly</t>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>United Nations Environment Assembly (UNEA)</t>
+          <t>United Nations Peacekeeping Force in Cyprus (UNFICYP)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Also referred to as "United Nations Environment Assembly of the United Nations Environment Programme (UNEP)"
-</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>UNFICYP has remained on the island to supervise ceasefire lines, maintain a buffer zone, undertake humanitarian activities and support the good offices mission of the Secretary-General.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.unep.org/environmentassembly/</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+          <t>https://unficyp.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Peacekeeping_Force_in_Cyprus</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://unficyp.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
@@ -11030,90 +11116,113 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>Assemblies and Councils</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr"/>
+          <t>Peacekeeping Operations</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="b">
+        <v>0</v>
+      </c>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
-      <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr"/>
-      <c r="AC120" t="inlineStr"/>
-      <c r="AD120" t="inlineStr"/>
-      <c r="AE120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>https://www.securitycouncilreport.org/un-documents/cyprus/</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>https://x.com/UN_CYPRUS</t>
+        </is>
+      </c>
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UNEP</t>
+          <t>UNFPA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>United Nations Environment Programme</t>
+          <t>United Nations Population Fund</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>United Nations Environment Programme (UNEP)</t>
+          <t>United Nations Population Fund (UNFPA)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>The global authority for the environment with programmes focusing on climate, nature, pollution, sustainable development and more.</t>
+          <t>UNFPA is the United Nations sexual and reproductive health agency. Our mission is to deliver a world where every pregnancy is wanted, every childbirth is safe and every young person's potential is fulfilled.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB)
-- The secretariat of this entity is part of the United Nations Secretariat.
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
 </t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.unep.org/</t>
+          <t>https://www.unfpa.org/</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Environment_Programme</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Population_Fund</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://www.unep.org/news</t>
+          <t>https://www.unfpa.org/news</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" t="b">
+        <v>1</v>
+      </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nairobi, Kenya</t>
+          <t>New York City, USA</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -11136,37 +11245,37 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>https://www.unep.org/resources/programme-work-and-budget</t>
+          <t>https://www.unfpa.org/finance-and-budget-policies</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unfpa.org/results-based-management-unfpa</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>https://wedocs.unep.org/bitstream/handle/20.500.11822/42683/medium_term_strategy_2022.pdf?sequence=1&amp;isAllowed=y</t>
+          <t>https://www.unfpa.org/sites/default/files/board-documents/DP.FPA_.2025.9%20-%20Strategic%20Plan%202026-2029%20-%20Annex%201%20-%20IRRF%20-%20FINAL%20-%2018Jul25.pdf</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>https://www.unep.org/annualreport/2021/index.php</t>
+          <t>https://www.unfpa.org/annual-report</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>https://open.unep.org/</t>
+          <t>https://www.unfpa.org/data/transparency-portal</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-environment-programme/</t>
+          <t>https://www.linkedin.com/company/united-nations-population-fund-unfpa/</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>https://x.com/UNEP</t>
+          <t>https://x.com/UNFPA</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr"/>
@@ -11178,81 +11287,71 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>UNGC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Nations Educational, Scientific and Cultural Organization</t>
+          <t>United Nations Global Compact</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>United Nations Educational, Scientific and Cultural Organization (UNESCO)</t>
+          <t>United Nations Global Compact (UNGC)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UNESCO contributes to peace and security by promoting collaboration among nations through education, science and culture.</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+          <t>The United Nations Global Compact is a voluntary initiative based on CEO commitments to implement universal sustainability principles and to undertake partnerships in support of UN goals.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/</t>
+          <t>https://unglobalcompact.org/</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UNESCO</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Global_Compact</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/news</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
+          <t>https://unglobalcompact.org/news</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Paris, France</t>
-        </is>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>https://unesdoc.unesco.org/archives/organization-charts</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>https://www.unesco.org/en/budget-strategy</t>
-        </is>
-      </c>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -11260,49 +11359,47 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>https://unesdoc.unesco.org/ark:/48223/pf0000378083_eng</t>
+          <t>https://unglobalcompact.org/what-is-gc/strategy</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/budget-strategy</t>
+          <t>https://unglobalcompact.org/library</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>https://core.unesco.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unesco/</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>https://x.com/UNESCO</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/united-nations-global-compact/</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH122" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH122" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UNFF</t>
+          <t>UNGEGN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>United Nations Forum on Forests</t>
+          <t>United Nations Group of Experts on Geographical Names</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>United Nations Forum on Forests (UNFF)</t>
+          <t>United Nations Group of Experts on Geographical Names (UNGEGN)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -11310,11 +11407,19 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.un.org/esa/forests/</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+          <t>https://unstats.un.org/unsd/ungegn</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Group_of_Experts_on_Geographical_Names</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
@@ -11329,21 +11434,43 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Functional Commissions</t>
+          <t>Other Bodies and Committees</t>
         </is>
       </c>
       <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
+      <c r="T123" t="b">
+        <v>0</v>
+      </c>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
-      <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
-      <c r="AB123" t="inlineStr"/>
-      <c r="AC123" t="inlineStr"/>
-      <c r="AD123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>https://unstats.un.org/unsd/ungegn/sessions/2nd_session_2021/documents/UNGEGN_Strategic_Plan_final_5May2021.pdf</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>https://unstats.un.org/unsd/ungegn/sessions/</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
@@ -11354,39 +11481,44 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNFICYP</t>
+          <t>UNHCR</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>United Nations Peacekeeping Force in Cyprus</t>
+          <t>Office of the United Nations High Commissioner for Refugees</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>United Nations Peacekeeping Force in Cyprus (UNFICYP)</t>
+          <t>Office of the United Nations High Commissioner for Refugees (UNHCR)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UNFICYP has remained on the island to supervise ceasefire lines, maintain a buffer zone, undertake humanitarian activities and support the good offices mission of the Secretary-General.</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+          <t>The work of the Office of the UNHCR is humanitarian and non-political. Its principal functions are to provide international protection to refugees and other persons of concern, and to seek durable solutions for them.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://unficyp.unmissions.org/</t>
+          <t>https://www.unhcr.org/</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Peacekeeping_Force_in_Cyprus</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_High_Commissioner_for_Refugees</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://unficyp.unmissions.org/news</t>
+          <t>https://www.unhcr.org/news</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -11395,56 +11527,60 @@
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland</t>
+        </is>
+      </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Peacekeeping Operations</t>
+          <t>Other Entities</t>
         </is>
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>https://www.unhcr.org/us/budget-and-expenditure</t>
+        </is>
+      </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unhcr.org/media/unhcrs-results-areas</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022-2026.pdfhttps://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022--2026.pdf</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>https://www.securitycouncilreport.org/un-documents/cyprus/</t>
+          <t>https://www.unhcr.org/cgi-bin/texis/vtx/search?page=&amp;comid=3b4f07fd4&amp;cid=49aea93a20&amp;scid=49aea93a16&amp;keywords=UNHCR%20Annual%20Reports%20General%20Assembly</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://reporting.unhcr.org/</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>https://x.com/UN_CYPRUS</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/unhcr/</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>1</v>
@@ -11454,23 +11590,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UNFPA</t>
+          <t>UNICEF</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>United Nations Population Fund</t>
+          <t>United Nations Children's Fund</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>United Nations Population Fund (UNFPA)</t>
+          <t>United Nations Children's Fund (UNICEF)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UNFPA is the United Nations sexual and reproductive health agency. Our mission is to deliver a world where every pregnancy is wanted, every childbirth is safe and every young person's potential is fulfilled.</t>
+          <t>UNICEF works in the world’s toughest places to reach the most disadvantaged children and to protect the rights of every child, everywhere.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -11481,17 +11617,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/</t>
+          <t>https://www.unicef.org/</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Population_Fund</t>
+          <t>https://en.wikipedia.org/wiki/UNICEF</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/news</t>
+          <t>https://www.unicef.org/press-releases</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -11524,40 +11660,44 @@
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>https://www.unicef.org/executiveboard/media/21691/file/Integrated-Budget-MTR-Annexes.pdf</t>
+        </is>
+      </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/finance-and-budget-policies</t>
+          <t>https://www.unicef.org/executiveboard/documents/unicef-integrated-budget-2026-2029-srs-2025</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/results-based-management-unfpa</t>
+          <t>https://www.unicef.org/executiveboard/media/32061/file/2025-29-Add1-SP-2026-2029-IRRF-EN-2025-07-21.pdf</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/sites/default/files/board-documents/DP.FPA_.2025.9%20-%20Strategic%20Plan%202026-2029%20-%20Annex%201%20-%20IRRF%20-%20FINAL%20-%2018Jul25.pdf</t>
+          <t>https://www.unicef.org/executiveboard/documents/unicef-strategic-plan-2026-2029-draft-review-as-2025</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/annual-report</t>
+          <t>https://www.unicef.org/topics/annual-report</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>https://www.unfpa.org/data/transparency-portal</t>
+          <t>https://open.unicef.org/</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-population-fund-unfpa/</t>
+          <t>https://www.linkedin.com/company/unicef/</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>https://x.com/UNFPA</t>
+          <t>https://x.com/UNICEF</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr"/>
@@ -11569,119 +11709,83 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UNGC</t>
+          <t>UNICEF EB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>United Nations Global Compact</t>
+          <t>Executive Board of the United Nations Children's Fund</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>United Nations Global Compact (UNGC)</t>
+          <t>Executive Board of the United Nations Children's Fund (UNICEF EB)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>The United Nations Global Compact is a voluntary initiative based on CEO commitments to implement universal sustainability principles and to undertake partnerships in support of UN goals.</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://unglobalcompact.org/</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Global_Compact</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>https://unglobalcompact.org/news</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
-        </is>
-      </c>
+          <t>https://www.unicef.org/executiveboard/</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>https://unglobalcompact.org/participation/getting-started/brand-guidelines</t>
-        </is>
-      </c>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="b">
-        <v>0</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>https://unglobalcompact.org/what-is-gc/strategy</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>https://unglobalcompact.org/library</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-global-compact/</t>
-        </is>
-      </c>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
-      <c r="AH126" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>UNGEGN</t>
+          <t>UNICRI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>United Nations Group of Experts on Geographical Names</t>
+          <t>United Nations Interregional Crime and Justice Research Institute</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>United Nations Group of Experts on Geographical Names (UNGEGN)</t>
+          <t>United Nations Interregional Crime and Justice Research Institute (UNICRI)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -11689,24 +11793,18 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/unsd/ungegn</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Group_of_Experts_on_Geographical_Names</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+          <t>https://unicri.org/</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="b">
+        <v>1</v>
+      </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
@@ -11716,7 +11814,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Other Bodies and Committees</t>
+          <t>Research and Training</t>
         </is>
       </c>
       <c r="S127" t="inlineStr"/>
@@ -11728,31 +11826,15 @@
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
+      <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>https://unstats.un.org/unsd/ungegn/sessions/2nd_session_2021/documents/UNGEGN_Strategic_Plan_final_5May2021.pdf</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>https://unstats.un.org/unsd/ungegn/sessions/</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+          <t>https://unicri.org/sites/default/files/2020-07/UNICRI_AI_CentreStrategicPlan.pdf</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr"/>
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
@@ -11763,44 +11845,39 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>UNHCR</t>
+          <t>UNIDIR</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Office of the United Nations High Commissioner for Refugees</t>
+          <t>United Nations Institute for Disarmament Research</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Office of the United Nations High Commissioner for Refugees (UNHCR)</t>
+          <t>United Nations Institute for Disarmament Research (UNIDIR)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>The work of the Office of the UNHCR is humanitarian and non-political. Its principal functions are to provide international protection to refugees and other persons of concern, and to seek durable solutions for them.</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+          <t>The UNIDIR is an autonomous body of the UN, established by the General Assembly to carry out independent research on disarmament and related international security issues.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/</t>
+          <t>https://www.unidir.org/</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_High_Commissioner_for_Refugees</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Disarmament_Research</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/news</t>
+          <t>https://www.unidir.org/news</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -11821,12 +11898,12 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Research and Training</t>
         </is>
       </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
@@ -11834,35 +11911,39 @@
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/us/budget-and-expenditure</t>
+          <t>https://unidir.org/who-we-are/funding-and-support/</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/media/unhcrs-results-areas</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022-2026.pdfhttps://www.unhcr.org/sites/default/files/2025-06/UNHCR%20Strategic%20Directions%202022--2026.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>https://www.unhcr.org/cgi-bin/texis/vtx/search?page=&amp;comid=3b4f07fd4&amp;cid=49aea93a20&amp;scid=49aea93a16&amp;keywords=UNHCR%20Annual%20Reports%20General%20Assembly</t>
+          <t>https://unidir.org/report-of-the-director</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>https://reporting.unhcr.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unhcr/</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/unidir</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>https://x.com/UNIDIR</t>
+        </is>
+      </c>
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>1</v>
@@ -11872,69 +11953,64 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UNICEF</t>
+          <t>UNIDO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>United Nations Children's Fund</t>
+          <t>United Nations Industrial Development Organization</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>United Nations Children's Fund (UNICEF)</t>
+          <t>United Nations Industrial Development Organization (UNIDO)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UNICEF works in the world’s toughest places to reach the most disadvantaged children and to protect the rights of every child, everywhere.</t>
+          <t>UNIDO's objective is the promotion and acceleration of industrial development in developing countries and countries with economies in transition and the promotion of international industrial cooperation.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
           <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
 </t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/</t>
+          <t>https://www.unido.org/</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/UNICEF</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Industrial_Development_Organization</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/press-releases</t>
+          <t>https://www.unido.org/news</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="b">
-        <v>1</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>New York City, USA</t>
+          <t>Vienna, Austria</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="b">
         <v>1</v>
@@ -11944,42 +12020,42 @@
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/media/21691/file/Integrated-Budget-MTR-Annexes.pdf</t>
+          <t>https://www.unido.org/sites/default/files/unido-publications/2025-04/ANNUAL%20REPORT%202024.pdf</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/documents/unicef-integrated-budget-2026-2029-srs-2025</t>
+          <t>https://www.unido.org/resources/policymaking-organs/programme-and-budget-committee/reports-programme-and-budget-committee</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/media/32061/file/2025-29-Add1-SP-2026-2029-IRRF-EN-2025-07-21.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/documents/unicef-strategic-plan-2026-2029-draft-review-as-2025</t>
+          <t>https://www.unido.org/publications/key-policy-documents</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/topics/annual-report</t>
+          <t>https://www.unido.org/annualreport</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>https://open.unicef.org/</t>
+          <t>https://open.unido.org/</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unicef/</t>
+          <t>https://www.linkedin.com/company/unido/</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>https://x.com/UNICEF</t>
+          <t>https://x.com/UNIDO</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr"/>
@@ -11991,112 +12067,154 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UNICEF EB</t>
+          <t>UNIFIL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Executive Board of the United Nations Children's Fund</t>
+          <t>United Nations Interim Force in Lebanon</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Executive Board of the United Nations Children's Fund (UNICEF EB)</t>
+          <t>United Nations Interim Force in Lebanon (UNIFIL)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>UNIFIL was created to confirm Israeli withdrawal from Lebanon, restore international peace and security and assist the Lebanese Government in restoring its effective authority in the area.</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.unicef.org/executiveboard/</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+          <t>https://unifil.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Force_in_Lebanon</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://unifil.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="b">
+        <v>1</v>
+      </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
-      <c r="T130" t="inlineStr"/>
+          <t>Peacekeeping Operations</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="b">
+        <v>0</v>
+      </c>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
-      <c r="Z130" t="inlineStr"/>
-      <c r="AA130" t="inlineStr"/>
-      <c r="AB130" t="inlineStr"/>
-      <c r="AC130" t="inlineStr"/>
-      <c r="AD130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>https://unifil.unmissions.org/unifil-documents</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UNICRI</t>
+          <t>UNISFA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>United Nations Interregional Crime and Justice Research Institute</t>
+          <t>United Nations Interim Security Force for Abyei</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>United Nations Interregional Crime and Justice Research Institute (UNICRI)</t>
+          <t>United Nations Interim Security Force for Abyei (UNISFA)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>UNISFA enhances the peace and stability, through operations to ensure that the Abyei Area is weapons-free and reducing intercommunal tensions by employing conflict prevention measures and promoting dialogue.</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://unicri.org/</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+          <t>https://unisfa.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Security_Force_for_Abyei</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://unisfa.unmissions.org/en/news</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="b">
-        <v>1</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Research and Training</t>
+          <t>Peacekeeping Operations</t>
         </is>
       </c>
       <c r="S131" t="inlineStr"/>
@@ -12108,16 +12226,36 @@
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
-      <c r="Z131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>https://unicri.org/sites/default/files/2020-07/UNICRI_AI_CentreStrategicPlan.pdf</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr"/>
-      <c r="AC131" t="inlineStr"/>
-      <c r="AD131" t="inlineStr"/>
-      <c r="AE131" t="inlineStr"/>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>https://digitallibrary.un.org/search?ln=en&amp;cc=Reports&amp;p=%22UN+Interim+Security+Force+for+Abyei%22+OR+UNISFA&amp;f=&amp;action_search=Search&amp;rm=&amp;ln=en&amp;sf=year&amp;so=d&amp;rg=50&amp;c=Reports&amp;c=&amp;of=hb&amp;fti=0&amp;fti=0</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>https://x.com/UNISFA_1</t>
+        </is>
+      </c>
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>1</v>
@@ -12127,46 +12265,48 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UNIDIR</t>
+          <t>UNITAR</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>United Nations Institute for Disarmament Research</t>
+          <t>United Nations Institute for Training and Research</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>United Nations Institute for Disarmament Research (UNIDIR)</t>
+          <t>United Nations Institute for Training and Research (UNITAR)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>The UNIDIR is an autonomous body of the UN, established by the General Assembly to carry out independent research on disarmament and related international security issues.</t>
+          <t>The United Nations Institute for Training and Research (UNITAR) provides innovative learning solutions to individuals, organizations and institutions to enhance global decision-making and support country-level action for shaping a better future.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.unidir.org/</t>
+          <t>https://unitar.org/</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Disarmament_Research</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Training_and_Research</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://www.unidir.org/news</t>
+          <t>https://unitar.org/news-events</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="b">
+        <v>1</v>
+      </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -12193,22 +12333,22 @@
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>https://unidir.org/who-we-are/funding-and-support/</t>
+          <t>https://unitar.org/about/programme-budget</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unitar.org/results-evidence-learning/results-reports-and-other-reports</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unitar.org/sites/default/files/media/publication/doc/UNITAR_Strategic%20Framework_2022-2025.pdf</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>https://unidir.org/report-of-the-director</t>
+          <t>https://unitar.org/about/unitar/governance/board-trustees/board-reports</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -12218,12 +12358,12 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unidir</t>
+          <t>https://www.linkedin.com/company/unitar</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>https://x.com/UNIDIR</t>
+          <t>https://x.com/UNITAR</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr"/>
@@ -12235,162 +12375,112 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNIDO</t>
+          <t>UNJSPB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>United Nations Industrial Development Organization</t>
+          <t>United Nations Joint Staff Pension Board</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>United Nations Industrial Development Organization (UNIDO)</t>
+          <t>United Nations Joint Staff Pension Board (UNJSPB)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>UNIDO's objective is the promotion and acceleration of industrial development in developing countries and countries with economies in transition and the promotion of international industrial cooperation.</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.unido.org/</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Industrial_Development_Organization</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>https://www.unido.org/news</t>
-        </is>
-      </c>
+          <t>https://www.unjspf.org/governance/</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Vienna, Austria</t>
-        </is>
-      </c>
+      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="b">
-        <v>1</v>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Boards</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>https://www.unido.org/sites/default/files/unido-publications/2025-04/ANNUAL%20REPORT%202024.pdf</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>https://www.unido.org/resources/policymaking-organs/programme-and-budget-committee/reports-programme-and-budget-committee</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>https://www.unido.org/publications/key-policy-documents</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>https://www.unido.org/annualreport</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>https://open.unido.org/</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unido/</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>https://x.com/UNIDO</t>
-        </is>
-      </c>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>UNMIK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
+          <t>United Nations Interim Administration Mission in Kosovo</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon (UNIFIL)</t>
+          <t>United Nations Interim Administration Mission in Kosovo (UNMIK)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>UNIFIL was created to confirm Israeli withdrawal from Lebanon, restore international peace and security and assist the Lebanese Government in restoring its effective authority in the area.</t>
+          <t>Following the declaration of independence by the Kosovo authorities in 2008, the UNMIK has been mandated to focus primarily on the promotion of security, stability and respect for human rights in Kosovo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://unifil.unmissions.org/</t>
+          <t>https://unmik.unmissions.org/</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Force_in_Lebanon</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Administration_Mission_in_Kosovo</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://unifil.unmissions.org/news</t>
+          <t>https://unmik.unmissions.org/news</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="b">
-        <v>1</v>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr">
@@ -12407,10 +12497,19 @@
       <c r="T134" t="b">
         <v>0</v>
       </c>
-      <c r="U134" t="inlineStr"/>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unmik.unmissions.org/mandate&gt;
+</t>
+        </is>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>https://unmik.unmissions.org/united-nations-resolution-1244</t>
+        </is>
+      </c>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr">
         <is>
@@ -12424,7 +12523,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>https://unifil.unmissions.org/unifil-documents</t>
+          <t>https://unmik.unmissions.org/sg-reports</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -12434,10 +12533,14 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/unmik</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>https://x.com/UNMIKosovo</t>
+        </is>
+      </c>
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>1</v>
@@ -12447,39 +12550,39 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UNISFA</t>
+          <t>UNMISS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei</t>
+          <t>United Nations Mission in South Sudan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei (UNISFA)</t>
+          <t>United Nations Mission in South Sudan (UNMISS)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>UNISFA enhances the peace and stability, through operations to ensure that the Abyei Area is weapons-free and reducing intercommunal tensions by employing conflict prevention measures and promoting dialogue.</t>
+          <t>UNMISS' efforts in South Sudan focus on the protection of civilians, delivering humanitarian assistance, supporting the implementation of the revitalized agreement and the peace process, and monitoring and investigating human rights</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://unisfa.unmissions.org/</t>
+          <t>https://unmiss.unmissions.org/</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Security_Force_for_Abyei</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Mission_in_South_Sudan</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://unisfa.unmissions.org/en/news</t>
+          <t>https://unmiss.unmissions.org/news</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -12503,7 +12606,12 @@
       <c r="T135" t="b">
         <v>0</v>
       </c>
-      <c r="U135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unmiss.unmissions.org/mandate&gt;
+</t>
+        </is>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
@@ -12520,7 +12628,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>https://digitallibrary.un.org/search?ln=en&amp;cc=Reports&amp;p=%22UN+Interim+Security+Force+for+Abyei%22+OR+UNISFA&amp;f=&amp;action_search=Search&amp;rm=&amp;ln=en&amp;sf=year&amp;so=d&amp;rg=50&amp;c=Reports&amp;c=&amp;of=hb&amp;fti=0&amp;fti=0</t>
+          <t>https://unmiss.unmissions.org/documents</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -12530,12 +12638,12 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/unmiss/</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>https://x.com/UNISFA_1</t>
+          <t>https://x.com/unmissmedia</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr"/>
@@ -12547,62 +12655,56 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UNITAR</t>
+          <t>UNMOGIP</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>United Nations Institute for Training and Research</t>
+          <t>United Nations Military Observer Group in India and Pakistan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>United Nations Institute for Training and Research (UNITAR)</t>
+          <t>United Nations Military Observer Group in India and Pakistan (UNMOGIP)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>The United Nations Institute for Training and Research (UNITAR) provides innovative learning solutions to individuals, organizations and institutions to enhance global decision-making and support country-level action for shaping a better future.</t>
+          <t>UNMOGIP supervises, in the State of Jammu and Kashmir, the ceasefire between India and Pakistan, and assists the Military Adviser to the United Nations Commission for India and Pakistan</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://unitar.org/</t>
+          <t>https://unmogip.unmissions.org/</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Institute_for_Training_and_Research</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Military_Observer_Group_in_India_and_Pakistan</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://unitar.org/news-events</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="b">
-        <v>1</v>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Research and Training</t>
+          <t>Peacekeeping Operations</t>
         </is>
       </c>
       <c r="S136" t="inlineStr"/>
@@ -12613,24 +12715,20 @@
       <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>https://unitar.org/about/programme-budget</t>
-        </is>
-      </c>
+      <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>https://unitar.org/results-evidence-learning/results-reports-and-other-reports</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>https://unitar.org/sites/default/files/media/publication/doc/UNITAR_Strategic%20Framework_2022-2025.pdf</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>https://unitar.org/about/unitar/governance/board-trustees/board-reports</t>
+          <t>https://unmogip.unmissions.org/reports</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -12640,14 +12738,10 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unitar</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>https://x.com/UNITAR</t>
-        </is>
-      </c>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>1</v>
@@ -12657,29 +12751,41 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UNJSPB</t>
+          <t>UNOAU</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>United Nations Joint Staff Pension Board</t>
+          <t>United Nations Office to the African Union</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>United Nations Joint Staff Pension Board (UNJSPB)</t>
+          <t>United Nations Office to the African Union (UNOAU)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>UNOAU is mandated to enhance the partnership between the United Nations and the African Union in the area of peace and security and provide United Nations advice to the African Union on both long-term capacity-building and short-term operational support</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.unjspf.org/governance/</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+          <t>https://unoau.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_to_the_African_Union</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>https://unoau.unmissions.org/en/news</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
@@ -12689,73 +12795,96 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr"/>
+          <t>Special Political Missions and Other Political Presences</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="b">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unoau.unmissions.org/mandate&gt;
+</t>
+        </is>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
-      <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr"/>
-      <c r="AB137" t="inlineStr"/>
-      <c r="AC137" t="inlineStr"/>
-      <c r="AD137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>https://unoau.unmissions.org/documents</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UNMIK</t>
+          <t>UNOCA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>United Nations Interim Administration Mission in Kosovo</t>
+          <t>United Nations Regional Office for Central Africa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>United Nations Interim Administration Mission in Kosovo (UNMIK)</t>
+          <t>United Nations Regional Office for Central Africa (UNOCA)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Following the declaration of independence by the Kosovo authorities in 2008, the UNMIK has been mandated to focus primarily on the promotion of security, stability and respect for human rights in Kosovo</t>
+          <t>UNOCA has a regional mandate to help prevent conflict and consolidate peace in Central Africa and provides assistance to support preventive diplomacy and mediation in situations of tension or potential conflict.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://unmik.unmissions.org/</t>
+          <t>https://unoca.unmissions.org/</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Interim_Administration_Mission_in_Kosovo</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Regional_Office_for_Central_Africa</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://unmik.unmissions.org/news</t>
+          <t>https://unoca.unmissions.org/en/news</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -12772,7 +12901,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Peacekeeping Operations</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S138" t="inlineStr"/>
@@ -12781,17 +12910,13 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;https://unmik.unmissions.org/mandate&gt;
+          <t xml:space="preserve">&lt;https://unoca.unmissions.org/en/mandate-and-missions&gt;
 </t>
         </is>
       </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>https://unmik.unmissions.org/united-nations-resolution-1244</t>
-        </is>
-      </c>
+      <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr">
         <is>
@@ -12805,7 +12930,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>https://unmik.unmissions.org/sg-reports</t>
+          <t>https://unoca.unmissions.org/rapports-du-s%C3%A9cr%C3%A9taire-g%C3%A9n%C3%A9ral</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -12815,14 +12940,10 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unmik</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>https://x.com/UNMIKosovo</t>
-        </is>
-      </c>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>1</v>
@@ -12832,85 +12953,83 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UNMISS</t>
+          <t>UNODC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan</t>
+          <t>United Nations Office on Drugs and Crime</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan (UNMISS)</t>
+          <t>United Nations Office on Drugs and Crime (UNODC)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>UNMISS' efforts in South Sudan focus on the protection of civilians, delivering humanitarian assistance, supporting the implementation of the revitalized agreement and the peace process, and monitoring and investigating human rights</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
+          <t>The UNODC is the secretariat of the Conference of the Parties to the UN Convention against Transnational Organized Crime and of the Conference of the States Parties to the UN Convention against Corruption.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://unmiss.unmissions.org/</t>
+          <t>https://www.unodc.org/</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Mission_in_South_Sudan</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_on_Drugs_and_Crime</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://unmiss.unmissions.org/news</t>
+          <t>https://www.unodc.org/unodc/en/press/releases.html</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="b">
+        <v>1</v>
+      </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>Peacekeeping Operations</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="b">
-        <v>0</v>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unmiss.unmissions.org/mandate&gt;
-</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unodc.org/unodc/en/evaluation/reports.html</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unodc.org/unodc/en/strategy/index.html</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>https://unmiss.unmissions.org/documents</t>
+          <t>https://www.unodc.org/unodc/en/about-unodc/annual-report.html</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -12920,12 +13039,12 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unmiss/</t>
+          <t>https://www.linkedin.com/company/united-nations-office-on-drugs-and-crime-unodc/</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>https://x.com/unmissmedia</t>
+          <t>https://x.com/UNODC</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr"/>
@@ -12937,58 +13056,56 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNMOGIP</t>
+          <t>UNOG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>United Nations Military Observer Group in India and Pakistan</t>
+          <t>United Nations Office at Geneva</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>United Nations Military Observer Group in India and Pakistan (UNMOGIP)</t>
+          <t>United Nations Office at Geneva (UNOG)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>UNMOGIP supervises, in the State of Jammu and Kashmir, the ceasefire between India and Pakistan, and assists the Military Adviser to the United Nations Commission for India and Pakistan</t>
+          <t>The UNOG services more than 8,000 meetings every year, making it one of the busiest conference centres in the world. With more than 1,600 staff, it is the biggest duty stations outside of United Nations headquarters in New York.</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://unmogip.unmissions.org/</t>
+          <t>https://www.ungeneva.org/</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Military_Observer_Group_in_India_and_Pakistan</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Geneva</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.ungeneva.org/en/news-media</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="b">
+        <v>1</v>
+      </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>Peacekeeping Operations</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="b">
         <v>0</v>
@@ -13010,7 +13127,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>https://unmogip.unmissions.org/reports</t>
+          <t>https://sites.ungeneva.org/annualreport/2021/</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -13020,7 +13137,7 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/united-nations-office-at-geneva/</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr"/>
@@ -13033,39 +13150,35 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UNOAU</t>
+          <t>UNOMS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>United Nations Office to the African Union</t>
+          <t>Office of the United Nations Ombudsman and Mediation Services</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>United Nations Office to the African Union (UNOAU)</t>
+          <t>Office of the United Nations Ombudsman and Mediation Services (UNOMS)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>UNOAU is mandated to enhance the partnership between the United Nations and the African Union in the area of peace and security and provide United Nations advice to the African Union on both long-term capacity-building and short-term operational support</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://unoau.unmissions.org/</t>
+          <t>https://www.un.org/ombudsman/</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_to_the_African_Union</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Ombudsman_and_Mediation_Services</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://unoau.unmissions.org/en/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -13077,24 +13190,19 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>Secretariat</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Special Advisers, Representatives, Advocates and Envoys</t>
         </is>
       </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="b">
         <v>0</v>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unoau.unmissions.org/mandate&gt;
-</t>
-        </is>
-      </c>
+      <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
@@ -13111,7 +13219,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>https://unoau.unmissions.org/documents</t>
+          <t>https://www.un.org/ombudsman/resources/annual-reports</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -13129,73 +13237,68 @@
       <c r="AG141" t="b">
         <v>1</v>
       </c>
-      <c r="AH141" t="inlineStr"/>
+      <c r="AH141" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>UNOCA</t>
+          <t>UNON</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>United Nations Regional Office for Central Africa</t>
+          <t>United Nations Office at Nairobi</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>United Nations Regional Office for Central Africa (UNOCA)</t>
+          <t>United Nations Office at Nairobi (UNON)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>UNOCA has a regional mandate to help prevent conflict and consolidate peace in Central Africa and provides assistance to support preventive diplomacy and mediation in situations of tension or potential conflict.</t>
+          <t>The UNON performs representation and liaison functions and facilitates cooperation between with permanent missions, the host-country and other Governments, and intergovernmental and non-governmental organizations in Nairobi.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://unoca.unmissions.org/</t>
+          <t>https://www.unon.org/</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Regional_Office_for_Central_Africa</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Nairobi</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://unoca.unmissions.org/en/news</t>
+          <t>https://www.unon.org/news</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="b">
+        <v>1</v>
+      </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>Special Political Missions and Other Political Presences</t>
-        </is>
-      </c>
+          <t>Secretariat</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="b">
         <v>0</v>
       </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unoca.unmissions.org/en/mandate-and-missions&gt;
-</t>
-        </is>
-      </c>
+      <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
@@ -13212,7 +13315,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>https://unoca.unmissions.org/rapports-du-s%C3%A9cr%C3%A9taire-g%C3%A9n%C3%A9ral</t>
+          <t>No annual report</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -13222,7 +13325,7 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/united-nations-office-at-nairobi-unon/</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr"/>
@@ -13235,53 +13338,39 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>UNODC</t>
+          <t>UNOP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>United Nations Office on Drugs and Crime</t>
+          <t>United Nations Office for Partnerships</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>United Nations Office on Drugs and Crime (UNODC)</t>
+          <t>United Nations Office for Partnerships (UNOP)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>The UNODC is the secretariat of the Conference of the Parties to the UN Convention against Transnational Organized Crime and of the Conference of the States Parties to the UN Convention against Corruption.</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+          <t xml:space="preserve">- The United Nations Office for Partnerships is the focal point vis-a-vis the United Nations Foundation, Inc.
 </t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.unodc.org/</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_on_Drugs_and_Crime</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>https://www.unodc.org/unodc/en/press/releases.html</t>
-        </is>
-      </c>
+          <t>https://unpartnerships.un.org/</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="b">
-        <v>1</v>
-      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr">
@@ -13292,43 +13381,23 @@
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
-      <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>https://www.unodc.org/unodc/en/evaluation/reports.html</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>https://www.unodc.org/unodc/en/strategy/index.html</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>https://www.unodc.org/unodc/en/about-unodc/annual-report.html</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/united-nations-office-on-drugs-and-crime-unodc/</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>https://x.com/UNODC</t>
-        </is>
-      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>https://mptf.undp.org/participating-organizations/unop</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>1</v>
@@ -13338,64 +13407,79 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UNOG</t>
+          <t>UNOPS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>United Nations Office at Geneva</t>
+          <t>United Nations Office for Project Services</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>United Nations Office at Geneva (UNOG)</t>
+          <t>United Nations Office for Project Services (UNOPS)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>The UNOG services more than 8,000 meetings every year, making it one of the busiest conference centres in the world. With more than 1,600 staff, it is the biggest duty stations outside of United Nations headquarters in New York.</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
+          <t>UNOPS' mission is to expand the capacity of the UN system and its partners to implement peace building, humanitarian and development operations that matter for people in need.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.ungeneva.org/</t>
+          <t>https://www.unops.org/</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Geneva</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Project_Services</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://www.ungeneva.org/en/news-media</t>
+          <t>https://www.unops.org/news-and-stories</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="b">
-        <v>1</v>
-      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Copenhagen, Denmark</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Other Entities</t>
+        </is>
+      </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>https://content.unops.org/documents/libraries/policies-2020/executive-office-directives-and-instructions/organizational-principles-and-governance-model/en/UNOPS-organigramme_EN.pdf</t>
+        </is>
+      </c>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr">
         <is>
@@ -13404,22 +13488,22 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://docs.un.org/en/DP/OPS/2025/9</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>https://sites.ungeneva.org/annualreport/2021/</t>
+          <t>https://www.unops.org/about/governance/executive-board/executive-board-documents</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://data.unops.org/</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-office-at-geneva/</t>
+          <t>https://www.linkedin.com/company/unops/</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr"/>
@@ -13432,17 +13516,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>UNOMS</t>
+          <t>UNOSSC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Office of the United Nations Ombudsman and Mediation Services</t>
+          <t>United Nations Office for South-South Cooperation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Office of the United Nations Ombudsman and Mediation Services (UNOMS)</t>
+          <t>United Nations Office for South-South Cooperation (UNOSSC)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -13450,19 +13534,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.un.org/ombudsman/</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Ombudsman_and_Mediation_Services</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
+          <t>https://unsouthsouth.org/</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
@@ -13472,12 +13548,12 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Secretariat</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Special Advisers, Representatives, Advocates and Envoys</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S145" t="inlineStr"/>
@@ -13489,76 +13565,54 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>https://www.un.org/ombudsman/resources/annual-reports</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH145" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>UNON</t>
+          <t>UNOV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>United Nations Office at Nairobi</t>
+          <t>United Nations Office at Vienna</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>United Nations Office at Nairobi (UNON)</t>
+          <t>United Nations Office at Vienna (UNOV)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>The UNON performs representation and liaison functions and facilitates cooperation between with permanent missions, the host-country and other Governments, and intergovernmental and non-governmental organizations in Nairobi.</t>
+          <t>The UNOV performs representation and liaison functions with permanent missions to the United Nations (Vienna), the host Government and intergovernmental and non-governmental organizations in Vienna.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.unon.org/</t>
+          <t>https://www.unvienna.org/</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Nairobi</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Vienna</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://www.unon.org/news</t>
+          <t>https://www.unvienna.org/unov/en/news.html</t>
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
@@ -13576,7 +13630,11 @@
         </is>
       </c>
       <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>EntityCard</t>
+        </is>
+      </c>
       <c r="T146" t="b">
         <v>0</v>
       </c>
@@ -13597,7 +13655,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>No annual report</t>
+          <t>No annual report (only from the SG)</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -13607,7 +13665,7 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-office-at-nairobi-unon/</t>
+          <t>https://www.linkedin.com/company/united-nations-office-at-vienna/</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr"/>
@@ -13620,34 +13678,41 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>UNOP</t>
+          <t>UNOWAS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>United Nations Office for Partnerships</t>
+          <t>United Nations Office for West Africa and the Sahel</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>United Nations Office for Partnerships (UNOP)</t>
+          <t>United Nations Office for West Africa and the Sahel (UNOWAS)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- The United Nations Office for Partnerships is the focal point vis-a-vis the United Nations Foundation, Inc.
-</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>UNOWAS has the responsibility for preventive diplomacy, good offices and political mediation and facilitation efforts in West Africa and the Sahel and works to consolidate peace and democratic governance in countries emerging from conflict or political crises.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://unpartnerships.un.org/</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+          <t>https://unowas.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_West_Africa_and_the_Sahel</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://unowas.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
@@ -13657,28 +13722,57 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr"/>
+          <t>Security Council</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Special Political Missions and Other Political Presences</t>
+        </is>
+      </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="b">
         <v>0</v>
       </c>
-      <c r="U147" t="inlineStr"/>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unowas.unmissions.org/unowas-mandate&gt;
+</t>
+        </is>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>https://mptf.undp.org/participating-organizations/unop</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
-      <c r="AB147" t="inlineStr"/>
-      <c r="AC147" t="inlineStr"/>
-      <c r="AD147" t="inlineStr"/>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>https://unowas.unmissions.org/unowas-mandate</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>https://unowas.unmissions.org/reports</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
@@ -13689,44 +13783,39 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>UNOPS</t>
+          <t>UNRCCA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>United Nations Office for Project Services</t>
+          <t>United Nations Regional Centre for Preventive Diplomacy for Central Asia</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>United Nations Office for Project Services (UNOPS)</t>
+          <t>United Nations Regional Centre for Preventive Diplomacy for Central Asia (UNRCCA)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>UNOPS' mission is to expand the capacity of the UN system and its partners to implement peace building, humanitarian and development operations that matter for people in need.</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+          <t>The UNRCCA implements the concept of preventive diplomacy in practice through enhanced dialogue, confidence building measures and genuine partnerships in responding to existing and emerging challenges in Central Asia.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.unops.org/</t>
+          <t>https://unrcca.unmissions.org/</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_Project_Services</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Regional_Centre_for_Preventive_Diplomacy_for_Central_Asia</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://www.unops.org/news-and-stories</t>
+          <t>https://unrcca.unmissions.org/news</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
@@ -13735,33 +13824,30 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Copenhagen, Denmark</t>
-        </is>
-      </c>
+      <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="b">
-        <v>1</v>
-      </c>
-      <c r="U148" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;https://unrcca.unmissions.org/mandate&gt;
+</t>
+        </is>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>https://content.unops.org/documents/libraries/policies-2020/executive-office-directives-and-instructions/organizational-principles-and-governance-model/en/UNOPS-organigramme_EN.pdf</t>
-        </is>
-      </c>
+      <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr">
         <is>
@@ -13770,22 +13856,22 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/DP/OPS/2025/9</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>https://www.unops.org/about/governance/executive-board/executive-board-documents</t>
+          <t>https://unrcca.unmissions.org/reports</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>https://data.unops.org/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unops/</t>
+          <t>https://www.linkedin.com/company/un-regional-center-for-preventive-diplomacy-for-central-asia-unrcca-</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr"/>
@@ -13798,25 +13884,29 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>UNOSSC</t>
+          <t>UNRISD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>United Nations Office for South-South Cooperation</t>
+          <t>United Nations Research Institute for Social Development</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>United Nations Office for South-South Cooperation (UNOSSC)</t>
+          <t>United Nations Research Institute for Social Development (UNRISD)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>UNRISD co-creates knowledge and insight on the social dimensions of contemporary development issues through interdisciplinary research and policy analysis with our global networks.</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://unsouthsouth.org/</t>
+          <t>https://www.unrisd.org/</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -13830,12 +13920,12 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Funds and Programmes</t>
+          <t>Research and Training</t>
         </is>
       </c>
       <c r="S149" t="inlineStr"/>
@@ -13848,53 +13938,62 @@
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="inlineStr"/>
-      <c r="AA149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>https://cdn.unrisd.org/assets/legacy-files/301-info-files/4A1D94EBE95DA31A802586D8004198E8/UNRISD-Strategy-2021-2025.pdf</t>
+        </is>
+      </c>
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="inlineStr"/>
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>UNOV</t>
+          <t>UNRWA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>United Nations Office at Vienna</t>
+          <t>United Nations Relief and Works Agency for Palestine Refugees in the Near East</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>United Nations Office at Vienna (UNOV)</t>
+          <t>United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>The UNOV performs representation and liaison functions with permanent missions to the United Nations (Vienna), the host Government and intergovernmental and non-governmental organizations in Vienna.</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
+          <t>The UNRWA carries out direct relief and works programmes for Palestine refugees.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.unvienna.org/</t>
+          <t>https://www.unrwa.org/</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_at_Vienna</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Relief_and_Works_Agency_for_Palestine_Refugees_in_the_Near_East</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://www.unvienna.org/unov/en/news.html</t>
+          <t>https://www.unrwa.org/news</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
@@ -13905,49 +14004,57 @@
         <v>1</v>
       </c>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Amman, Jordan</t>
+        </is>
+      </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>EntityCard</t>
-        </is>
-      </c>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Other Entities</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
       <c r="T150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr"/>
-      <c r="Y150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>https://www.unrwa.org/how-you-can-help/how-we-spend-funds/core-programme-budget</t>
+        </is>
+      </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unrwa.org/resources/strategy-policy</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.unrwa.org/resources/strategy-policy</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>No annual report (only from the SG)</t>
+          <t>https://www.unrwa.org/tags/annual-report</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://open.unrwa.org/</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-office-at-vienna/</t>
+          <t>https://www.linkedin.com/company/unrwa</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr"/>
@@ -13960,39 +14067,40 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>UNOWAS</t>
+          <t>UNSCO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>United Nations Office for West Africa and the Sahel</t>
+          <t>Office of the United Nations Special Coordinator for the Middle East Peace Process</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>United Nations Office for West Africa and the Sahel (UNOWAS)</t>
+          <t>Office of the United Nations Special Coordinator for the Middle East Peace Process (UNSCO)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UNOWAS has the responsibility for preventive diplomacy, good offices and political mediation and facilitation efforts in West Africa and the Sahel and works to consolidate peace and democratic governance in countries emerging from conflict or political crises.</t>
+          <t xml:space="preserve">The Office of the United Nations Special Coordinator for the Middle East Peace Process (UNSCO) is mandated to coordinate UN activities related to the Middle East peace process, support negotiations aimed at achieving a peaceful resolution to the Israeli-Palestinian conflict, and mobilize international support towards a comprehensive, just, and lasting peace.
+</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://unowas.unmissions.org/</t>
+          <t>https://unsco.unmissions.org/</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Office_for_West_Africa_and_the_Sahel</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Special_Coordinator_for_the_Middle_East_Peace_Process</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://unowas.unmissions.org/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
@@ -14016,19 +14124,10 @@
       <c r="T151" t="b">
         <v>0</v>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unowas.unmissions.org/unowas-mandate&gt;
-</t>
-        </is>
-      </c>
+      <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" t="inlineStr"/>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>https://unowas.unmissions.org/unowas-mandate</t>
-        </is>
-      </c>
+      <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr">
         <is>
@@ -14042,7 +14141,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>https://unowas.unmissions.org/reports</t>
+          <t>https://unsco.unmissions.org/ahlc-socioeconomic-reports</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -14060,44 +14159,46 @@
       <c r="AG151" t="b">
         <v>1</v>
       </c>
-      <c r="AH151" t="inlineStr"/>
+      <c r="AH151" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>UNRCCA</t>
+          <t>UNSCOL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>United Nations Regional Centre for Preventive Diplomacy for Central Asia</t>
+          <t>Office of the United Nations Special Coordinator for Lebanon</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>United Nations Regional Centre for Preventive Diplomacy for Central Asia (UNRCCA)</t>
+          <t>Office of the United Nations Special Coordinator for Lebanon (UNSCOL)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>The UNRCCA implements the concept of preventive diplomacy in practice through enhanced dialogue, confidence building measures and genuine partnerships in responding to existing and emerging challenges in Central Asia.</t>
+          <t>The UNSCOL provides leadership and coordination to UN efforts in Lebanon, assistinng the country in forging a peaceful, stable and democratic future.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://unrcca.unmissions.org/</t>
+          <t>https://unscol.unmissions.org/</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Regional_Centre_for_Preventive_Diplomacy_for_Central_Asia</t>
+          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Special_Coordinator_for_Lebanon</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://unrcca.unmissions.org/news</t>
+          <t>https://unscol.unmissions.org/news</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
@@ -14121,12 +14222,7 @@
       <c r="T152" t="b">
         <v>0</v>
       </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://unrcca.unmissions.org/mandate&gt;
-</t>
-        </is>
-      </c>
+      <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr"/>
@@ -14143,7 +14239,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>https://unrcca.unmissions.org/reports</t>
+          <t>https://unscol.unmissions.org/secretary-general-statements-relevant-lebanon</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -14153,7 +14249,7 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/un-regional-center-for-preventive-diplomacy-for-central-asia-unrcca-</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr"/>
@@ -14166,48 +14262,58 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>UNRISD</t>
+          <t>UNSMIL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>United Nations Research Institute for Social Development</t>
+          <t>United Nations Support Mission in Libya</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>United Nations Research Institute for Social Development (UNRISD)</t>
+          <t>United Nations Support Mission in Libya (UNSMIL)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>UNRISD co-creates knowledge and insight on the social dimensions of contemporary development issues through interdisciplinary research and policy analysis with our global networks.</t>
+          <t>UNSMIL, in full accordannce with the principles of national ownership, is an integrated special political mission that supports support Libya's new transitional authorities in their post-conflict efforts.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.unrisd.org/</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
+          <t>https://unsmil.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Support_Mission_in_Libya</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://unsmil.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="b">
+        <v>1</v>
+      </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Research and Training</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S153" t="inlineStr"/>
@@ -14219,15 +14325,31 @@
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
-      <c r="Z153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>https://unsmil.unmissions.org/un-libya-results-report-2022</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>https://cdn.unrisd.org/assets/legacy-files/301-info-files/4A1D94EBE95DA31A802586D8004198E8/UNRISD-Strategy-2021-2025.pdf</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr"/>
-      <c r="AC153" t="inlineStr"/>
-      <c r="AD153" t="inlineStr"/>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>https://unsmil.unmissions.org/reports-secretary-general</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/united-nations-support-mission-in-libya</t>
+        </is>
+      </c>
       <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
@@ -14238,107 +14360,64 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>UNRWA</t>
+          <t>UNSOH</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>United Nations Relief and Works Agency for Palestine Refugees in the Near East</t>
+          <t>United Nations Support Office in Haiti</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA)</t>
+          <t>United Nations Support Office in Haiti (UNSOH)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>The UNRWA carries out direct relief and works programmes for Palestine refugees.</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.unrwa.org/</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Relief_and_Works_Agency_for_Palestine_Refugees_in_the_Near_East</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>https://www.unrwa.org/news</t>
-        </is>
-      </c>
+          <t>https://www.unmissions.org/unsoh</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="b">
-        <v>1</v>
-      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Amman, Jordan</t>
-        </is>
-      </c>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>General Assembly</t>
+          <t>Security Council</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Other Entities</t>
+          <t>Special Political Missions and Other Political Presences</t>
         </is>
       </c>
       <c r="S154" t="inlineStr"/>
-      <c r="T154" t="b">
-        <v>1</v>
-      </c>
-      <c r="U154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.unmissions.org/en/unsoh/mandate
+**The United Nations Support Office in Haiti (UNSOH)** was established on 30 September 2025 by **UN Security Council Resolution 2793** following the Secretary General’s assessment that a UN Support Office should provide comprehensive logistical and operational support to the Gang Suppression Force in Haiti (GSF), BINUH, the Haitian National Police (HNP) and the Haitian armed forces on any joint operations with the GSF, as well as technical support to the Organization of American States (OAS), in full compliance with the Secretary-General’s HRDDP
+</t>
+        </is>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr"/>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>https://www.unrwa.org/how-you-can-help/how-we-spend-funds/core-programme-budget</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>https://www.unrwa.org/resources/strategy-policy</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>https://www.unrwa.org/resources/strategy-policy</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>https://www.unrwa.org/tags/annual-report</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>https://open.unrwa.org/</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/unrwa</t>
-        </is>
-      </c>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
       <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
@@ -14349,57 +14428,62 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>UNSCO</t>
+          <t>UNSSC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Office of the United Nations Special Coordinator for the Middle East Peace Process</t>
+          <t>United Nations System Staff College</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Office of the United Nations Special Coordinator for the Middle East Peace Process (UNSCO)</t>
+          <t>United Nations System Staff College (UNSSC)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Office of the United Nations Special Coordinator for the Middle East Peace Process (UNSCO) is mandated to coordinate UN activities related to the Middle East peace process, support negotiations aimed at achieving a peaceful resolution to the Israeli-Palestinian conflict, and mobilize international support towards a comprehensive, just, and lasting peace.
-</t>
+          <t>The UNSSC delivers high-quality learning programmes and tailored solutions for UN staff and partners, equipping them with the knowledge and skills to support important UN activities and objectives.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://unsco.unmissions.org/</t>
+          <t>https://www.unssc.org/</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Special_Coordinator_for_the_Middle_East_Peace_Process</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_System_Staff_College</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://www.unssc.org/news</t>
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="b">
+        <v>1</v>
+      </c>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Turin, Italy</t>
+        </is>
+      </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Research and Training</t>
         </is>
       </c>
       <c r="S155" t="inlineStr"/>
@@ -14410,7 +14494,11 @@
       <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr"/>
-      <c r="Y155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>https://w04.unssc.org/financial</t>
+        </is>
+      </c>
       <c r="Z155" t="inlineStr">
         <is>
           <t>No link found</t>
@@ -14423,7 +14511,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>https://unsco.unmissions.org/ahlc-socioeconomic-reports</t>
+          <t>https://www.unssc.org/about-unssc/</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -14433,56 +14521,46 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/united-nations-system-staff-college/</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>https://x.com/UNSSC</t>
+        </is>
+      </c>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>1</v>
       </c>
-      <c r="AH155" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>UNSCOL</t>
+          <t>UNTC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Office of the United Nations Special Coordinator for Lebanon</t>
+          <t>Committee of Experts on International Cooperation in Tax Matters</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Office of the United Nations Special Coordinator for Lebanon (UNSCOL)</t>
+          <t>Committee of Experts on International Cooperation in Tax Matters (UNTC)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>The UNSCOL provides leadership and coordination to UN efforts in Lebanon, assistinng the country in forging a peaceful, stable and democratic future.</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://unscol.unmissions.org/</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Office_of_the_United_Nations_Special_Coordinator_for_Lebanon</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>https://unscol.unmissions.org/news</t>
-        </is>
-      </c>
+          <t>https://financing.desa.un.org/what-we-do/ECOSOC/tax-committee/tax-committee-home</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
@@ -14492,100 +14570,76 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Security Council</t>
+          <t>Economic and Social Council</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Other Bodies and Committees</t>
         </is>
       </c>
       <c r="S156" t="inlineStr"/>
-      <c r="T156" t="b">
-        <v>0</v>
-      </c>
+      <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>https://unscol.unmissions.org/secretary-general-statements-relevant-lebanon</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>Not found.</t>
-        </is>
-      </c>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
       <c r="AE156" t="inlineStr"/>
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>UNSMIL</t>
+          <t>UNTMIS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>United Nations Support Mission in Libya</t>
+          <t>United Nations Transitional Assistance Mission in Somalia</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>United Nations Support Mission in Libya (UNSMIL)</t>
+          <t>United Nations Transitional Assistance Mission in Somalia (UNTMIS)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UNSMIL, in full accordannce with the principles of national ownership, is an integrated special political mission that supports support Libya's new transitional authorities in their post-conflict efforts.</t>
+          <t>The United Nations Transitional Assistance Mission in Somalia (UNTMIS) succeeded the United Nations Assistance Mission in Somalia (UNSOM) as of 1 November 2024 following the conclusion of UNSOM’s operations on 31 October 2024, in accordance with UN Security Council resolution 2753.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://unsmil.unmissions.org/</t>
+          <t>https://dppa.un.org/en/mission/untmis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Support_Mission_in_Libya</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://unsmil.unmissions.org/news</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="b">
-        <v>1</v>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr">
@@ -14609,7 +14663,7 @@
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>https://unsmil.unmissions.org/un-libya-results-report-2022</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -14619,7 +14673,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>https://unsmil.unmissions.org/reports-secretary-general</t>
+          <t>No annual report</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -14629,7 +14683,7 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-support-mission-in-libya</t>
+          <t>Not found.</t>
         </is>
       </c>
       <c r="AE157" t="inlineStr"/>
@@ -14642,29 +14696,41 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>UNSOH</t>
+          <t>UNTSO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Haiti</t>
+          <t>United Nations Truce Supervision Organization</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Haiti (UNSOH)</t>
+          <t>United Nations Truce Supervision Organization (UNTSO)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>UNTSO observers monitor ceasefires, supervise armistice agreements, prevent isolated incidents from escalating and assist other United Nations peacekeeping operations in the Middle East.</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.unmissions.org/unsoh</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
+          <t>https://untso.unmissions.org/</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Truce_Supervision_Organization</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>https://untso.unmissions.org/news</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
@@ -14679,15 +14745,16 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Special Political Missions and Other Political Presences</t>
+          <t>Peacekeeping Operations</t>
         </is>
       </c>
       <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr"/>
+      <c r="T158" t="b">
+        <v>0</v>
+      </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.unmissions.org/en/unsoh/mandate
-**The United Nations Support Office in Haiti (UNSOH)** was established on 30 September 2025 by **UN Security Council Resolution 2793** following the Secretary General’s assessment that a UN Support Office should provide comprehensive logistical and operational support to the Gang Suppression Force in Haiti (GSF), BINUH, the Haitian National Police (HNP) and the Haitian armed forces on any joint operations with the GSF, as well as technical support to the Organization of American States (OAS), in full compliance with the Secretary-General’s HRDDP
+          <t xml:space="preserve">&lt;https://untso.unmissions.org/mandate&gt;
 </t>
         </is>
       </c>
@@ -14695,54 +14762,76 @@
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
-      <c r="Z158" t="inlineStr"/>
-      <c r="AA158" t="inlineStr"/>
-      <c r="AB158" t="inlineStr"/>
-      <c r="AC158" t="inlineStr"/>
-      <c r="AD158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>https://untso.unmissions.org/documents</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
       <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>1</v>
       </c>
-      <c r="AH158" t="inlineStr"/>
+      <c r="AH158" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>UNSSC</t>
+          <t>UNU</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>United Nations System Staff College</t>
+          <t>United Nations University</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>United Nations System Staff College (UNSSC)</t>
+          <t>United Nations University (UNU)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>The UNSSC delivers high-quality learning programmes and tailored solutions for UN staff and partners, equipping them with the knowledge and skills to support important UN activities and objectives.</t>
+          <t>The mission of the UN University is to contribute, through collaborative research and education, to efforts to resolve the pressing global problems of human survival, development and welfare.</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.unssc.org/</t>
+          <t>https://unu.edu/</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_System_Staff_College</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_University</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://www.unssc.org/news</t>
+          <t>https://unu.edu/news</t>
         </is>
       </c>
       <c r="J159" t="inlineStr"/>
@@ -14755,7 +14844,7 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Turin, Italy</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -14778,22 +14867,22 @@
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://w04.unssc.org/financial</t>
+          <t>https://unu.edu/budget-and-finance</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>No centralized RBM results framework found</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://unu.edu/sites/default/files/2024-06/UNU-Strategy_2025-2029.pdf</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>https://www.unssc.org/about-unssc/</t>
+          <t>https://unu.edu/about/annual-reports</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
@@ -14803,12 +14892,12 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-system-staff-college/</t>
+          <t>https://www.linkedin.com/company/united-nations-university/</t>
         </is>
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>https://x.com/UNSSC</t>
+          <t>https://x.com/UNUniversity</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr"/>
@@ -14820,17 +14909,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>UNSU</t>
+          <t>UNU Council</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>United Nations Staff Union</t>
+          <t>Council of the United Nations University</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>United Nations Staff Union (UNSU)</t>
+          <t>Council of the United Nations University (UNU Council)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -14838,7 +14927,7 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://u-seek.org/</t>
+          <t>https://unu.edu/about/unu-council</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -14852,11 +14941,19 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>Secretariat</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
+          <t>General Assembly</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Intergovernmental and Expert Bodies</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Assemblies and Councils</t>
+        </is>
+      </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
@@ -14873,108 +14970,147 @@
       <c r="AG160" t="b">
         <v>0</v>
       </c>
-      <c r="AH160" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>UNTC</t>
+          <t>UNV</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Committee of Experts on International Cooperation in Tax Matters</t>
+          <t>United Nations Volunteers</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Committee of Experts on International Cooperation in Tax Matters (UNTC)</t>
+          <t>United Nations Volunteers (UNV)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>The United Nations Volunteers programme is a United Nations organization that open volunteer opportunities and mobilize volunteers in 150 countries.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- UNV is administered by UNDP and reports to the UNDP/UNFPA/UNOPS Executive Board.
+</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://financing.desa.un.org/what-we-do/ECOSOC/tax-committee/tax-committee-home</t>
+          <t>https://www.unv.org/</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://knowledge.unv.org/</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="b">
+        <v>1</v>
+      </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Economic and Social Council</t>
+          <t>General Assembly</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Other Bodies and Committees</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr"/>
+      <c r="T161" t="b">
+        <v>0</v>
+      </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr"/>
-      <c r="Z161" t="inlineStr"/>
-      <c r="AA161" t="inlineStr"/>
-      <c r="AB161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>https://www.unv.org/sites/default/files/UNV%20Strategic%20Framework%202022-2025.pdf</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>https://www.unv.org/publications/unv-strategic-framework-2022-2025</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>https://www.unv.org/annual-reports</t>
+        </is>
+      </c>
       <c r="AC161" t="inlineStr"/>
-      <c r="AD161" t="inlineStr"/>
-      <c r="AE161" t="inlineStr"/>
-      <c r="AF161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/united-nations-volunteers/</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>https://x.com/UNVolunteers</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unvolunteers/</t>
+        </is>
+      </c>
       <c r="AG161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>UNTMIS</t>
+          <t>UNVMC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>United Nations Transitional Assistance Mission in Somalia</t>
+          <t>United Nations Verification Mission in Colombia</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>United Nations Transitional Assistance Mission in Somalia (UNTMIS)</t>
+          <t>United Nations Verification Mission in Colombia (UNVMC)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>The United Nations Transitional Assistance Mission in Somalia (UNTMIS) succeeded the United Nations Assistance Mission in Somalia (UNSOM) as of 1 November 2024 following the conclusion of UNSOM’s operations on 31 October 2024, in accordance with UN Security Council resolution 2753.</t>
+          <t>The Mission will verify the reintegration of former FARC-EP members into political, economic and social life and the security guarantees for former FARC-EP members, their families, and communities in the territories.</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://dppa.un.org/en/mission/untmis</t>
+          <t>https://colombia.unmissions.org/</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://en.wikipedia.org/wiki/United_Nations_Verification_Mission_in_Colombia</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>https://colombia.unmissions.org/en/news</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
@@ -15015,7 +15151,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>No annual report</t>
+          <t>https://colombia.unmissions.org/en/reports-secretary-general-0</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -15025,7 +15161,7 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>Not found.</t>
+          <t>https://www.linkedin.com/company/united-nations-verification-mission-in-colombia/</t>
         </is>
       </c>
       <c r="AE162" t="inlineStr"/>
@@ -15038,85 +15174,96 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>UNTSO</t>
+          <t>UPU</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>United Nations Truce Supervision Organization</t>
+          <t>Universal Postal Union</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>United Nations Truce Supervision Organization (UNTSO)</t>
+          <t>Universal Postal Union (UPU)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>UNTSO observers monitor ceasefires, supervise armistice agreements, prevent isolated incidents from escalating and assist other United Nations peacekeeping operations in the Middle East.</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr"/>
+          <t>The UPU aims to secure the organisation and improvements of postal services, promote international collaboration and undertake technical assistance in postal matters requested by members countries.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://untso.unmissions.org/</t>
+          <t>https://www.upu.int/</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Truce_Supervision_Organization</t>
+          <t>https://en.wikipedia.org/wiki/Universal_Postal_Union</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://untso.unmissions.org/news</t>
+          <t>https://www.upu.int/en/News</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="b">
+        <v>1</v>
+      </c>
       <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Bern, Switzerland</t>
+        </is>
+      </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>Peacekeeping Operations</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="b">
-        <v>0</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;https://untso.unmissions.org/mandate&gt;
-</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" t="inlineStr"/>
-      <c r="X163" t="inlineStr"/>
-      <c r="Y163" t="inlineStr"/>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>https://www.upu.int/en/universal-postal-union/about-upu/bodies/international-bureau/organizational-structure</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>https://www.upu.int/en/universal-postal-union/about-upu/finance#programme-and-budget</t>
+        </is>
+      </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.upu.int/en/universal-postal-union/about-upu/strategy#implementation-and-monitoring</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.upu.int/en/universal-postal-union/about-upu/strategy</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>https://untso.unmissions.org/documents</t>
+          <t>https://www.upu.int/en/Universal-Postal-Union/About-UPU/Strategy</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -15126,59 +15273,74 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>Not found.</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/universal-postal-union/</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>https://x.com/UPU_UN</t>
+        </is>
+      </c>
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>1</v>
       </c>
-      <c r="AH163" t="b">
-        <v>1</v>
-      </c>
+      <c r="AH163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>UNU</t>
+          <t>WFP</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>United Nations University</t>
+          <t>World Food Programme</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>United Nations University (UNU)</t>
+          <t>World Food Programme (WFP)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>The mission of the UN University is to contribute, through collaborative research and education, to efforts to resolve the pressing global problems of human survival, development and welfare.</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr"/>
+          <t>We are the world’s largest humanitarian organization, saving lives in emergencies and using food assistance to build a pathway to peace, stability and prosperity for people recovering from conflict, disasters and the impact of climate change.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://unu.edu/</t>
+          <t>https://www.wfp.org/</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_University</t>
+          <t>https://en.wikipedia.org/wiki/World_Food_Programme</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://unu.edu/news</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
+          <t>https://www.wfp.org/news</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>www.wfp.org/UIGuide</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>https://uikit.wfp.org/docs/index.html?path=/docs/documentation-core-logos--page</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="b">
         <v>1</v>
@@ -15186,7 +15348,7 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>Rome, Italy</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -15196,35 +15358,35 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Research and Training</t>
+          <t>Funds and Programmes</t>
         </is>
       </c>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" t="inlineStr"/>
-      <c r="X164" t="inlineStr"/>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>https://unu.edu/budget-and-finance</t>
-        </is>
-      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>https://www.wfp.org/publications/wfp-organigram</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr"/>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>No centralized RBM results framework found</t>
+          <t>https://www.wfp.org/publications/corporate-results-framework-2022-2025</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>https://unu.edu/sites/default/files/2024-06/UNU-Strategy_2025-2029.pdf</t>
+          <t>https://executiveboard.wfp.org/document_download/WFP-0000132205https://www.wfp.org/publications/wfp-strategic-plan-2022-25</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>https://unu.edu/about/annual-reports</t>
+          <t>https://www.wfp.org/publications?f%5B0%5D=publication_type%3A2149</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -15234,12 +15396,12 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-university/</t>
+          <t>https://www.linkedin.com/company/world-food-programme/</t>
         </is>
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>https://x.com/UNUniversity</t>
+          <t>https://x.com/WFP</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr"/>
@@ -15251,17 +15413,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>UNU Council</t>
+          <t>WFP EB</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Council of the United Nations University</t>
+          <t>Executive Board of the World Food Programme</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Council of the United Nations University (UNU Council)</t>
+          <t>Executive Board of the World Food Programme (WFP EB)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -15269,7 +15431,7 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://unu.edu/about/unu-council</t>
+          <t>https://executiveboard.wfp.org/</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -15293,7 +15455,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>Assemblies and Councils</t>
+          <t>Boards</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -15317,101 +15479,134 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>UNV</t>
+          <t>WHO</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>United Nations Volunteers</t>
+          <t>World Health Organization</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>United Nations Volunteers (UNV)</t>
+          <t>World Health Organization (WHO)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>The United Nations Volunteers programme is a United Nations organization that open volunteer opportunities and mobilize volunteers in 150 countries.</t>
+          <t>The United Nations agency working to promote health, keep the world safe and serve the vulnerable.</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">- UNV is administered by UNDP and reports to the UNDP/UNFPA/UNOPS Executive Board.
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
 </t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.unv.org/</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+          <t>https://www.who.int/</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/World_Health_Organization</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://www.who.int/about/communications/credible-and-trusted/who-brand</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://knowledge.unv.org/</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
+          <t>https://www.who.int/data/</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>https://www.who.int/about/policies/publishing/logo</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>https://www.who.int/images/default-source/fallback/header-logos/h-logo-blue1820eae93c154e37b2588ab90fdbc17e.svg?sfvrsn=aaed4f35_20</t>
+        </is>
+      </c>
       <c r="N166" t="b">
         <v>1</v>
       </c>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>https://www.who.int/careers</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland</t>
+        </is>
+      </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" t="inlineStr"/>
-      <c r="X166" t="inlineStr"/>
-      <c r="Y166" t="inlineStr"/>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>https://cdn.who.int/media/docs/default-source/documents/about-us/who-hq-organigramme.pdf</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>https://www.who.int/about/accountability/budget</t>
+        </is>
+      </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>https://www.unv.org/sites/default/files/UNV%20Strategic%20Framework%202022-2025.pdf</t>
+          <t>https://www.who.int/publications/m/item/who-results-framework-delivering-a-measurable-impact-in-countries</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>https://www.unv.org/publications/unv-strategic-framework-2022-2025</t>
+          <t>https://www.who.int/publications/i/item/9789240061545</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>https://www.unv.org/annual-reports</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr"/>
+          <t>https://www.who.int/about/accountability/results</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>https://open.who.int/</t>
+        </is>
+      </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-volunteers/</t>
+          <t>https://www.linkedin.com/company/world-health-organization/</t>
         </is>
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>https://x.com/UNVolunteers</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/unvolunteers/</t>
-        </is>
-      </c>
+          <t>https://x.com/WHO</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>1</v>
       </c>
@@ -15420,80 +15615,96 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>UNVMC</t>
+          <t>WIPO</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>United Nations Verification Mission in Colombia</t>
+          <t>World Intellectual Property Organization</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>United Nations Verification Mission in Colombia (UNVMC)</t>
+          <t>World Intellectual Property Organization (WIPO)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>The Mission will verify the reintegration of former FARC-EP members into political, economic and social life and the security guarantees for former FARC-EP members, their families, and communities in the territories.</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
+          <t>The world’s number one source for global intellectual property (patents, industrial designs, copyright, trademarks etc.) information, resources, and services.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://colombia.unmissions.org/</t>
+          <t>https://www.wipo.int/</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/United_Nations_Verification_Mission_in_Colombia</t>
+          <t>https://en.wikipedia.org/wiki/World_Intellectual_Property_Organization</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://colombia.unmissions.org/en/news</t>
+          <t>https://www.wipo.int/news</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="b">
+        <v>1</v>
+      </c>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland</t>
+        </is>
+      </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>Security Council</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>Special Political Missions and Other Political Presences</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" t="inlineStr"/>
-      <c r="X167" t="inlineStr"/>
-      <c r="Y167" t="inlineStr"/>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/about-wipo/budget/index</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/en/web/about-wipo/budget/financial</t>
+        </is>
+      </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.wipo.int/en/web/about-wipo/budget/index</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>No link found</t>
+          <t>https://www.wipo.int/en/web/about-wipo/budget/index</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>https://colombia.unmissions.org/en/reports-secretary-general-0</t>
+          <t>https://www.wipo.int/about-wipo/en/</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -15503,10 +15714,14 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/united-nations-verification-mission-in-colombia/</t>
-        </is>
-      </c>
-      <c r="AE167" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/world-intellectual-property-organization-wipo/</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>https://x.com/WIPO</t>
+        </is>
+      </c>
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>1</v>
@@ -15516,23 +15731,23 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>UPU</t>
+          <t>WMO</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Universal Postal Union</t>
+          <t>World Meteorological Organization</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Universal Postal Union (UPU)</t>
+          <t>World Meteorological Organization (WMO)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>The UPU aims to secure the organisation and improvements of postal services, promote international collaboration and undertake technical assistance in postal matters requested by members countries.</t>
+          <t>A specialized agency of the United Nations whose mandate covers weather, climate and water resources. The UN’s scientific voice on the state and behaviour of our atmosphere and climate.</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -15544,17 +15759,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.upu.int/</t>
+          <t>https://public.wmo.int/</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Universal_Postal_Union</t>
+          <t>https://en.wikipedia.org/wiki/World_Meteorological_Organization</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://www.upu.int/en/News</t>
+          <t>https://public.wmo.int/en/media/news</t>
         </is>
       </c>
       <c r="J168" t="inlineStr"/>
@@ -15567,7 +15782,7 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Bern, Switzerland</t>
+          <t>Geneva, Switzerland</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -15585,27 +15800,27 @@
       <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr">
         <is>
-          <t>https://www.upu.int/en/universal-postal-union/about-upu/bodies/international-bureau/organizational-structure</t>
+          <t>https://wmo.int/about-wmo/governance</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://www.upu.int/en/universal-postal-union/about-upu/finance#programme-and-budget</t>
+          <t>https://wmo.int/about-wmo/finance-and-accountability</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>https://www.upu.int/en/universal-postal-union/about-upu/strategy#implementation-and-monitoring</t>
+          <t>https://community.wmo.int/en/planning-and-monitoring/operational-planning</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>https://www.upu.int/en/universal-postal-union/about-upu/strategy</t>
+          <t>https://wmo.int/about-wmo/our-mandate</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>https://www.upu.int/en/Universal-Postal-Union/About-UPU/Strategy</t>
+          <t>https://library.wmo.int/index.php?lvl=notice_display&amp;id=5301#.XxG4WJ5KiUk</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -15615,12 +15830,12 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/universal-postal-union/</t>
+          <t>https://www.linkedin.com/company/world-meteorological-organization/</t>
         </is>
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>https://x.com/UPU_UN</t>
+          <t>https://x.com/WMO</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr"/>
@@ -15632,57 +15847,47 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>WFP</t>
+          <t>WORLD BANK GROUP</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>World Food Programme</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>World Food Programme (WFP)</t>
+          <t>World Bank Group (WORLD BANK GROUP)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>We are the world’s largest humanitarian organization, saving lives in emergencies and using food assistance to build a pathway to peace, stability and prosperity for people recovering from conflict, disasters and the impact of climate change.</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+- International Centre for Settlement of Investment Disputes (ICSID) and Multilateral Investment Guarantee Agency (MIGA) are not specialized agencies in accordance with Articles 57 and 63 of the Charter, but are part of the World Bank Group.
 </t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.wfp.org/</t>
+          <t>https://www.worldbank.org/</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/World_Food_Programme</t>
+          <t>https://en.wikipedia.org/wiki/World_Bank</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://www.wfp.org/news</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>www.wfp.org/UIGuide</t>
-        </is>
-      </c>
+          <t>https://www.worldbank.org/en/news</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>https://uikit.wfp.org/docs/index.html?path=/docs/documentation-core-logos--page</t>
-        </is>
-      </c>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="b">
         <v>1</v>
@@ -15690,19 +15895,15 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Rome, Italy</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>Funds and Programmes</t>
-        </is>
-      </c>
+          <t>Specialized Agencies</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="b">
         <v>1</v>
@@ -15712,23 +15913,27 @@
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://www.wfp.org/publications/wfp-organigram</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr"/>
+          <t>https://thedocs.worldbank.org/en/doc/404071412346998230-0090022021/The-World-Bank-Organizational-Chart-English</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>https://financesone.worldbank.org/world-bank-program-budget-and-all-funds/DS00032</t>
+        </is>
+      </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>https://www.wfp.org/publications/corporate-results-framework-2022-2025</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>https://executiveboard.wfp.org/document_download/WFP-0000132205https://www.wfp.org/publications/wfp-strategic-plan-2022-25</t>
+          <t>No link found</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>https://www.wfp.org/publications?f%5B0%5D=publication_type%3A2149</t>
+          <t>https://www.worldbank.org/en/about/annual-report</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -15738,12 +15943,12 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/world-food-programme/</t>
+          <t>https://www.linkedin.com/company/world-bank/</t>
         </is>
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>https://x.com/WFP</t>
+          <t>https://x.com/WorldBank</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr"/>
@@ -15755,669 +15960,122 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>WFP EB</t>
+          <t>WTO</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Executive Board of the World Food Programme</t>
+          <t>World Trade Organization</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Executive Board of the World Food Programme (WFP EB)</t>
+          <t>World Trade Organization (WTO)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>The World Trade Organization (WTO) deals with the global rules of trade between nations. Its main function is to ensure that global trade flows smoothly, predictably and freely as possible.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
+- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
+</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://executiveboard.wfp.org/</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
+          <t>https://www.wto.org/</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/World_Trade_Organization</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/news_e/news_e.htm</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://data.wto.org/</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="b">
+        <v>1</v>
+      </c>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Geneva, Switzerland</t>
+        </is>
+      </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>General Assembly</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>Intergovernmental and Expert Bodies</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>Boards</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr"/>
+          <t>Related Organizations</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="b">
+        <v>1</v>
+      </c>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" t="inlineStr"/>
-      <c r="X170" t="inlineStr"/>
-      <c r="Y170" t="inlineStr"/>
-      <c r="Z170" t="inlineStr"/>
-      <c r="AA170" t="inlineStr"/>
-      <c r="AB170" t="inlineStr"/>
-      <c r="AC170" t="inlineStr"/>
-      <c r="AD170" t="inlineStr"/>
-      <c r="AE170" t="inlineStr"/>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/thewto_e/whatis_e/tif_e/organigram_e.pdf</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/thewto_e/secre_e/budget_e.htm</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>No link found</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/thewto_e/secretariat_strategy2030_e.htm</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/res_e/reser_e/annual_report_e.htm</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/world-trade-organization/</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>https://x.com/wto</t>
+        </is>
+      </c>
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>WHO</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>World Health Organization</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>World Health Organization (WHO)</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>The United Nations agency working to promote health, keep the world safe and serve the vulnerable.</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/World_Health_Organization</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/about/communications/credible-and-trusted/who-brand</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/data/</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/about/policies/publishing/logo</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/images/default-source/fallback/header-logos/h-logo-blue1820eae93c154e37b2588ab90fdbc17e.svg?sfvrsn=aaed4f35_20</t>
-        </is>
-      </c>
-      <c r="N171" t="b">
-        <v>1</v>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/careers</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
-      <c r="T171" t="b">
-        <v>1</v>
-      </c>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>https://cdn.who.int/media/docs/default-source/documents/about-us/who-hq-organigramme.pdf</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/about/accountability/budget</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/publications/m/item/who-results-framework-delivering-a-measurable-impact-in-countries</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/publications/i/item/9789240061545</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>https://www.who.int/about/accountability/results</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>https://open.who.int/</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/world-health-organization/</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>https://x.com/WHO</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr"/>
-      <c r="AG171" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>WIPO</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>World Intellectual Property Organization</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>World Intellectual Property Organization (WIPO)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>The world’s number one source for global intellectual property (patents, industrial designs, copyright, trademarks etc.) information, resources, and services.</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/World_Intellectual_Property_Organization</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/news</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="b">
-        <v>1</v>
-      </c>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
-      <c r="T172" t="b">
-        <v>1</v>
-      </c>
-      <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/en/web/about-wipo/budget/index</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/en/web/about-wipo/budget/financial</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/en/web/about-wipo/budget/index</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/en/web/about-wipo/budget/index</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>https://www.wipo.int/about-wipo/en/</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/world-intellectual-property-organization-wipo/</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>https://x.com/WIPO</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr"/>
-      <c r="AG172" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>WMO</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>World Meteorological Organization</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>World Meteorological Organization (WMO)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>A specialized agency of the United Nations whose mandate covers weather, climate and water resources. The UN’s scientific voice on the state and behaviour of our atmosphere and climate.</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://public.wmo.int/</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/World_Meteorological_Organization</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>https://public.wmo.int/en/media/news</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="b">
-        <v>1</v>
-      </c>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
-      <c r="T173" t="b">
-        <v>1</v>
-      </c>
-      <c r="U173" t="inlineStr"/>
-      <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>https://wmo.int/about-wmo/governance</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>https://wmo.int/about-wmo/finance-and-accountability</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>https://community.wmo.int/en/planning-and-monitoring/operational-planning</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>https://wmo.int/about-wmo/our-mandate</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>https://library.wmo.int/index.php?lvl=notice_display&amp;id=5301#.XxG4WJ5KiUk</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/world-meteorological-organization/</t>
-        </is>
-      </c>
-      <c r="AE173" t="inlineStr">
-        <is>
-          <t>https://x.com/WMO</t>
-        </is>
-      </c>
-      <c r="AF173" t="inlineStr"/>
-      <c r="AG173" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>WORLD BANK GROUP</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>World Bank Group (WORLD BANK GROUP)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-- International Centre for Settlement of Investment Disputes (ICSID) and Multilateral Investment Guarantee Agency (MIGA) are not specialized agencies in accordance with Articles 57 and 63 of the Charter, but are part of the World Bank Group.
-</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.worldbank.org/</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/World_Bank</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>https://www.worldbank.org/en/news</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="b">
-        <v>1</v>
-      </c>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>Washington, DC, USA</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>Specialized Agencies</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="b">
-        <v>1</v>
-      </c>
-      <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr"/>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>https://thedocs.worldbank.org/en/doc/404071412346998230-0090022021/The-World-Bank-Organizational-Chart-English</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>https://financesone.worldbank.org/world-bank-program-budget-and-all-funds/DS00032</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>https://www.worldbank.org/en/about/annual-report</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/world-bank/</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>https://x.com/WorldBank</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr"/>
-      <c r="AG174" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>WTO</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>World Trade Organization</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>World Trade Organization (WTO)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>The World Trade Organization (WTO) deals with the global rules of trade between nations. Its main function is to ensure that global trade flows smoothly, predictably and freely as possible.</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Member of the United Nations System Chief Executives Board for Coordination (CEB).
-- This organization is separate and independent from the United Nations. It has been brought into relationship with the United Nations through a relationship agreement.
-</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.wto.org/</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/World_Trade_Organization</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>https://www.wto.org/english/news_e/news_e.htm</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>https://data.wto.org/</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="b">
-        <v>1</v>
-      </c>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>Geneva, Switzerland</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>Related Organizations</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="b">
-        <v>1</v>
-      </c>
-      <c r="U175" t="inlineStr"/>
-      <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>https://www.wto.org/english/thewto_e/whatis_e/tif_e/organigram_e.pdf</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>https://www.wto.org/english/thewto_e/secre_e/budget_e.htm</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>No link found</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>https://www.wto.org/english/thewto_e/secretariat_strategy2030_e.htm</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>https://www.wto.org/english/res_e/reser_e/annual_report_e.htm</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/world-trade-organization/</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>https://x.com/wto</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr"/>
-      <c r="AG175" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
